--- a/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
+++ b/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
@@ -8,18 +8,23 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -203,7 +208,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Mizuho International plc — Cash Flow Summary by Year</a:t>
+              <a:t>Mizuho International plc — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -298,6 +303,30 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!I9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$J$5:$N$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$J$9:$N$9</f>
+            </numRef>
+          </val>
+        </ser>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -377,6 +406,552 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Mizuho International plc — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Mizuho International plc — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$22:$AD$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Mizuho International plc — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$28:$AL$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Mizuho International plc — Pillar 3 Key Metrics by Year</a:t>
             </a:r>
           </a:p>
@@ -404,7 +979,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
@@ -422,12 +997,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -437,7 +1012,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
@@ -455,12 +1030,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -537,7 +1112,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -559,10 +1134,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -572,6 +1147,72 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>81</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>125</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -869,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:AT35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -892,6 +1533,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -904,14 +1569,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (£m)</t>
+          <t>Balance Sheet Summary (£m)</t>
         </is>
       </c>
     </row>
@@ -971,27 +1636,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1000,282 +1665,936 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash flow from operating activities</t>
+          <t>Total Assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>-92.5</v>
+        <v>23914.9</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>216.7</v>
+        <v>24933.9</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>25.3</v>
+        <v>27378.9</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>384.9</v>
+        <v>22058.9</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-485.7</v>
+        <v>18208.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash flow from operating activities</t>
+          <t>Total Assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-485.7</v>
+        <v>18208.4</v>
       </c>
       <c r="K6" t="n">
-        <v>384.9</v>
+        <v>22058.9</v>
       </c>
       <c r="L6" t="n">
-        <v>25.3</v>
+        <v>27378.9</v>
       </c>
       <c r="M6" t="n">
-        <v>216.7</v>
+        <v>24933.9</v>
       </c>
       <c r="N6" t="n">
-        <v>-92.5</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>23914.9</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AP6" t="n">
         <v>31.12</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>31.14</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AR6" t="n">
         <v>28</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AS6" t="n">
         <v>22.8</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AT6" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash flows used in investing activities</t>
+          <t>Reverse repurchase agreements with customers</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-50</v>
+        <v>4587.1</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-32.9</v>
+        <v>3059.6</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-31.6</v>
+        <v>2303.5</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-33</v>
+        <v>5417</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-25.1</v>
+        <v>4288.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash flows used in investing activities</t>
+          <t>Reverse repurchase agreements with customers</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-25.1</v>
+        <v>4288.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-33</v>
+        <v>5417</v>
       </c>
       <c r="L7" t="n">
-        <v>-31.6</v>
+        <v>2303.5</v>
       </c>
       <c r="M7" t="n">
-        <v>-32.9</v>
+        <v>3059.6</v>
       </c>
       <c r="N7" t="n">
-        <v>-50</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>4587.1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AP7" t="n">
         <v>4.75</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>4.07</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
         <v>4.24</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AS7" t="n">
         <v>4.07</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AT7" t="n">
         <v>4.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>Derivative assets</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>8520.1</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>9707.700000000001</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>13072.6</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>6443.1</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>6513.8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Derivative assets</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>6513.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6443.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>13072.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9707.700000000001</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8520.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>773.5</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>720.7</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>707.7</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>712.4</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>741.6</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>741.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>712.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>707.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>720.7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>773.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Profit &amp; Loss Summary (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Net income from operations</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>373.4</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>244.1</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>265.1</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Net income from operations</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>265.1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>244.1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>373.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-367.6</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-229.1</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-204.8</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-203.9</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-221.3</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-221.3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-203.9</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-204.8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-229.1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-367.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>720.7</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>707.7</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>712.4</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>741.6</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>699.2</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>699.2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>741.6</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>712.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>707.7</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>720.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>773.5</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>720.7</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>707.7</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>712.4</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>741.6</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>741.6</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>712.4</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>707.7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>720.7</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>773.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flow from operating activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-92.5</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>216.7</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>384.9</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-485.7</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net cash flow from operating activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>-485.7</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>384.9</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>216.7</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-92.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Net cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-50</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-32.9</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>-31.6</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-33</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Net cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-33</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-31.6</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-32.9</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>Cash and cash equivalents at end of period</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B28" s="5" t="n">
         <v>175.7</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C28" s="5" t="n">
         <v>375.6</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D28" s="5" t="n">
         <v>417.2</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E28" s="5" t="n">
         <v>558.8</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F28" s="5" t="n">
         <v>337.5</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of period</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="AH28" t="n">
         <v>337.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="AI28" t="n">
         <v>558.8</v>
       </c>
-      <c r="L8" t="n">
+      <c r="AJ28" t="n">
         <v>417.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="AK28" t="n">
         <v>375.6</v>
       </c>
-      <c r="N8" t="n">
+      <c r="AL28" t="n">
         <v>175.7</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Pillar 3 Key Metrics</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>22.8%</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>28.0%</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>31.14%</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>31.12%</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>4.2%</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>4.07%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>4.24%</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>4.07%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>4.75%</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Note: Annual consolidated Group data. 2025 Pillar 3 source was unavailable at the official archive URL checked, so latest-year values use the 2025 Annual Report KPI and regulatory-capital disclosures.</t>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Note: Annual consolidated Group data.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1302,7 +2621,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mizuho International plc — Leverage Ratio</t>
+          <t>Mizuho International plc — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
@@ -1348,32 +2667,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Leverage Ratio</t>
+          <t>Tier 1 Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>22.84%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>4.24%</t>
+          <t>28.00%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>31.14%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>31.12%</t>
         </is>
       </c>
     </row>
@@ -1381,8 +2700,7 @@
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
-FY2025 Pillar 3 PDF was not available at the official archive URL checked; 2025 values are included only where disclosed in the Annual Report KPI/regulatory-capital sections.</t>
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
@@ -1414,14 +2732,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mizuho International plc — LCR</t>
+          <t>Mizuho International plc — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£ millions</t>
         </is>
       </c>
     </row>
@@ -1460,41 +2778,30 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>LCR</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>268.7%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>250.39%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>302.67%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>364.04%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>303.00%</t>
-        </is>
+          <t>Total Capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>670.5</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>637.4</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>627.7</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>640.8</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>711.6</v>
       </c>
     </row>
     <row r="6" ht="220" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
-FY2025 Pillar 3 PDF was not available at the official archive URL checked; 2025 values are included only where disclosed in the Annual Report KPI/regulatory-capital sections.</t>
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
@@ -1507,6 +2814,666 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mizuho International plc — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total Capital Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>22.84%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>28.00%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>31.14%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>32.78%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="220" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mizuho International plc — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£ millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total RWAs</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>3353.2</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>2790.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2241.7</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>2057.9</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="6" ht="220" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mizuho International plc — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated Group basis, Pillar 3 'UK OV1 - Overview of risk weighted exposure amounts' template (Table 10, only non-nil rows shown per the source document's own convention), £m. 'Large exposures' (row 22a of the PRA template) only appears as a non-nil row in the FY2023 report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (excluding CCR)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>140.1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>92.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk (CCR)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>682.4</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>638.9</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>530.6</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>357.3</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>259.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Settlement risk</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Position, foreign exchange and commodities risks (Market risk)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>2014.2</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1626.8</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1166.8</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1224.3</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1445.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Large exposures</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>506.1</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>376.6</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>389.6</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>368.1</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>373.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>3353.2</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2790.7</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2241.7</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2057.9</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="12" ht="220" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
+Table 10 'RWAs and Pillar 1 capital requirements', section 6.1, in each year's own Pillar 3 disclosure document listed above.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mizuho International plc — Leverage Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Leverage Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>4.07%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>4.24%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>4.07%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>4.75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="220" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mizuho International plc — LCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>LCR</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>268.7%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>250.39%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>302.67%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>364.04%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>303.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="220" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1608,8 +3575,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
-FY2025 Pillar 3 PDF was not available at the official archive URL checked; 2025 values are included only where disclosed in the Annual Report KPI/regulatory-capital sections.</t>
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
@@ -1622,7 +3588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1708,8 +3674,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
-FY2025 Pillar 3 PDF was not available at the official archive URL checked; 2025 values are included only where disclosed in the Annual Report KPI/regulatory-capital sections.</t>
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
@@ -1723,6 +3688,1801 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mizuho International plc — Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated Group basis. £m. FY2021 shows a genuine structural difference from later years: a standalone 'Subordinated liabilities' line (£45.2m), fully repaid during FY2022 (see the Cash Flow Statement's 'Net repayment of subordinated liabilities' row) and absent from FY2022 onward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and balances at central banks</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>370.4</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>481</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>227.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Reverse repurchase agreements with banks</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>4055.8</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>5131</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>5841.9</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>3854.3</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2107.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Reverse repurchase agreements with customers</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>4587.1</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>3059.6</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>2303.5</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>5417</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>4288.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Debt and other fixed income securities</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>5644.9</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>5463.7</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>5087.2</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>4772</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>4261.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Equity shares</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Derivative assets</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>8520.1</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>9707.700000000001</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>13072.6</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>6443.1</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>6513.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Shares in group undertakings</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Tangible fixed assets</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>559.8</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>897.9</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>449.5</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>832.2</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>517.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Prepayments and accrued income</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>229.9</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>177.1</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>82.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>23914.9</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>24933.9</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>27378.9</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>22058.9</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>18208.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Deposits by banks</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>678.7</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>519.1</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>292.1</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1153.3</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>285.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Customer accounts</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>473.5</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>707.5</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>897.9</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>228.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Repurchase agreements with banks</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>4580.9</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>3769.7</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>1675.3</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1775.5</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1984.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Repurchase agreements with customers</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>4078</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>3425.7</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>5231.3</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>5799.8</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>3133.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Debt securities in issue</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>1292.3</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>1395</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>1616.5</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1760.1</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>1851.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Short trading positions</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>2889.1</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>3925.7</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>3418.7</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>3560.9</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>3072.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Derivative liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>8548.4</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>9603.299999999999</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>12833.5</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>6422.7</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>6481.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>365.8</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>651.2</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>581.4</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>452.1</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>225.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Accruals and deferred income</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>234.5</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>212.9</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>155.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Provisions for liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Subordinated liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>23141.4</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>24213.2</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>26671.2</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>21346.5</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>17466.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Called up share capital</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>754.9</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>709.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Share premium account</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Pension reserve</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>-5.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Profit and loss account</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>773.5</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>720.7</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>707.7</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>712.4</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>741.6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Total Liabilities and Equity</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>23914.9</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>24933.9</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>27378.9</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>22058.9</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>18208.4</v>
+      </c>
+    </row>
+    <row r="40" ht="240" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
+Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf
+Balance Sheet/P&amp;L/Equity figures are the Consolidated Mizuho International plc Group basis (distinct from the Company-only basis also shown in each Annual Report). FY2025/FY2024: Annual Report 2025, Consolidated Statement of Comprehensive Income and Consolidated Statement of Financial Position p.88-89, Consolidated Statement of Changes in Equity p.90-91. FY2023/FY2022: Annual Report 2024, same statements p.86-89. FY2021: Annual Report 2022, Consolidated Statement of Comprehensive Income p.84-85, Consolidated Statement of Financial Position and Consolidated Statement of Changes in Equity p.86, 88.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A40:F40"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mizuho International plc — Profit &amp; Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated Group basis. £m. Re-measurement losses from defined benefit scheme were nil (not disclosed as a line) in FY2021; Provisions for liabilities was nil in FY2021 Company statement terms and is shown blank for FY2021 Consolidated as the report discloses no separate figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest receivable</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest payable</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-105.7</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-103.3</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-38.7</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-5.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income/(expense)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>-77.3</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>-70</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fees and commissions receivable</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>198.7</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>175.6</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>182.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fees and commissions payable</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-76</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-71.90000000000001</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-53.4</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-91.3</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-99.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net fees and commissions</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>82.90000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Dealing profit</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>175.1</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>204.9</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>183.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Other operating income</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Net income from operations</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>373.4</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>244.1</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>265.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-338.6</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-200.7</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-178.3</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-178.5</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-192</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>-28.9</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>-29.3</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-25.6</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-25.4</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-29.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Provisions for liabilities</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>-367.6</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-229.1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-204.8</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-203.9</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-221.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) on ordinary activities before taxation</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-37.6</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Tax credit/(charge) on profit/(loss) on ordinary activities</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Profit/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Re-measurement losses from defined benefit scheme</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>FX translation gain/(loss) relating to net investment in subsidiary</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-29.2</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="26" ht="240" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
+Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf
+Balance Sheet/P&amp;L/Equity figures are the Consolidated Mizuho International plc Group basis (distinct from the Company-only basis also shown in each Annual Report). FY2025/FY2024: Annual Report 2025, Consolidated Statement of Comprehensive Income and Consolidated Statement of Financial Position p.88-89, Consolidated Statement of Changes in Equity p.90-91. FY2023/FY2022: Annual Report 2024, same statements p.86-89. FY2021: Annual Report 2022, Consolidated Statement of Comprehensive Income p.84-85, Consolidated Statement of Financial Position and Consolidated Statement of Changes in Equity p.86, 88.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A26:F26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mizuho International plc — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Chronological roll-forward, oldest to newest, Consolidated Group basis. £m. Equity reconciliation ladder confirmed: every year's own closing balance ties exactly to both the next year's own opening balance and that year's own Balance Sheet Total Equity - zero plug rows needed anywhere across all 5 years. FY2025's Capital injection/Equity contribution/Transfer-to-P&amp;L rows relate to a capital raise and the release of a net dilapidation provision following termination of the Company's sub-lease, per the source's own explanatory note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Share premium account</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Pension reserve</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Profit and loss account</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>At 1 April 2020 (FY2021 opening)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>699.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2021 (FY2021 closing)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>741.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-28.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2022 (FY2022 closing)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>712.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2023 (FY2023 closing)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>707.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2024 (FY2024 closing)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>720.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Capital injection</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Equity contribution</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Transfer to profit and loss account</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2025 (FY2025 closing)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>754.9</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>773.5</v>
+      </c>
+    </row>
+    <row r="24" ht="150" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
+Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf
+Balance Sheet/P&amp;L/Equity figures are the Consolidated Mizuho International plc Group basis (distinct from the Company-only basis also shown in each Annual Report). FY2025/FY2024: Annual Report 2025, Consolidated Statement of Comprehensive Income and Consolidated Statement of Financial Position p.88-89, Consolidated Statement of Changes in Equity p.90-91. FY2023/FY2022: Annual Report 2024, same statements p.86-89. FY2021: Annual Report 2022, Consolidated Statement of Comprehensive Income p.84-85, Consolidated Statement of Financial Position and Consolidated Statement of Changes in Equity p.86, 88.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A24:G24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2327,7 +6087,339 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="74" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mizuho International plc — Asset Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Pillar 3 credit risk exposures by credit quality step (Table 23), standardised approach, £m — substitutes for an IFRS 9 stage split, which this Group does not disclose (it runs no material customer lending book).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Credit risk exposures by credit quality step (standardised approach), net of CRM</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Credit quality step 1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>368.5</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>531.4</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>303.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Credit quality step 2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Credit quality step 3</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Credit quality step 4</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Credit quality step 5</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Credit quality step 6</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Unrated</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>64.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Total net credit exposure</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>585.7</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>609.5</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>662.7</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>408.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Memo: Total gross credit exposure (before CRM)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>420.8</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>665.7</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>681.1</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>725</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>437.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk RWAs (excluding CCR)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>140.1</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>92.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk RWA density (RWAs / net credit exposure)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>40.05%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>25.34%</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>22.99%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>16.33%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>22.73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="240" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
+Table 23 'Credit risk exposures and RWAs by credit quality step', section 8.3 'Analysis of credit risk exposures', in each year's own Pillar 3 disclosure document listed above.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A17:F17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2423,8 +6515,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
-FY2025 Pillar 3 PDF was not available at the official archive URL checked; 2025 values are included only where disclosed in the Annual Report KPI/regulatory-capital sections.</t>
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
@@ -2432,434 +6523,6 @@
   <mergeCells count="2">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mizuho International plc — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>CET1 Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>22.8%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>28.0%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>31.14%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>31.12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="220" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
-FY2025 Pillar 3 PDF was not available at the official archive URL checked; 2025 values are included only where disclosed in the Annual Report KPI/regulatory-capital sections.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mizuho International plc — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£ millions</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 Capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>670.5</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>637.4</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>627.7</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>640.8</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>675.6</v>
-      </c>
-    </row>
-    <row r="6" ht="220" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
-FY2025 Pillar 3 PDF was not available at the official archive URL checked; 2025 values are included only where disclosed in the Annual Report KPI/regulatory-capital sections.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mizuho International plc — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>22.84%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>28.00%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>31.14%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>31.12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="220" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
-FY2025 Pillar 3 PDF was not available at the official archive URL checked; 2025 values are included only where disclosed in the Annual Report KPI/regulatory-capital sections.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mizuho International plc — Total Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£ millions</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total Capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>670.5</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>637.4</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>627.7</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>640.8</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>711.6</v>
-      </c>
-    </row>
-    <row r="6" ht="220" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
-FY2025 Pillar 3 PDF was not available at the official archive URL checked; 2025 values are included only where disclosed in the Annual Report KPI/regulatory-capital sections.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2885,7 +6548,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mizuho International plc — Total Capital Ratio</t>
+          <t>Mizuho International plc — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -2931,7 +6594,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total Capital Ratio</t>
+          <t>CET1 Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2941,12 +6604,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>22.84%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>28.00%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -2956,7 +6619,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>32.78%</t>
+          <t>31.12%</t>
         </is>
       </c>
     </row>
@@ -2964,8 +6627,7 @@
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
-FY2025 Pillar 3 PDF was not available at the official archive URL checked; 2025 values are included only where disclosed in the Annual Report KPI/regulatory-capital sections.</t>
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
@@ -2983,7 +6645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2997,7 +6659,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mizuho International plc — Total RWAs</t>
+          <t>Mizuho International plc — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -3043,43 +6705,36 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total RWAs</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
+          <t>Tier 1 Capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>670.5</v>
+      </c>
       <c r="C4" s="6" t="n">
-        <v>2790.7</v>
+        <v>637.4</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2241.7</v>
+        <v>627.7</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>2057.9</v>
+        <v>640.8</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2025 standalone RWA was not numerically disclosed in the Annual Report sections checked; no ratio-based estimate is made.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="220" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+        <v>675.6</v>
+      </c>
+    </row>
+    <row r="6" ht="220" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
-FY2025 Pillar 3 PDF was not available at the official archive URL checked; 2025 values are included only where disclosed in the Annual Report KPI/regulatory-capital sections.</t>
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
+++ b/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
@@ -236,7 +236,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!I6</f>
+              <f>'Overview'!P6</f>
             </strRef>
           </tx>
           <spPr>
@@ -246,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$Q$5:$AB$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$6:$N$6</f>
+              <f>'Overview'!$Q$6:$AB$6</f>
             </numRef>
           </val>
         </ser>
@@ -260,7 +260,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!I7</f>
+              <f>'Overview'!P7</f>
             </strRef>
           </tx>
           <spPr>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$Q$5:$AB$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$7:$N$7</f>
+              <f>'Overview'!$Q$7:$AB$7</f>
             </numRef>
           </val>
         </ser>
@@ -284,7 +284,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!I8</f>
+              <f>'Overview'!P8</f>
             </strRef>
           </tx>
           <spPr>
@@ -294,12 +294,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$Q$5:$AB$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$8:$N$8</f>
+              <f>'Overview'!$Q$8:$AB$8</f>
             </numRef>
           </val>
         </ser>
@@ -308,7 +308,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!I9</f>
+              <f>'Overview'!P9</f>
             </strRef>
           </tx>
           <spPr>
@@ -318,12 +318,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$J$5:$N$5</f>
+              <f>'Overview'!$Q$5:$AB$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$J$9:$N$9</f>
+              <f>'Overview'!$Q$9:$AB$9</f>
             </numRef>
           </val>
         </ser>
@@ -434,7 +434,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q13</f>
+              <f>'Overview'!AE13</f>
             </strRef>
           </tx>
           <spPr>
@@ -444,12 +444,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$AF$12:$AQ$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$13:$V$13</f>
+              <f>'Overview'!$AF$13:$AQ$13</f>
             </numRef>
           </val>
         </ser>
@@ -458,7 +458,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q14</f>
+              <f>'Overview'!AE14</f>
             </strRef>
           </tx>
           <spPr>
@@ -468,12 +468,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$AF$12:$AQ$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$14:$V$14</f>
+              <f>'Overview'!$AF$14:$AQ$14</f>
             </numRef>
           </val>
         </ser>
@@ -482,7 +482,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q15</f>
+              <f>'Overview'!AE15</f>
             </strRef>
           </tx>
           <spPr>
@@ -492,12 +492,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$R$12:$V$12</f>
+              <f>'Overview'!$AF$12:$AQ$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$15:$V$15</f>
+              <f>'Overview'!$AF$15:$AQ$15</f>
             </numRef>
           </val>
         </ser>
@@ -608,7 +608,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y19</f>
+              <f>'Overview'!AT19</f>
             </strRef>
           </tx>
           <spPr>
@@ -618,12 +618,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AU$18:$BF$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$19:$AD$19</f>
+              <f>'Overview'!$AU$19:$BF$19</f>
             </numRef>
           </val>
         </ser>
@@ -632,7 +632,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y20</f>
+              <f>'Overview'!AT20</f>
             </strRef>
           </tx>
           <spPr>
@@ -642,12 +642,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AU$18:$BF$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$20:$AD$20</f>
+              <f>'Overview'!$AU$20:$BF$20</f>
             </numRef>
           </val>
         </ser>
@@ -656,7 +656,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y21</f>
+              <f>'Overview'!AT21</f>
             </strRef>
           </tx>
           <spPr>
@@ -666,12 +666,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AU$18:$BF$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$21:$AD$21</f>
+              <f>'Overview'!$AU$21:$BF$21</f>
             </numRef>
           </val>
         </ser>
@@ -680,7 +680,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Y22</f>
+              <f>'Overview'!AT22</f>
             </strRef>
           </tx>
           <spPr>
@@ -690,12 +690,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$Z$18:$AD$18</f>
+              <f>'Overview'!$AU$18:$BF$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$Z$22:$AD$22</f>
+              <f>'Overview'!$AU$22:$BF$22</f>
             </numRef>
           </val>
         </ser>
@@ -806,7 +806,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG26</f>
+              <f>'Overview'!BI26</f>
             </strRef>
           </tx>
           <spPr>
@@ -816,12 +816,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$BJ$25:$BU$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$26:$AL$26</f>
+              <f>'Overview'!$BJ$26:$BU$26</f>
             </numRef>
           </val>
         </ser>
@@ -830,7 +830,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG27</f>
+              <f>'Overview'!BI27</f>
             </strRef>
           </tx>
           <spPr>
@@ -840,12 +840,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$BJ$25:$BU$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$27:$AL$27</f>
+              <f>'Overview'!$BJ$27:$BU$27</f>
             </numRef>
           </val>
         </ser>
@@ -854,7 +854,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!AG28</f>
+              <f>'Overview'!BI28</f>
             </strRef>
           </tx>
           <spPr>
@@ -864,12 +864,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$AH$25:$AL$25</f>
+              <f>'Overview'!$BJ$25:$BU$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AH$28:$AL$28</f>
+              <f>'Overview'!$BJ$28:$BU$28</f>
             </numRef>
           </val>
         </ser>
@@ -979,7 +979,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO6</f>
+              <f>'Overview'!BX6</f>
             </strRef>
           </tx>
           <spPr>
@@ -997,12 +997,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BY$5:$CJ$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$6:$AT$6</f>
+              <f>'Overview'!$BY$6:$CJ$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1012,7 +1012,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!AO7</f>
+              <f>'Overview'!BX7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1030,12 +1030,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$AP$5:$AT$5</f>
+              <f>'Overview'!$BY$5:$CJ$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$AP$7:$AT$7</f>
+              <f>'Overview'!$BY$7:$CJ$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1510,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT35"/>
+  <dimension ref="A1:CJ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1519,13 +1519,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
-    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
-    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
-    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
-    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
-    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
-    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
     <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
     <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
     <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
@@ -1557,6 +1557,48 @@
     <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
     <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
     <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
+    <col hidden="1" width="13" customWidth="1" min="47" max="47"/>
+    <col hidden="1" width="13" customWidth="1" min="48" max="48"/>
+    <col hidden="1" width="13" customWidth="1" min="49" max="49"/>
+    <col hidden="1" width="13" customWidth="1" min="50" max="50"/>
+    <col hidden="1" width="13" customWidth="1" min="51" max="51"/>
+    <col hidden="1" width="13" customWidth="1" min="52" max="52"/>
+    <col hidden="1" width="13" customWidth="1" min="53" max="53"/>
+    <col hidden="1" width="13" customWidth="1" min="54" max="54"/>
+    <col hidden="1" width="13" customWidth="1" min="55" max="55"/>
+    <col hidden="1" width="13" customWidth="1" min="56" max="56"/>
+    <col hidden="1" width="13" customWidth="1" min="57" max="57"/>
+    <col hidden="1" width="13" customWidth="1" min="58" max="58"/>
+    <col hidden="1" width="13" customWidth="1" min="59" max="59"/>
+    <col hidden="1" width="13" customWidth="1" min="60" max="60"/>
+    <col hidden="1" width="13" customWidth="1" min="61" max="61"/>
+    <col hidden="1" width="13" customWidth="1" min="62" max="62"/>
+    <col hidden="1" width="13" customWidth="1" min="63" max="63"/>
+    <col hidden="1" width="13" customWidth="1" min="64" max="64"/>
+    <col hidden="1" width="13" customWidth="1" min="65" max="65"/>
+    <col hidden="1" width="13" customWidth="1" min="66" max="66"/>
+    <col hidden="1" width="13" customWidth="1" min="67" max="67"/>
+    <col hidden="1" width="13" customWidth="1" min="68" max="68"/>
+    <col hidden="1" width="13" customWidth="1" min="69" max="69"/>
+    <col hidden="1" width="13" customWidth="1" min="70" max="70"/>
+    <col hidden="1" width="13" customWidth="1" min="71" max="71"/>
+    <col hidden="1" width="13" customWidth="1" min="72" max="72"/>
+    <col hidden="1" width="13" customWidth="1" min="73" max="73"/>
+    <col hidden="1" width="13" customWidth="1" min="74" max="74"/>
+    <col hidden="1" width="13" customWidth="1" min="75" max="75"/>
+    <col hidden="1" width="13" customWidth="1" min="76" max="76"/>
+    <col hidden="1" width="13" customWidth="1" min="77" max="77"/>
+    <col hidden="1" width="13" customWidth="1" min="78" max="78"/>
+    <col hidden="1" width="13" customWidth="1" min="79" max="79"/>
+    <col hidden="1" width="13" customWidth="1" min="80" max="80"/>
+    <col hidden="1" width="13" customWidth="1" min="81" max="81"/>
+    <col hidden="1" width="13" customWidth="1" min="82" max="82"/>
+    <col hidden="1" width="13" customWidth="1" min="83" max="83"/>
+    <col hidden="1" width="13" customWidth="1" min="84" max="84"/>
+    <col hidden="1" width="13" customWidth="1" min="85" max="85"/>
+    <col hidden="1" width="13" customWidth="1" min="86" max="86"/>
+    <col hidden="1" width="13" customWidth="1" min="87" max="87"/>
+    <col hidden="1" width="13" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1611,52 +1653,157 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1683,44 +1830,107 @@
       <c r="F6" s="5" t="n">
         <v>18208.4</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="G6" s="5" t="n">
+        <v>25045.1</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>19384.1</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>15517.3</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>15395.2</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>13192.8</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>21487.5</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>28883.2</v>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="Q6" t="n">
+        <v>28883.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>21487.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>13192.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>15395.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>15517.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>19384.1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>25045.1</v>
+      </c>
+      <c r="X6" t="n">
         <v>18208.4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="Y6" t="n">
         <v>22058.9</v>
       </c>
-      <c r="L6" t="n">
+      <c r="Z6" t="n">
         <v>27378.9</v>
       </c>
-      <c r="M6" t="n">
+      <c r="AA6" t="n">
         <v>24933.9</v>
       </c>
-      <c r="N6" t="n">
+      <c r="AB6" t="n">
         <v>23914.9</v>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="BY6" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="CF6" t="n">
         <v>31.12</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="CG6" t="n">
         <v>31.14</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="CH6" t="n">
         <v>28</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="CI6" t="n">
         <v>22.8</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="CJ6" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1745,44 +1955,99 @@
       <c r="F7" s="5" t="n">
         <v>4288.6</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" s="5" t="n">
+        <v>5895.2</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>7204.8</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>4636.4</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>5106.9</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>3176.7</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>5083.7</v>
+      </c>
+      <c r="M7" s="5" t="n"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Reverse repurchase agreements with customers</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="R7" t="n">
+        <v>5083.7</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3176.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5106.9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4636.4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7204.8</v>
+      </c>
+      <c r="W7" t="n">
+        <v>5895.2</v>
+      </c>
+      <c r="X7" t="n">
         <v>4288.6</v>
       </c>
-      <c r="K7" t="n">
+      <c r="Y7" t="n">
         <v>5417</v>
       </c>
-      <c r="L7" t="n">
+      <c r="Z7" t="n">
         <v>2303.5</v>
       </c>
-      <c r="M7" t="n">
+      <c r="AA7" t="n">
         <v>3059.6</v>
       </c>
-      <c r="N7" t="n">
+      <c r="AB7" t="n">
         <v>4587.1</v>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="BZ7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="CF7" t="n">
         <v>4.75</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="CG7" t="n">
         <v>4.07</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="CH7" t="n">
         <v>4.24</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="CI7" t="n">
         <v>4.07</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="CJ7" t="n">
         <v>4.2</v>
       </c>
     </row>
@@ -1807,24 +2072,66 @@
       <c r="F8" s="5" t="n">
         <v>6513.8</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="G8" s="5" t="n">
+        <v>11566.9</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>4451.4</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>2136.2</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1498.4</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>424</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>301.9</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>204.7</v>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Derivative assets</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="Q8" t="n">
+        <v>204.7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>301.9</v>
+      </c>
+      <c r="S8" t="n">
+        <v>424</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1498.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2136.2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4451.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>11566.9</v>
+      </c>
+      <c r="X8" t="n">
         <v>6513.8</v>
       </c>
-      <c r="K8" t="n">
+      <c r="Y8" t="n">
         <v>6443.1</v>
       </c>
-      <c r="L8" t="n">
+      <c r="Z8" t="n">
         <v>13072.6</v>
       </c>
-      <c r="M8" t="n">
+      <c r="AA8" t="n">
         <v>9707.700000000001</v>
       </c>
-      <c r="N8" t="n">
+      <c r="AB8" t="n">
         <v>8520.1</v>
       </c>
     </row>
@@ -1849,24 +2156,66 @@
       <c r="F9" s="5" t="n">
         <v>741.6</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="G9" s="5" t="n">
+        <v>699.2</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>740.2</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>761.6</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>736.4</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>460.8</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>441.6</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>439.6</v>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="Q9" t="n">
+        <v>439.6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>441.6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>460.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>736.4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>761.6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>740.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>699.2</v>
+      </c>
+      <c r="X9" t="n">
         <v>741.6</v>
       </c>
-      <c r="K9" t="n">
+      <c r="Y9" t="n">
         <v>712.4</v>
       </c>
-      <c r="L9" t="n">
+      <c r="Z9" t="n">
         <v>707.7</v>
       </c>
-      <c r="M9" t="n">
+      <c r="AA9" t="n">
         <v>720.7</v>
       </c>
-      <c r="N9" t="n">
+      <c r="AB9" t="n">
         <v>773.5</v>
       </c>
     </row>
@@ -1908,27 +2257,97 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1955,24 +2374,66 @@
       <c r="F13" s="5" t="n">
         <v>265.1</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="G13" s="5" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>174.6</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>145.6</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="AE13" t="inlineStr">
         <is>
           <t>Net income from operations</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="AF13" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>145.6</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>235</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>174.6</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="AM13" t="n">
         <v>265.1</v>
       </c>
-      <c r="S13" t="n">
+      <c r="AN13" t="n">
         <v>166.3</v>
       </c>
-      <c r="T13" t="n">
+      <c r="AO13" t="n">
         <v>194.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AP13" t="n">
         <v>244.1</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AQ13" t="n">
         <v>373.4</v>
       </c>
     </row>
@@ -1997,24 +2458,66 @@
       <c r="F14" s="5" t="n">
         <v>-221.3</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="G14" s="5" t="n">
+        <v>-207.6</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>-203.9</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>-205.2</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>-208.1</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>-161</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>-126.9</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>-115.6</v>
+      </c>
+      <c r="AE14" t="inlineStr">
         <is>
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="AF14" t="n">
+        <v>-115.6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-126.9</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-161</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-208.1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-205.2</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-203.9</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-207.6</v>
+      </c>
+      <c r="AM14" t="n">
         <v>-221.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="AN14" t="n">
         <v>-203.9</v>
       </c>
-      <c r="T14" t="n">
+      <c r="AO14" t="n">
         <v>-204.8</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AP14" t="n">
         <v>-229.1</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AQ14" t="n">
         <v>-367.6</v>
       </c>
     </row>
@@ -2039,24 +2542,66 @@
       <c r="F15" s="5" t="n">
         <v>42.8</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="G15" s="5" t="n">
+        <v>-40.7</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AE15" t="inlineStr">
         <is>
           <t>Profit/(loss) for the year</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="AF15" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-40.7</v>
+      </c>
+      <c r="AM15" t="n">
         <v>42.8</v>
       </c>
-      <c r="S15" t="n">
+      <c r="AN15" t="n">
         <v>-28.8</v>
       </c>
-      <c r="T15" t="n">
+      <c r="AO15" t="n">
         <v>-4.5</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AP15" t="n">
         <v>13.5</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AQ15" t="n">
         <v>7.2</v>
       </c>
     </row>
@@ -2098,27 +2643,97 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="BD18" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="BE18" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="BF18" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2145,24 +2760,66 @@
       <c r="F19" s="5" t="n">
         <v>699.2</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="G19" s="5" t="n">
+        <v>740.2</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>761.6</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>736.4</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>460.8</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>441.6</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>439.1</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>425.1</v>
+      </c>
+      <c r="AT19" t="inlineStr">
         <is>
           <t>Opening equity</t>
         </is>
       </c>
-      <c r="Z19" t="n">
+      <c r="AU19" t="n">
+        <v>425.1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>439.1</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>441.6</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>460.8</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>736.4</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>761.6</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>740.2</v>
+      </c>
+      <c r="BB19" t="n">
         <v>699.2</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="BC19" t="n">
         <v>741.6</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="BD19" t="n">
         <v>712.4</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="BE19" t="n">
         <v>707.7</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="BF19" t="n">
         <v>720.7</v>
       </c>
     </row>
@@ -2187,24 +2844,66 @@
       <c r="F20" s="5" t="n">
         <v>42.8</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="G20" s="5" t="n">
+        <v>-40.7</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AT20" t="inlineStr">
         <is>
           <t>Profit/(loss) for the year</t>
         </is>
       </c>
-      <c r="Z20" t="n">
+      <c r="AU20" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-40.7</v>
+      </c>
+      <c r="BB20" t="n">
         <v>42.8</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="BC20" t="n">
         <v>-28.8</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="BD20" t="n">
         <v>-4.5</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="BE20" t="n">
         <v>13.5</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="BF20" t="n">
         <v>7.2</v>
       </c>
     </row>
@@ -2229,24 +2928,66 @@
       <c r="F21" s="5" t="n">
         <v>-0.4</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="G21" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>263.4</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AT21" t="inlineStr">
         <is>
           <t>Other equity movements, net</t>
         </is>
       </c>
-      <c r="Z21" t="n">
+      <c r="AU21" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>263.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="BB21" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="BC21" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="BD21" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="BE21" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="BF21" t="n">
         <v>45.6</v>
       </c>
     </row>
@@ -2271,24 +3012,66 @@
       <c r="F22" s="5" t="n">
         <v>741.6</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="G22" s="5" t="n">
+        <v>699.2</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>740.2</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>761.6</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>736.4</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>460.8</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>441.6</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>439.6</v>
+      </c>
+      <c r="AT22" t="inlineStr">
         <is>
           <t>Closing equity</t>
         </is>
       </c>
-      <c r="Z22" t="n">
+      <c r="AU22" t="n">
+        <v>439.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>441.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>460.8</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>736.4</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>761.6</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>740.2</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>699.2</v>
+      </c>
+      <c r="BB22" t="n">
         <v>741.6</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="BC22" t="n">
         <v>712.4</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="BD22" t="n">
         <v>707.7</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="BE22" t="n">
         <v>720.7</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="BF22" t="n">
         <v>773.5</v>
       </c>
     </row>
@@ -2330,27 +3113,97 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+      <c r="BK25" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="BN25" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="BO25" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="BP25" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="BQ25" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="BR25" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="BS25" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="AK25" t="inlineStr">
+      <c r="BT25" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
+      <c r="BU25" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -2377,24 +3230,31 @@
       <c r="F26" s="5" t="n">
         <v>-485.7</v>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="BI26" t="inlineStr">
         <is>
           <t>Net cash flow from operating activities</t>
         </is>
       </c>
-      <c r="AH26" t="n">
+      <c r="BQ26" t="n">
         <v>-485.7</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="BR26" t="n">
         <v>384.9</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="BS26" t="n">
         <v>25.3</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="BT26" t="n">
         <v>216.7</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="BU26" t="n">
         <v>-92.5</v>
       </c>
     </row>
@@ -2419,24 +3279,31 @@
       <c r="F27" s="5" t="n">
         <v>-25.1</v>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="BI27" t="inlineStr">
         <is>
           <t>Net cash flows used in investing activities</t>
         </is>
       </c>
-      <c r="AH27" t="n">
+      <c r="BQ27" t="n">
         <v>-25.1</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="BR27" t="n">
         <v>-33</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="BS27" t="n">
         <v>-31.6</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="BT27" t="n">
         <v>-32.9</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="BU27" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -2461,24 +3328,31 @@
       <c r="F28" s="5" t="n">
         <v>337.5</v>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="BI28" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of period</t>
         </is>
       </c>
-      <c r="AH28" t="n">
+      <c r="BQ28" t="n">
         <v>337.5</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="BR28" t="n">
         <v>558.8</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="BS28" t="n">
         <v>417.2</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="BT28" t="n">
         <v>375.6</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="BU28" t="n">
         <v>175.7</v>
       </c>
     </row>
@@ -2520,6 +3394,41 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -2552,6 +3461,41 @@
           <t>31.12%</t>
         </is>
       </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>20.02%</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>30.6%</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>32.9%</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>49.5%</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>50.3%</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -2584,17 +3528,48 @@
           <t>4.75%</t>
         </is>
       </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>3.74%</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>3.74%</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>4.36%</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>3.28%</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>1.87%</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="n"/>
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Note: Annual consolidated Group data.</t>
+          <t>Note: Annual data; Consolidated Group basis FY2019-FY2025, Company-only basis FY2014-FY2018 (see the Balance Sheet sheet's REPORTING BASIS note). Cash flow totals are blank for FY2014-FY2020 (no cash flow statement prepared those years).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A35:M35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2607,7 +3582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2616,6 +3591,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2663,6 +3645,41 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2695,18 +3712,53 @@
           <t>31.12%</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>20.02%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>30.6%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>32.9%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>49.5%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>50.3%</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="220" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:M6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2718,7 +3770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2727,6 +3779,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2774,6 +3833,41 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2796,18 +3890,47 @@
       <c r="F4" s="6" t="n">
         <v>711.6</v>
       </c>
-    </row>
-    <row r="6" ht="220" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+      <c r="G4" s="6" t="n">
+        <v>668.7</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>707.5</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>735.9</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>703.3</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>453.3</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>451.9</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>456.9</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2015/FY2014: Total capital equals Tier 1 capital because no Tier 2 capital had yet been issued (first appears FY2016).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="220" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A7:M7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2819,7 +3942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2828,6 +3951,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2875,6 +4005,41 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2907,18 +4072,53 @@
           <t>32.78%</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>21.46%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>29.7%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>32.6%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>35.1%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>40.4%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>49.5%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>50.3%</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="220" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:M6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2930,7 +4130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2939,6 +4139,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2986,6 +4193,41 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3008,18 +4250,39 @@
       <c r="F4" s="6" t="n">
         <v>2171</v>
       </c>
+      <c r="G4" s="6" t="n">
+        <v>3115.3</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>2385.8</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>2257</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>2002.2</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>1122.3</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>913.7</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>908.5</v>
+      </c>
     </row>
     <row r="6" ht="220" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:M6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3031,7 +4294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -3040,6 +4303,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3052,7 +4322,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Group basis, Pillar 3 'UK OV1 - Overview of risk weighted exposure amounts' template (Table 10, only non-nil rows shown per the source document's own convention), £m. 'Large exposures' (row 22a of the PRA template) only appears as a non-nil row in the FY2023 report.</t>
+          <t>Consolidated Group basis FY2019 onward; MHI Company-only basis FY2017-FY2018; MSUKH group-level basis FY2014-FY2016 (see the P3 source dict comment). Pillar 3 RWA-by-risk-type template (labelled 'UK OV1' from FY2021 onward, an unlabelled equivalent table in earlier years - Table 10 for FY2018-FY2020, Table 9 for FY2014-FY2017; column/row numbering shifts across years but the risk categories are consistent), only non-nil rows shown per each source document's own convention, £m. 'Large exposures' (row 22a of the PRA template) only appears as a non-nil row in the FY2023 report. 'Concentration risk' was only disclosed as a separate line in the FY2015-FY2016 MSUKH Pillar 3 documents (nil/folded into credit risk in all other years). FY2016's own five risk-type rows here sum to £1,129.9m against the FY2016 document's own stated Total of £1,122.3m (a ~£7.6m/0.7% reconciling difference disclosed in the source table itself, not a transcription error here - each row is transcribed as printed).</t>
         </is>
       </c>
     </row>
@@ -3087,6 +4357,41 @@
           <t>FY2021 (£m)</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£m)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£m)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£m)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£m)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016 (£m)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015 (£m)</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014 (£m)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3109,6 +4414,27 @@
       <c r="F4" s="6" t="n">
         <v>92.8</v>
       </c>
+      <c r="G4" s="6" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>64.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3131,121 +4457,242 @@
       <c r="F5" s="6" t="n">
         <v>259.6</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>134</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>123.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Settlement risk</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
+          <t>Concentration risk</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="L6" s="6" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="M6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Position, foreign exchange and commodities risks (Market risk)</t>
+          <t>Settlement risk</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2014.2</v>
+        <v>0</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1626.8</v>
+        <v>0.2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1166.8</v>
+        <v>0.1</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1224.3</v>
+        <v>0.2</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1445.4</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Large exposures</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+          <t>Position, foreign exchange and commodities risks (Market risk)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>2014.2</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1626.8</v>
+      </c>
       <c r="D8" s="6" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+        <v>1166.8</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1224.3</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1445.4</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>2442.2</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1722.7</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1598.7</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1393.4</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>659.7</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>552</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>633.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>Large exposures</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
           <t>Operational risk</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B10" s="6" t="n">
         <v>506.1</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C10" s="6" t="n">
         <v>376.6</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D10" s="6" t="n">
         <v>389.6</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E10" s="6" t="n">
         <v>368.1</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F10" s="6" t="n">
         <v>373.3</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="n">
+        <v>354.4</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>393.6</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>377.3</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>306.7</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>235.1</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>87.09999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B11" s="5" t="n">
         <v>3353.2</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C11" s="5" t="n">
         <v>2790.7</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D11" s="5" t="n">
         <v>2241.7</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E11" s="5" t="n">
         <v>2057.9</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>2171</v>
       </c>
-    </row>
-    <row r="12" ht="220" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
-Table 10 'RWAs and Pillar 1 capital requirements', section 6.1, in each year's own Pillar 3 disclosure document listed above.</t>
+      <c r="G11" s="5" t="n">
+        <v>3115.3</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>2385.8</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>2257</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>2002.2</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1122.3</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>913.7</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>908.5</v>
+      </c>
+    </row>
+    <row r="13" ht="260" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf
+RWAs and Pillar 1 capital requirements table (by risk type) in each year's own Pillar 3 disclosure document listed above.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:M13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3257,7 +4704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3266,6 +4713,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3313,6 +4767,41 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3345,18 +4834,57 @@
           <t>4.75%</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="220" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>3.74%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>3.74%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>4.50%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>4.36%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>3.28%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>1.87%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2014 leverage ratio was discussed qualitatively (implementation of PRA bank-level reporting was noted as having 'commenced') but no computed ratio was numerically disclosed in the FY2014 Pillar 3 document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="220" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A7:M7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3368,7 +4896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3377,6 +4905,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3424,6 +4959,41 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3456,18 +5026,45 @@
           <t>303.00%</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="220" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>340%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>416%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>396%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: LCR was first disclosed in the FY2018 Pillar 3 document (the document itself states this); not disclosed FY2014-FY2017.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="220" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A7:M7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3479,7 +5076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3488,6 +5085,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3535,6 +5139,41 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3563,26 +5202,33 @@
         </is>
       </c>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: NSFR was not disclosed in the 2021 report; 2025 is from the Annual Report KPI section.</t>
+          <t>Note: NSFR was not disclosed in the 2021 report or any FY2014-FY2020 report; 2025 is from the Annual Report KPI section.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="220" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A7:M7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3594,7 +5240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3603,6 +5249,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3648,6 +5301,41 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
         </is>
       </c>
     </row>
@@ -3662,26 +5350,33 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: MREL ratio was not numerically disclosed in the official annual/Pillar 3 reports checked.</t>
+          <t>Note: MREL ratio was not numerically disclosed in any FY2014-FY2025 official annual/Pillar 3 report checked.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="220" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A7:M7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3693,7 +5388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -3702,6 +5397,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3714,7 +5416,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Group basis. £m. FY2021 shows a genuine structural difference from later years: a standalone 'Subordinated liabilities' line (£45.2m), fully repaid during FY2022 (see the Cash Flow Statement's 'Net repayment of subordinated liabilities' row) and absent from FY2022 onward.</t>
+          <t>Consolidated Group basis for FY2019-FY2025; Company-only basis for FY2014-FY2018 (see the 'REPORTING BASIS' source note). FY2021 shows a genuine structural difference from FY2022 onward: the standalone 'Subordinated liabilities' line was fully repaid during FY2022 (see the Cash Flow Statement's 'Net repayment of subordinated liabilities' row) and is absent from FY2022 onward; it was first issued in FY2016 and continued unbroken FY2016-FY2021. FY2014 (originally-filed UK GAAP, pre-FRS 102) combines several lines that later years disclose separately: 'Reverse repurchase agreements with banks' and 'Repurchase agreements with banks' each carry the FY2014 source's single undifferentiated repo total (not split by bank/customer counterparty - the 'with customers' rows are blank for FY2014 only); 'Derivative assets'/'Derivative liabilities' sum the FY2014 source's separate trading and risk-management derivative lines; 'Debt and other fixed income securities' carries the FY2014 source's combined 'Trading financial assets' line (equity shares not split out); 'Short trading positions' carries the FY2014 source's 'Trading financial liabilities' line; 'Other liabilities' includes the FY2014 source's separately-disclosed £2.3m defined benefit pension liability. FY2014 has no separate Cash/Shares in group undertakings/Intangible assets/Pension reserve lines (nil or not yet recognised as separate categories pre-FRS 102) - shown blank, not zero. £m.</t>
         </is>
       </c>
     </row>
@@ -3747,6 +5449,41 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£m)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£m)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£m)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£m)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£m)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016 (£m)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015 (£m)</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014 (£m)</t>
         </is>
       </c>
     </row>
@@ -3761,6 +5498,13 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3783,6 +5527,23 @@
       <c r="F5" s="6" t="n">
         <v>227.5</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>601</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>230.2</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3805,695 +5566,1355 @@
       <c r="F6" s="6" t="n">
         <v>110</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>166.4</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>96.09999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Reverse repurchase agreements with banks</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>4055.8</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>5131</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>5841.9</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>3854.3</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>2107.5</v>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Reverse repurchase agreements with customers</t>
+          <t>Reverse repurchase agreements with banks</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>4587.1</v>
+        <v>4055.8</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3059.6</v>
+        <v>5131</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2303.5</v>
+        <v>5841.9</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>5417</v>
+        <v>3854.3</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>4288.6</v>
+        <v>2107.5</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>963</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>2052.7</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>2756.6</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>4091.3</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>3268.7</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>11535.2</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>24398.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Debt and other fixed income securities</t>
+          <t>Reverse repurchase agreements with customers</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>5644.9</v>
+        <v>4587.1</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5463.7</v>
+        <v>3059.6</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5087.2</v>
+        <v>2303.5</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>4772</v>
+        <v>5417</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4261.9</v>
-      </c>
+        <v>4288.6</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>5895.2</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>7204.8</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>4636.4</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>5106.9</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>3176.7</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>5083.7</v>
+      </c>
+      <c r="M9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Equity shares</t>
+          <t>Debt and other fixed income securities</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2.6</v>
+        <v>5644.9</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>4.3</v>
+        <v>5463.7</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>6.1</v>
+        <v>5087.2</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>3.5</v>
+        <v>4772</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1.8</v>
+        <v>4261.9</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>4998</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>5087</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>5248.4</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>4054.6</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>5268.4</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>4191.1</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>3907.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Derivative assets</t>
+          <t>Equity shares</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>8520.1</v>
+        <v>2.6</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>9707.700000000001</v>
+        <v>4.3</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>13072.6</v>
+        <v>6.1</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>6443.1</v>
+        <v>3.5</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>6513.8</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Shares in group undertakings</t>
+          <t>Derivative assets</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>17.6</v>
+        <v>8520.1</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>13.2</v>
+        <v>9707.700000000001</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>9.9</v>
+        <v>13072.6</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>8.1</v>
+        <v>6443.1</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>6.8</v>
+        <v>6513.8</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>11566.9</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4451.4</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2136.2</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1498.4</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>424</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>301.9</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>204.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
+          <t>Shares in group undertakings</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>96.3</v>
+        <v>17.6</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>76.7</v>
+        <v>13.2</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>73.7</v>
+        <v>9.9</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>66.2</v>
+        <v>8.1</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>63.2</v>
-      </c>
+        <v>6.8</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Tangible fixed assets</t>
+          <t>Intangible assets</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>25.1</v>
+        <v>96.3</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>27.1</v>
+        <v>76.7</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>27.3</v>
+        <v>73.7</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>29</v>
+        <v>66.2</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>27</v>
-      </c>
+        <v>63.2</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="M14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Other assets</t>
+          <t>Tangible fixed assets</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>559.8</v>
+        <v>25.1</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>897.9</v>
+        <v>27.1</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>449.5</v>
+        <v>27.3</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>832.2</v>
+        <v>29</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>517.6</v>
+        <v>27</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>12.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>559.8</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>897.9</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>449.5</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>832.2</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>517.6</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>659.1</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>236.4</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>210.9</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>193</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>752.2</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>159</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>217.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
           <t>Prepayments and accrued income</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B17" s="6" t="n">
         <v>229.9</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C17" s="6" t="n">
         <v>177.1</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D17" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>74.7</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F17" s="6" t="n">
         <v>82.7</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>23914.9</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>24933.9</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>27378.9</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>22058.9</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>18208.4</v>
+      <c r="G17" s="6" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>46.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>23914.9</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>24933.9</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>27378.9</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>22058.9</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>18208.4</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>25045.1</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>19384.1</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>15517.3</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>15395.2</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>13192.8</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>21487.5</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>28883.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>Liabilities</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Deposits by banks</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>678.7</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>519.1</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>292.1</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>1153.3</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>285.5</v>
-      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Customer accounts</t>
+          <t>Deposits by banks</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>473.5</v>
+        <v>678.7</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>707.5</v>
+        <v>519.1</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>897.9</v>
+        <v>292.1</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>295.7</v>
+        <v>1153.3</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>228.6</v>
+        <v>285.5</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>471.6</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>196.2</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>398</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>318.9</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>613.1</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>655.7</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>744.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Repurchase agreements with banks</t>
+          <t>Customer accounts</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>4580.9</v>
+        <v>473.5</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>3769.7</v>
+        <v>707.5</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1675.3</v>
+        <v>897.9</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>1775.5</v>
+        <v>295.7</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1984.1</v>
+        <v>228.6</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>909.7</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>610</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>337.8</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>432</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>310.2</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>273.2</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>294</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Repurchase agreements with customers</t>
+          <t>Repurchase agreements with banks</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>4078</v>
+        <v>4580.9</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>3425.7</v>
+        <v>3769.7</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5231.3</v>
+        <v>1675.3</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>5799.8</v>
+        <v>1775.5</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>3133.7</v>
+        <v>1984.1</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>1614.4</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1734.2</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1861.6</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>2448.5</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>2462.1</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>3515.8</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>23465.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Debt securities in issue</t>
+          <t>Repurchase agreements with customers</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>1292.3</v>
+        <v>4078</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>1395</v>
+        <v>3425.7</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1616.5</v>
+        <v>5231.3</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>1760.1</v>
+        <v>5799.8</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1851.6</v>
-      </c>
+        <v>3133.7</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>3638.8</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>4572</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>3301.7</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>3779.3</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>2992.4</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>11966</v>
+      </c>
+      <c r="M23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Short trading positions</t>
+          <t>Debt securities in issue</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>2889.1</v>
+        <v>1292.3</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>3925.7</v>
+        <v>1395</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>3418.7</v>
+        <v>1616.5</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>3560.9</v>
+        <v>1760.1</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>3072.9</v>
+        <v>1851.6</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1776.6</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1453.2</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1773.3</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>1387.9</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>879.3</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>1142.7</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>976.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Derivative liabilities</t>
+          <t>Short trading positions</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>8548.4</v>
+        <v>2889.1</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>9603.299999999999</v>
+        <v>3925.7</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>12833.5</v>
+        <v>3418.7</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>6422.7</v>
+        <v>3560.9</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>6481.2</v>
+        <v>3072.9</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>3728.3</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>5208.7</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>4561.1</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>4297.7</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>4570.4</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>2892.2</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>2600.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Other liabilities</t>
+          <t>Derivative liabilities</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>365.8</v>
+        <v>8548.4</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>651.2</v>
+        <v>9603.299999999999</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>581.4</v>
+        <v>12833.5</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>452.1</v>
+        <v>6422.7</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>225.3</v>
+        <v>6481.2</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>11514</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>4285.1</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>2030.6</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>1433.1</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>421.4</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>250.9</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>181.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Accruals and deferred income</t>
+          <t>Other liabilities</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>234.5</v>
+        <v>365.8</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>212.9</v>
+        <v>651.2</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>120.5</v>
+        <v>581.4</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>123.3</v>
+        <v>452.1</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>155.4</v>
+        <v>225.3</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>504.3</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>380.7</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>296.2</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>357.3</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>307.3</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>257.2</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>95.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Provisions for liabilities</t>
+          <t>Accruals and deferred income</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0.2</v>
+        <v>234.5</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>3.1</v>
+        <v>212.9</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>4</v>
+        <v>120.5</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>3.1</v>
+        <v>123.3</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>3.3</v>
+        <v>155.4</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>139</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>153.6</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>137.8</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
+          <t>Provisions for liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
           <t>Subordinated liabilities</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n">
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n">
         <v>45.2</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Total Liabilities</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>23141.4</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>24213.2</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>26671.2</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>21346.5</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>17466.8</v>
-      </c>
+      <c r="G30" s="6" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>23141.4</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>24213.2</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>26671.2</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>21346.5</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>17466.8</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>24345.9</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>18643.9</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>14755.7</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>14658.8</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>12732</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>21045.9</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>28443.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Called up share capital</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>754.9</v>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>709.9</v>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>709.9</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>709.9</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>709.9</v>
-      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Share premium account</t>
+          <t>Called up share capital</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>15.6</v>
+        <v>754.9</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>15.6</v>
+        <v>709.9</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>15.6</v>
+        <v>709.9</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>15.6</v>
+        <v>709.9</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>15.6</v>
+        <v>709.9</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>2875.3</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>2840.3</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>2840.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Pension reserve</t>
+          <t>Share premium account</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>-7.1</v>
+        <v>15.6</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>-6.8</v>
+        <v>15.6</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>-6.5</v>
+        <v>15.6</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>-6.2</v>
+        <v>15.6</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-5.9</v>
+        <v>15.6</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>15.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Other reserves</t>
+          <t>Pension reserve</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>-0.8</v>
+        <v>-7.1</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>-0.6</v>
+        <v>-6.8</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>-0.4</v>
+        <v>-6.5</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>-0.5</v>
+        <v>-6.2</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>-0.4</v>
-      </c>
+        <v>-5.9</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>-16.8</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="M35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="n"/>
+      <c r="L36" s="6" t="n"/>
+      <c r="M36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
           <t>Profit and loss account</t>
         </is>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B37" s="6" t="n">
         <v>10.9</v>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C37" s="6" t="n">
         <v>2.6</v>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D37" s="6" t="n">
         <v>-10.9</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E37" s="6" t="n">
         <v>-6.4</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F37" s="6" t="n">
         <v>22.4</v>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Total Equity</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>773.5</v>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>720.7</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>707.7</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>712.4</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>741.6</v>
+      <c r="G37" s="6" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>-2413.3</v>
+      </c>
+      <c r="L37" s="6" t="n">
+        <v>-2397.9</v>
+      </c>
+      <c r="M37" s="6" t="n">
+        <v>-2416.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>773.5</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>720.7</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>707.7</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>712.4</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>741.6</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>699.2</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>740.2</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>761.6</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>736.4</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>460.8</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>441.6</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>439.6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>Total Liabilities and Equity</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B39" s="5" t="n">
         <v>23914.9</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C39" s="5" t="n">
         <v>24933.9</v>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D39" s="5" t="n">
         <v>27378.9</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E39" s="5" t="n">
         <v>22058.9</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F39" s="5" t="n">
         <v>18208.4</v>
       </c>
-    </row>
-    <row r="40" ht="240" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf
-Balance Sheet/P&amp;L/Equity figures are the Consolidated Mizuho International plc Group basis (distinct from the Company-only basis also shown in each Annual Report). FY2025/FY2024: Annual Report 2025, Consolidated Statement of Comprehensive Income and Consolidated Statement of Financial Position p.88-89, Consolidated Statement of Changes in Equity p.90-91. FY2023/FY2022: Annual Report 2024, same statements p.86-89. FY2021: Annual Report 2022, Consolidated Statement of Comprehensive Income p.84-85, Consolidated Statement of Financial Position and Consolidated Statement of Changes in Equity p.86, 88.</t>
+      <c r="G39" s="5" t="n">
+        <v>25045.1</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>19384.1</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>15517.3</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>15395.2</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>13192.8</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>21487.5</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>28883.2</v>
+      </c>
+    </row>
+    <row r="41" ht="260" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863028d4802cdc23dd6552c_2020-mizuho-international-plc-annual-report.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302ac32d1c7376f1f1877_2019-mizuho-international-plc-annual-report.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302c5e1d535ec3306fbee_2018-mizuho-international-plc-annual-report-1.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302d732d1c7376f1f2ad2_2017-mizuho-international-plc-annual-report.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302eda925dd5c1687cecd_2016-mizuho-international-plc-annual-report.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68630302eca4998ff565c8ea_2015-mizuho-international-plc-annual-report.pdf; FY2014: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzEwNDY4NTMyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Balance Sheet/P&amp;L/Equity figures are the Consolidated Mizuho International plc Group basis for FY2019-FY2025 (distinct from the Company-only basis also shown in each Annual Report). FY2025/FY2024: Annual Report 2025, Consolidated Statement of Comprehensive Income and Consolidated Statement of Financial Position p.88-89, Consolidated Statement of Changes in Equity p.90-91. FY2023/FY2022: Annual Report 2024, same statements p.86-89. FY2021: Annual Report 2022, Consolidated Statement of Comprehensive Income p.84-85, Consolidated Statement of Financial Position and Consolidated Statement of Changes in Equity p.86, 88. FY2020: Annual Report 2020, Consolidated Statement of Comprehensive Income/Financial Position/Changes in Equity/Cash Flows p.34-39. FY2019: Annual Report 2019, same Consolidated statements p.22-27.
+REPORTING BASIS: FY2019-FY2025 are Consolidated Mizuho International plc Group basis (Group consolidation began FY2019). FY2015-FY2018 are Company-only basis under FRS 102 (restated from UK GAAP as at 1 April 2015 transition date); the Company did not yet prepare group accounts. FY2014 is Company-only, originally-filed UK GAAP (pre-FRS 102), sourced from the Companies House statutory filing rather than Mizuho's own site (see AR/P3 source dict comments) - there is a real ~£0.5m equity break between FY2014 as originally filed and the FRS102-restated FY2015 opening position (see the Statement of Changes in Equity's transition row). None of FY2014-FY2020 include a cash flow statement (FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent publishes consolidated accounts).
+FY2015-FY2018 (Company-only basis): FY2018 Annual Report, Statement of Comprehensive Income p.22, Statement of Financial Position p.23, Statement of Changes in Equity p.24. FY2017 Annual Report, same statements p.15-17. FY2016 Annual Report, same statements p.14-16 (FY2016 report's own FY2015 comparative column is the source for FY2015, restated to FRS 102). FY2014 (originally-filed UK GAAP, Company-only): Companies House 'Full accounts made up to 31 March 2014' filing, Profit and Loss Account p.13, Balance Sheet p.14, Consolidated Statement of Total Recognised Gains and Losses p.15.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A41:M41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4505,7 +6926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -4514,6 +6935,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4526,7 +6954,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Group basis. £m. Re-measurement losses from defined benefit scheme were nil (not disclosed as a line) in FY2021; Provisions for liabilities was nil in FY2021 Company statement terms and is shown blank for FY2021 Consolidated as the report discloses no separate figure.</t>
+          <t>Consolidated Group basis for FY2019-FY2025; Company-only basis for FY2014-FY2018 (see the 'REPORTING BASIS' source note). Re-measurement losses from defined benefit scheme were nil (not disclosed as a line) in FY2021; Provisions for liabilities was nil in FY2021 Company statement terms and is shown blank for FY2021 Consolidated as the report discloses no separate figure. FY2014-FY2020 did not disclose a separate FX translation line (shown blank, not zero). FY2014-FY2017 each disclosed a £nil tax charge/credit (shown here as 0, per each year's own source).</t>
         </is>
       </c>
     </row>
@@ -4559,6 +6987,41 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£m)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£m)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£m)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£m)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£m)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016 (£m)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015 (£m)</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014 (£m)</t>
         </is>
       </c>
     </row>
@@ -4573,6 +7036,13 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4595,6 +7065,27 @@
       <c r="F5" s="6" t="n">
         <v>4</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4617,6 +7108,27 @@
       <c r="F6" s="6" t="n">
         <v>-5.4</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>-21.8</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>-9.300000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -4639,6 +7151,27 @@
       <c r="F7" s="5" t="n">
         <v>-1.4</v>
       </c>
+      <c r="G7" s="5" t="n">
+        <v>-21.8</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>-17.3</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>-8.800000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -4661,6 +7194,27 @@
       <c r="F8" s="6" t="n">
         <v>182.4</v>
       </c>
+      <c r="G8" s="6" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>148.9</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>71.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4683,6 +7237,27 @@
       <c r="F9" s="6" t="n">
         <v>-99.5</v>
       </c>
+      <c r="G9" s="6" t="n">
+        <v>-56.6</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-73.90000000000001</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>-65.2</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>-58.1</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>-82.09999999999999</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>-43.5</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>-28.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -4705,6 +7280,27 @@
       <c r="F10" s="5" t="n">
         <v>82.90000000000001</v>
       </c>
+      <c r="G10" s="5" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>42.8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -4727,6 +7323,27 @@
       <c r="F11" s="6" t="n">
         <v>183.1</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>53.5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4749,6 +7366,27 @@
       <c r="F12" s="6" t="n">
         <v>0.5</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -4771,6 +7409,27 @@
       <c r="F13" s="5" t="n">
         <v>265.1</v>
       </c>
+      <c r="G13" s="5" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>174.6</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>145.6</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>87.59999999999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -4793,6 +7452,27 @@
       <c r="F14" s="6" t="n">
         <v>-192</v>
       </c>
+      <c r="G14" s="6" t="n">
+        <v>-176.6</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-177.4</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-178.4</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-174.8</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>-146.4</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>-124</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>-111.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -4814,6 +7494,27 @@
       </c>
       <c r="F15" s="6" t="n">
         <v>-29.5</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-31.6</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>-26.6</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>-4.4</v>
       </c>
     </row>
     <row r="16">
@@ -4835,6 +7536,27 @@
       <c r="F16" s="6" t="n">
         <v>0.2</v>
       </c>
+      <c r="G16" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -4857,6 +7579,27 @@
       <c r="F17" s="5" t="n">
         <v>-221.3</v>
       </c>
+      <c r="G17" s="5" t="n">
+        <v>-207.6</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-203.9</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>-205.2</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>-208.1</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>-161</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>-126.9</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>-115.6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -4879,6 +7622,27 @@
       <c r="F18" s="5" t="n">
         <v>43.8</v>
       </c>
+      <c r="G18" s="5" t="n">
+        <v>-50.1</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-29.3</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>-28</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -4901,6 +7665,27 @@
       <c r="F19" s="6" t="n">
         <v>-1</v>
       </c>
+      <c r="G19" s="6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -4922,6 +7707,27 @@
       </c>
       <c r="F20" s="5" t="n">
         <v>42.8</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>-40.7</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>-28</v>
       </c>
     </row>
     <row r="21">
@@ -4935,6 +7741,13 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -4955,6 +7768,27 @@
         <v>-0.3</v>
       </c>
       <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>-2.5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -4977,6 +7811,13 @@
       <c r="F23" s="6" t="n">
         <v>-0.4</v>
       </c>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -4999,19 +7840,42 @@
       <c r="F24" s="5" t="n">
         <v>42.4</v>
       </c>
+      <c r="G24" s="5" t="n">
+        <v>-41</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-21.4</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>-30.5</v>
+      </c>
     </row>
     <row r="26" ht="240" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf
-Balance Sheet/P&amp;L/Equity figures are the Consolidated Mizuho International plc Group basis (distinct from the Company-only basis also shown in each Annual Report). FY2025/FY2024: Annual Report 2025, Consolidated Statement of Comprehensive Income and Consolidated Statement of Financial Position p.88-89, Consolidated Statement of Changes in Equity p.90-91. FY2023/FY2022: Annual Report 2024, same statements p.86-89. FY2021: Annual Report 2022, Consolidated Statement of Comprehensive Income p.84-85, Consolidated Statement of Financial Position and Consolidated Statement of Changes in Equity p.86, 88.</t>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863028d4802cdc23dd6552c_2020-mizuho-international-plc-annual-report.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302ac32d1c7376f1f1877_2019-mizuho-international-plc-annual-report.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302c5e1d535ec3306fbee_2018-mizuho-international-plc-annual-report-1.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302d732d1c7376f1f2ad2_2017-mizuho-international-plc-annual-report.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302eda925dd5c1687cecd_2016-mizuho-international-plc-annual-report.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68630302eca4998ff565c8ea_2015-mizuho-international-plc-annual-report.pdf; FY2014: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzEwNDY4NTMyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Balance Sheet/P&amp;L/Equity figures are the Consolidated Mizuho International plc Group basis for FY2019-FY2025 (distinct from the Company-only basis also shown in each Annual Report). FY2025/FY2024: Annual Report 2025, Consolidated Statement of Comprehensive Income and Consolidated Statement of Financial Position p.88-89, Consolidated Statement of Changes in Equity p.90-91. FY2023/FY2022: Annual Report 2024, same statements p.86-89. FY2021: Annual Report 2022, Consolidated Statement of Comprehensive Income p.84-85, Consolidated Statement of Financial Position and Consolidated Statement of Changes in Equity p.86, 88. FY2020: Annual Report 2020, Consolidated Statement of Comprehensive Income/Financial Position/Changes in Equity/Cash Flows p.34-39. FY2019: Annual Report 2019, same Consolidated statements p.22-27.
+REPORTING BASIS: FY2019-FY2025 are Consolidated Mizuho International plc Group basis (Group consolidation began FY2019). FY2015-FY2018 are Company-only basis under FRS 102 (restated from UK GAAP as at 1 April 2015 transition date); the Company did not yet prepare group accounts. FY2014 is Company-only, originally-filed UK GAAP (pre-FRS 102), sourced from the Companies House statutory filing rather than Mizuho's own site (see AR/P3 source dict comments) - there is a real ~£0.5m equity break between FY2014 as originally filed and the FRS102-restated FY2015 opening position (see the Statement of Changes in Equity's transition row). None of FY2014-FY2020 include a cash flow statement (FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent publishes consolidated accounts).
+FY2015-FY2018 (Company-only basis): FY2018 Annual Report, Statement of Comprehensive Income p.22, Statement of Financial Position p.23, Statement of Changes in Equity p.24. FY2017 Annual Report, same statements p.15-17. FY2016 Annual Report, same statements p.14-16 (FY2016 report's own FY2015 comparative column is the source for FY2015, restated to FRS 102). FY2014 (originally-filed UK GAAP, Company-only): Companies House 'Full accounts made up to 31 March 2014' filing, Profit and Loss Account p.13, Balance Sheet p.14, Consolidated Statement of Total Recognised Gains and Losses p.15.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A26:M26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5023,7 +7887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -5045,7 +7909,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Chronological roll-forward, oldest to newest, Consolidated Group basis. £m. Equity reconciliation ladder confirmed: every year's own closing balance ties exactly to both the next year's own opening balance and that year's own Balance Sheet Total Equity - zero plug rows needed anywhere across all 5 years. FY2025's Capital injection/Equity contribution/Transfer-to-P&amp;L rows relate to a capital raise and the release of a net dilapidation provision following termination of the Company's sub-lease, per the source's own explanatory note.</t>
+          <t>Chronological roll-forward, oldest to newest. Consolidated Group basis FY2019 onward; Company-only basis FY2014-FY2018 (see the 'REPORTING BASIS' source note). £m. Equity reconciliation ladder confirmed: every year's own closing balance ties exactly to both the next year's own opening balance and that year's own Balance Sheet Total Equity across all 12 years, with one disclosed exception: a real ~£0.5m break between FY2014's closing position as originally filed (UK GAAP, Companies House) and the FRS102-restated FY2015 opening position shown in the FY2016 Annual Report - the 'FRS 102 transition adjustment' row makes that break explicit rather than silently plugging it. FY2025's Capital injection/Equity contribution/Transfer-to-P&amp;L rows relate to a capital raise and the release of a net dilapidation provision following termination of the Company's sub-lease, per the source's own explanatory note. The FY2017 'Share capital reduction' cancelled MHI's cumulative loss balance (135,000,000 JPY ordinary shares and £111,534,584 ordinary shares were cancelled per the source's own explanatory note).</t>
         </is>
       </c>
     </row>
@@ -5089,152 +7953,144 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>At 1 April 2020 (FY2021 opening)</t>
+          <t>At 1 April 2013 (FY2014 opening, originally-filed UK GAAP)</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>709.9</v>
+        <v>2795.3</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n">
-        <v>-20.4</v>
+        <v>-2385.8</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>699.2</v>
+        <v>425.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
+          <t>Increase in paid up share capital</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>45</v>
+      </c>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n">
-        <v>42.8</v>
-      </c>
+      <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n">
-        <v>42.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income/(loss)</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="F6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n">
+        <v>-28</v>
+      </c>
       <c r="G6" s="6" t="n">
-        <v>-0.4</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>At 31 March 2021 (FY2021 closing)</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>709.9</v>
-      </c>
-      <c r="C7" s="5" t="n">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Actuarial loss on defined benefit scheme</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2014 (FY2014 closing, originally-filed UK GAAP)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>2840.3</v>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>741.6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n">
-        <v>-28.8</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>-28.8</v>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n">
+        <v>-2416.3</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>439.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income/(loss)</t>
+          <t>FRS 102 transition adjustment (1 April 2014) - reclassifies a pension reserve out of the profit and loss account plus a further ~£0.5m net restatement</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F9" s="6" t="n"/>
+        <v>-14</v>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n">
+        <v>13.5</v>
+      </c>
       <c r="G9" s="6" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>At 31 March 2022 (FY2022 closing)</t>
+          <t>At 1 April 2014 (FY2015 opening, FRS 102-restated)</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>709.9</v>
+        <v>2840.3</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>15.6</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-6.2</v>
+        <v>-14</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-6.4</v>
+        <v>-2402.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>712.4</v>
+        <v>439.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
+          <t>Profit for the year</t>
         </is>
       </c>
       <c r="B11" s="6" t="n"/>
@@ -5242,10 +8098,10 @@
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n">
-        <v>-4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-4.5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="12">
@@ -5257,169 +8113,167 @@
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0.1</v>
-      </c>
+        <v>-2.4</v>
+      </c>
+      <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n">
-        <v>-0.2</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>At 31 March 2023 (FY2023 closing)</t>
+          <t>At 31 March 2015 (FY2015 closing)</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>709.9</v>
+        <v>2840.3</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>15.6</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-6.5</v>
+        <v>-16.4</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-10.9</v>
+        <v>-2397.9</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>707.7</v>
+        <v>441.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
+          <t>Increase in paid up share capital</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>35</v>
+      </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n">
-        <v>13.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income/(loss)</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="F15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n">
+        <v>-15.4</v>
+      </c>
       <c r="G15" s="6" t="n">
-        <v>-0.5</v>
+        <v>-15.4</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>At 31 March 2024 (FY2024 closing)</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>709.9</v>
-      </c>
-      <c r="C16" s="5" t="n">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2016 (FY2016 closing)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>2875.3</v>
+      </c>
+      <c r="C17" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>720.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>7.2</v>
+      <c r="D17" s="5" t="n">
+        <v>-16.8</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2413.3</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>460.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Capital injection</t>
+          <t>Increase in paid up share capital</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>45</v>
+        <v>267.9</v>
       </c>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n">
-        <v>45</v>
+        <v>267.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Equity contribution</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
+          <t>Share capital reduction (cancels cumulative loss)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>-2433.3</v>
+      </c>
       <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="D19" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n">
+        <v>2413.3</v>
+      </c>
+      <c r="G19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Transfer to profit and loss account</t>
+          <t>Profit for the year</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n">
-        <v>-1.1</v>
-      </c>
+      <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G20" s="6" t="n"/>
+        <v>12.2</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>12.2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -5430,53 +8284,609 @@
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>-0.2</v>
-      </c>
+        <v>-4.5</v>
+      </c>
+      <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n">
-        <v>-0.5</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>At 31 March 2025 (FY2025 closing)</t>
+          <t>At 31 March 2017 (FY2017 closing)</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>754.9</v>
+        <v>709.9</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>15.6</v>
       </c>
       <c r="D22" s="5" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>736.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2018 (FY2018 closing)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>761.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-19.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2019 (FY2019 closing)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>740.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n">
+        <v>-40.7</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-40.7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2020 (FY2020 closing)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>699.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>At 1 April 2020 (FY2021 opening)</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>699.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2021 (FY2021 closing)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>741.6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>-28.8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2022 (FY2022 closing)</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>712.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2023 (FY2023 closing)</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>707.7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2024 (FY2024 closing)</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>720.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Capital injection</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Equity contribution</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Transfer to profit and loss account</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2025 (FY2025 closing)</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>754.9</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D50" s="5" t="n">
         <v>-7.1</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E50" s="5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F50" s="5" t="n">
         <v>10.9</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G50" s="5" t="n">
         <v>773.5</v>
       </c>
     </row>
-    <row r="24" ht="150" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf
-Balance Sheet/P&amp;L/Equity figures are the Consolidated Mizuho International plc Group basis (distinct from the Company-only basis also shown in each Annual Report). FY2025/FY2024: Annual Report 2025, Consolidated Statement of Comprehensive Income and Consolidated Statement of Financial Position p.88-89, Consolidated Statement of Changes in Equity p.90-91. FY2023/FY2022: Annual Report 2024, same statements p.86-89. FY2021: Annual Report 2022, Consolidated Statement of Comprehensive Income p.84-85, Consolidated Statement of Financial Position and Consolidated Statement of Changes in Equity p.86, 88.</t>
+    <row r="52" ht="150" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863028d4802cdc23dd6552c_2020-mizuho-international-plc-annual-report.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302ac32d1c7376f1f1877_2019-mizuho-international-plc-annual-report.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302c5e1d535ec3306fbee_2018-mizuho-international-plc-annual-report-1.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302d732d1c7376f1f2ad2_2017-mizuho-international-plc-annual-report.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302eda925dd5c1687cecd_2016-mizuho-international-plc-annual-report.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68630302eca4998ff565c8ea_2015-mizuho-international-plc-annual-report.pdf; FY2014: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzEwNDY4NTMyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Balance Sheet/P&amp;L/Equity figures are the Consolidated Mizuho International plc Group basis for FY2019-FY2025 (distinct from the Company-only basis also shown in each Annual Report). FY2025/FY2024: Annual Report 2025, Consolidated Statement of Comprehensive Income and Consolidated Statement of Financial Position p.88-89, Consolidated Statement of Changes in Equity p.90-91. FY2023/FY2022: Annual Report 2024, same statements p.86-89. FY2021: Annual Report 2022, Consolidated Statement of Comprehensive Income p.84-85, Consolidated Statement of Financial Position and Consolidated Statement of Changes in Equity p.86, 88. FY2020: Annual Report 2020, Consolidated Statement of Comprehensive Income/Financial Position/Changes in Equity/Cash Flows p.34-39. FY2019: Annual Report 2019, same Consolidated statements p.22-27.
+REPORTING BASIS: FY2019-FY2025 are Consolidated Mizuho International plc Group basis (Group consolidation began FY2019). FY2015-FY2018 are Company-only basis under FRS 102 (restated from UK GAAP as at 1 April 2015 transition date); the Company did not yet prepare group accounts. FY2014 is Company-only, originally-filed UK GAAP (pre-FRS 102), sourced from the Companies House statutory filing rather than Mizuho's own site (see AR/P3 source dict comments) - there is a real ~£0.5m equity break between FY2014 as originally filed and the FRS102-restated FY2015 opening position (see the Statement of Changes in Equity's transition row). None of FY2014-FY2020 include a cash flow statement (FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent publishes consolidated accounts).
+FY2015-FY2018 (Company-only basis): FY2018 Annual Report, Statement of Comprehensive Income p.22, Statement of Financial Position p.23, Statement of Changes in Equity p.24. FY2017 Annual Report, same statements p.15-17. FY2016 Annual Report, same statements p.14-16 (FY2016 report's own FY2015 comparative column is the source for FY2015, restated to FRS 102). FY2014 (originally-filed UK GAAP, Company-only): Companies House 'Full accounts made up to 31 March 2014' filing, Profit and Loss Account p.13, Balance Sheet p.14, Consolidated Statement of Total Recognised Gains and Losses p.15.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A52:G52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5488,7 +8898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -5497,6 +8907,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5509,7 +8926,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Group basis, £ millions</t>
+          <t>Consolidated Group basis, £ millions. FY2014-FY2020 are blank (not zero): none of those years' Annual Reports include a cash flow statement, each invoking the FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent (Mizuho Financial Group, Inc.) publishes consolidated financial statements including the Company - the same exemption basis as FY2021-FY2025's ENTITY NOTE.</t>
         </is>
       </c>
     </row>
@@ -5542,6 +8959,41 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£m)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£m)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£m)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£m)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£m)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016 (£m)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015 (£m)</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014 (£m)</t>
         </is>
       </c>
     </row>
@@ -5556,6 +9008,13 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5578,6 +9037,13 @@
       <c r="F5" s="6" t="n">
         <v>43.8</v>
       </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -5600,6 +9066,13 @@
       <c r="F6" s="6" t="n">
         <v>23.3</v>
       </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -5622,6 +9095,13 @@
       <c r="F7" s="6" t="n">
         <v>-0.4</v>
       </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -5644,6 +9124,13 @@
       <c r="F8" s="6" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -5666,6 +9153,13 @@
       <c r="F9" s="6" t="n">
         <v>6374.7</v>
       </c>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -5688,6 +9182,13 @@
       <c r="F10" s="6" t="n">
         <v>-6952.2</v>
       </c>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -5710,6 +9211,13 @@
       <c r="F11" s="6" t="n">
         <v>-1.3</v>
       </c>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5732,6 +9240,13 @@
       <c r="F12" s="6" t="n">
         <v>16.4</v>
       </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -5754,6 +9269,13 @@
       <c r="F13" s="6" t="n">
         <v>10.5</v>
       </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -5776,6 +9298,13 @@
       <c r="F14" s="5" t="n">
         <v>-485.7</v>
       </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -5788,6 +9317,13 @@
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -5810,6 +9346,13 @@
       <c r="F16" s="6" t="n">
         <v>-0.1</v>
       </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -5832,6 +9375,13 @@
       <c r="F17" s="6" t="n">
         <v>0.4</v>
       </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -5854,6 +9404,13 @@
       <c r="F18" s="6" t="n">
         <v>-21.8</v>
       </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -5876,6 +9433,13 @@
       <c r="F19" s="6" t="n">
         <v>-3.6</v>
       </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -5898,6 +9462,13 @@
       <c r="F20" s="5" t="n">
         <v>-25.1</v>
       </c>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -5910,6 +9481,13 @@
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5932,6 +9510,13 @@
       <c r="F22" s="6" t="n">
         <v>75.59999999999999</v>
       </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -5946,6 +9531,13 @@
         <v>-45</v>
       </c>
       <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -5960,6 +9552,13 @@
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -5982,6 +9581,13 @@
       <c r="F25" s="5" t="n">
         <v>75.59999999999999</v>
       </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -6004,6 +9610,13 @@
       <c r="F26" s="5" t="n">
         <v>-435.2</v>
       </c>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -6026,6 +9639,13 @@
       <c r="F27" s="5" t="n">
         <v>-6.6</v>
       </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -6048,6 +9668,13 @@
       <c r="F28" s="5" t="n">
         <v>779.3</v>
       </c>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -6070,18 +9697,25 @@
       <c r="F29" s="5" t="n">
         <v>337.5</v>
       </c>
-    </row>
-    <row r="31" ht="220" customHeight="1">
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+    </row>
+    <row r="31" ht="240" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf</t>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863028d4802cdc23dd6552c_2020-mizuho-international-plc-annual-report.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302ac32d1c7376f1f1877_2019-mizuho-international-plc-annual-report.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302c5e1d535ec3306fbee_2018-mizuho-international-plc-annual-report-1.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302d732d1c7376f1f2ad2_2017-mizuho-international-plc-annual-report.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302eda925dd5c1687cecd_2016-mizuho-international-plc-annual-report.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68630302eca4998ff565c8ea_2015-mizuho-international-plc-annual-report.pdf; FY2014: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzEwNDY4NTMyOGFkaXF6a2N4/document?format=pdf&amp;download=0</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A31:M31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6093,7 +9727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
@@ -6102,6 +9736,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6114,7 +9755,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 3 credit risk exposures by credit quality step (Table 23), standardised approach, £m — substitutes for an IFRS 9 stage split, which this Group does not disclose (it runs no material customer lending book).</t>
+          <t>Pillar 3 credit risk exposures by credit quality step (Table 23; the equivalent table carries a different number in earlier disclosures, e.g. Table 25 for FY2014, Table 18 for FY2015-FY2016), standardised approach, £m — substitutes for an IFRS 9 stage split, which this Group does not disclose (it runs no material customer lending book). FY2014-FY2016 report at 'Mizuho Securities UK Holdings Ltd' (MSUKH) group level, MHI's immediate parent, not at MHI level directly (see the P3 source dict comment) — broadly but not exactly comparable to the MHI-level figures used from FY2017 onward, since MHI is described in those disclosures as MSUKH's principal operating subsidiary rather than its sole business.</t>
         </is>
       </c>
     </row>
@@ -6147,6 +9788,41 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021 (£m)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£m)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£m)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£m)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£m)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016 (£m)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015 (£m)</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014 (£m)</t>
         </is>
       </c>
     </row>
@@ -6161,6 +9837,13 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6183,6 +9866,27 @@
       <c r="F5" s="6" t="n">
         <v>303.7</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>611.6</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>234.5</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -6205,6 +9909,27 @@
       <c r="F6" s="6" t="n">
         <v>31.3</v>
       </c>
+      <c r="G6" s="6" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>128.4</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>61.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -6225,6 +9950,21 @@
         <v>20.4</v>
       </c>
       <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -6237,6 +9977,13 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -6259,6 +10006,21 @@
       <c r="F9" s="6" t="n">
         <v>6.9</v>
       </c>
+      <c r="G9" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -6281,6 +10043,23 @@
       <c r="F10" s="6" t="n">
         <v>1.7</v>
       </c>
+      <c r="G10" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -6303,6 +10082,27 @@
       <c r="F11" s="6" t="n">
         <v>64.7</v>
       </c>
+      <c r="G11" s="6" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>48.9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -6325,6 +10125,27 @@
       <c r="F12" s="5" t="n">
         <v>408.2</v>
       </c>
+      <c r="G12" s="5" t="n">
+        <v>743</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>334</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>175.9</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>174.8</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>119.4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -6347,6 +10168,27 @@
       <c r="F13" s="6" t="n">
         <v>437.9</v>
       </c>
+      <c r="G13" s="6" t="n">
+        <v>834.2</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>257.9</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>401.6</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>228.7</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>174.8</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>119.4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -6369,6 +10211,27 @@
       <c r="F14" s="6" t="n">
         <v>92.8</v>
       </c>
+      <c r="G14" s="6" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>64.3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -6401,19 +10264,54 @@
           <t>22.73%</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="240" customHeight="1">
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>11.56%</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>48.06%</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>26.36%</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>35.24%</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>57.48%</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>67.79%</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>53.87%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="260" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf
-Table 23 'Credit risk exposures and RWAs by credit quality step', section 8.3 'Analysis of credit risk exposures', in each year's own Pillar 3 disclosure document listed above.</t>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf
+Credit risk exposures and RWAs by credit quality step table, section 'Analysis of credit risk exposures', in each year's own Pillar 3 disclosure document listed above.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A17:M17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6425,7 +10323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6434,6 +10332,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6481,6 +10386,41 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6503,26 +10443,47 @@
       <c r="F4" s="6" t="n">
         <v>675.6</v>
       </c>
+      <c r="G4" s="6" t="n">
+        <v>623.7</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>662.5</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>690.9</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>658.3</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>408.3</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>451.9</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>456.9</v>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2025 Annual Report states regulatory capital consists solely of Tier 1 capital; treated as CET1 for this metric because no Tier 2 capital is reported.</t>
+          <t>Note: FY2025 Annual Report states regulatory capital consists solely of Tier 1 capital; treated as CET1 for this metric because no Tier 2 capital is reported. FY2014-FY2016 capital resources consisted solely of common equity Tier 1 (no Tier 2 issued yet); FY2014-FY2016 are MSUKH group-level figures, not MHI-level (see the P3 source dict comment).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="220" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A7:M7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6534,7 +10495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6543,6 +10504,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6590,6 +10558,41 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6622,18 +10625,53 @@
           <t>31.12%</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>20.02%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>30.6%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>32.9%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>49.5%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>50.3%</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="220" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:M6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6645,7 +10683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -6654,6 +10692,13 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6701,6 +10746,41 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6723,18 +10803,39 @@
       <c r="F4" s="6" t="n">
         <v>675.6</v>
       </c>
+      <c r="G4" s="6" t="n">
+        <v>623.7</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>662.5</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>690.9</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>658.3</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>408.3</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>451.9</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>456.9</v>
+      </c>
     </row>
     <row r="6" ht="220" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement.
-Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf</t>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:M6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
+++ b/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
@@ -5388,7 +5388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -5404,6 +5404,12 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5416,7 +5422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Group basis for FY2019-FY2025; Company-only basis for FY2014-FY2018 (see the 'REPORTING BASIS' source note). FY2021 shows a genuine structural difference from FY2022 onward: the standalone 'Subordinated liabilities' line was fully repaid during FY2022 (see the Cash Flow Statement's 'Net repayment of subordinated liabilities' row) and is absent from FY2022 onward; it was first issued in FY2016 and continued unbroken FY2016-FY2021. FY2014 (originally-filed UK GAAP, pre-FRS 102) combines several lines that later years disclose separately: 'Reverse repurchase agreements with banks' and 'Repurchase agreements with banks' each carry the FY2014 source's single undifferentiated repo total (not split by bank/customer counterparty - the 'with customers' rows are blank for FY2014 only); 'Derivative assets'/'Derivative liabilities' sum the FY2014 source's separate trading and risk-management derivative lines; 'Debt and other fixed income securities' carries the FY2014 source's combined 'Trading financial assets' line (equity shares not split out); 'Short trading positions' carries the FY2014 source's 'Trading financial liabilities' line; 'Other liabilities' includes the FY2014 source's separately-disclosed £2.3m defined benefit pension liability. FY2014 has no separate Cash/Shares in group undertakings/Intangible assets/Pension reserve lines (nil or not yet recognised as separate categories pre-FRS 102) - shown blank, not zero. £m.</t>
+          <t>Consolidated Group basis for FY2019-FY2025; Company-only basis for FY2014-FY2018 (see the 'REPORTING BASIS' source note). FY2021 shows a genuine structural difference from FY2022 onward: the standalone 'Subordinated liabilities' line was fully repaid during FY2022 (see the Cash Flow Statement's 'Net repayment of subordinated liabilities' row) and is absent from FY2022 onward; it was first issued in FY2016 and continued unbroken FY2016-FY2021. FY2014 (originally-filed UK GAAP, pre-FRS 102) combines several lines that later years disclose separately: 'Reverse repurchase agreements with banks' and 'Repurchase agreements with banks' each carry the FY2014 source's single undifferentiated repo total (not split by bank/customer counterparty - the 'with customers' rows are blank for FY2014 only); 'Derivative assets'/'Derivative liabilities' sum the FY2014 source's separate trading and risk-management derivative lines; 'Debt and other fixed income securities' carries the FY2014 source's combined 'Trading financial assets' line (equity shares not split out); 'Short trading positions' carries the FY2014 source's 'Trading financial liabilities' line; 'Other liabilities' includes the FY2014 source's separately-disclosed £2.3m defined benefit pension liability. FY2014 has no separate Cash/Shares in group undertakings/Intangible assets/Pension reserve lines (nil or not yet recognised as separate categories pre-FRS 102) - shown blank, not zero. HD-075: FY2008-FY2013 follow the same FY2014-style combined presentation (single 'Reverse repurchase agreements with banks'/'Repurchase agreements with banks' lines, combined 'Derivative assets'/'Derivative liabilities', 'Debt and other fixed income securities' carrying that year's combined trading financial assets total) since each year's own primary Balance Sheet presents them the same undifferentiated way; 'Equity shares' for FY2008-FY2013 carries that year's separately-disclosed 'Financial investments' note (unlisted equity securities designated at fair value) rather than a trading-book equity split, which those years don't disclose. 'Other liabilities' folds in each year's own separately-disclosed defined benefit pension liability where one exists (FY2010: £3.8m; FY2011: £0.9m; FY2008: £0.4m; nil FY2009/FY2012/FY2013). 'Subordinated liabilities' (£18.6m) appears only in FY2008 - fully repaid before FY2009's balance sheet date, not disclosed again until FY2016. FY2008/FY2009 Balance Sheet figures are Company-only (this Company did not present a separate Company P&amp;L those two years - see the REPORTING BASIS note). FY2011's own originally-filed balance sheet (not FY2012's later restated comparative) is used, following a disclosed voluntary change from trade-date to settlement-date accounting made during FY2012 - see the REPORTING BASIS note for the resulting break in 'Other assets'/'Debt and other fixed income securities' between FY2011 and FY2012. £m.</t>
         </is>
       </c>
     </row>
@@ -5484,6 +5490,36 @@
       <c r="M3" s="4" t="inlineStr">
         <is>
           <t>FY2014 (£m)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>FY2013 (£m)</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>FY2012 (£m)</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>FY2011 (£m)</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>FY2010 (£m)</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>FY2009 (£m)</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>FY2008 (£m)</t>
         </is>
       </c>
     </row>
@@ -5505,6 +5541,12 @@
       <c r="K4" s="6" t="n"/>
       <c r="L4" s="6" t="n"/>
       <c r="M4" s="6" t="n"/>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="6" t="n"/>
+      <c r="R4" s="6" t="n"/>
+      <c r="S4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5544,6 +5586,12 @@
       </c>
       <c r="L5" s="6" t="n"/>
       <c r="M5" s="6" t="n"/>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n"/>
+      <c r="Q5" s="6" t="n"/>
+      <c r="R5" s="6" t="n"/>
+      <c r="S5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -5586,6 +5634,24 @@
       </c>
       <c r="M6" s="6" t="n">
         <v>96.09999999999999</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="O6" s="6" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>38.2</v>
       </c>
     </row>
     <row r="7">
@@ -5610,6 +5676,24 @@
       <c r="M7" s="6" t="n">
         <v>0.4</v>
       </c>
+      <c r="N7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -5653,6 +5737,24 @@
       <c r="M8" s="6" t="n">
         <v>24398.2</v>
       </c>
+      <c r="N8" s="6" t="n">
+        <v>27598.4</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>23596.2</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>24795.3</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>29267.2</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>15811.8</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>19168.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -5694,6 +5796,12 @@
         <v>5083.7</v>
       </c>
       <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="6" t="n"/>
+      <c r="R9" s="6" t="n"/>
+      <c r="S9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -5737,6 +5845,24 @@
       <c r="M10" s="6" t="n">
         <v>3907.2</v>
       </c>
+      <c r="N10" s="6" t="n">
+        <v>2857.7</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>1421</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>1440.4</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>926.1</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>1421.5</v>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>2361.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -5778,6 +5904,24 @@
         <v>6.3</v>
       </c>
       <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="S11" s="6" t="n">
+        <v>78.09999999999999</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5821,6 +5965,24 @@
       <c r="M12" s="6" t="n">
         <v>204.7</v>
       </c>
+      <c r="N12" s="6" t="n">
+        <v>281.3</v>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>382.7</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>480.5</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>828.6</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>1925.9</v>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>1468.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -5862,6 +6024,12 @@
         <v>3.6</v>
       </c>
       <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="6" t="n"/>
+      <c r="R13" s="6" t="n"/>
+      <c r="S13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -5903,6 +6071,12 @@
         <v>47.6</v>
       </c>
       <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="6" t="n"/>
+      <c r="R14" s="6" t="n"/>
+      <c r="S14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -5946,6 +6120,24 @@
       <c r="M15" s="6" t="n">
         <v>12.7</v>
       </c>
+      <c r="N15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="O15" s="6" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>18.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -5989,6 +6181,24 @@
       <c r="M16" s="6" t="n">
         <v>217.7</v>
       </c>
+      <c r="N16" s="6" t="n">
+        <v>159</v>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>201.1</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>2786.9</v>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v>1983.5</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>2360.3</v>
+      </c>
+      <c r="S16" s="6" t="n">
+        <v>1534.4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -6032,6 +6242,24 @@
       <c r="M17" s="6" t="n">
         <v>46.2</v>
       </c>
+      <c r="N17" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="O17" s="6" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <v>84.59999999999999</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -6074,6 +6302,24 @@
       </c>
       <c r="M18" s="5" t="n">
         <v>28883.2</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>31059.8</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>25873.1</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>29781.5</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>33435.8</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>21815.2</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>24761.1</v>
       </c>
     </row>
     <row r="19">
@@ -6094,6 +6340,12 @@
       <c r="K19" s="6" t="n"/>
       <c r="L19" s="6" t="n"/>
       <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="n"/>
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -6137,6 +6389,24 @@
       <c r="M20" s="6" t="n">
         <v>744.1</v>
       </c>
+      <c r="N20" s="6" t="n">
+        <v>724.2</v>
+      </c>
+      <c r="O20" s="6" t="n">
+        <v>841.4</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>863.4</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>727.3</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>832.3</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>741.2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -6180,6 +6450,24 @@
       <c r="M21" s="6" t="n">
         <v>294</v>
       </c>
+      <c r="N21" s="6" t="n">
+        <v>311.4</v>
+      </c>
+      <c r="O21" s="6" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -6223,6 +6511,24 @@
       <c r="M22" s="6" t="n">
         <v>23465.2</v>
       </c>
+      <c r="N22" s="6" t="n">
+        <v>27233</v>
+      </c>
+      <c r="O22" s="6" t="n">
+        <v>21279.6</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>22658.3</v>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v>27548.1</v>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v>14302.6</v>
+      </c>
+      <c r="S22" s="6" t="n">
+        <v>18464.7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -6264,6 +6570,12 @@
         <v>11966</v>
       </c>
       <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="6" t="n"/>
+      <c r="R23" s="6" t="n"/>
+      <c r="S23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -6307,6 +6619,24 @@
       <c r="M24" s="6" t="n">
         <v>976.6</v>
       </c>
+      <c r="N24" s="6" t="n">
+        <v>866.8</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>1189.7</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>1350.3</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>1468.3</v>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v>2051.2</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <v>1514.5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -6350,6 +6680,24 @@
       <c r="M25" s="6" t="n">
         <v>2600.9</v>
       </c>
+      <c r="N25" s="6" t="n">
+        <v>1061.9</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>1439.6</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v>1317.2</v>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="S25" s="6" t="n">
+        <v>706.3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -6393,6 +6741,24 @@
       <c r="M26" s="6" t="n">
         <v>181.6</v>
       </c>
+      <c r="N26" s="6" t="n">
+        <v>283.6</v>
+      </c>
+      <c r="O26" s="6" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v>513.3</v>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v>920.8</v>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v>2563</v>
+      </c>
+      <c r="S26" s="6" t="n">
+        <v>2021</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -6436,6 +6802,24 @@
       <c r="M27" s="6" t="n">
         <v>95.3</v>
       </c>
+      <c r="N27" s="6" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="O27" s="6" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v>2594.5</v>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v>1836.7</v>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v>1447.4</v>
+      </c>
+      <c r="S27" s="6" t="n">
+        <v>602.4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -6479,6 +6863,24 @@
       <c r="M28" s="6" t="n">
         <v>69.59999999999999</v>
       </c>
+      <c r="N28" s="6" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="O28" s="6" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="S28" s="6" t="n">
+        <v>162.1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -6521,6 +6923,24 @@
       </c>
       <c r="M29" s="6" t="n">
         <v>16.3</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S29" s="6" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -6553,6 +6973,14 @@
       </c>
       <c r="L30" s="6" t="n"/>
       <c r="M30" s="6" t="n"/>
+      <c r="N30" s="6" t="n"/>
+      <c r="O30" s="6" t="n"/>
+      <c r="P30" s="6" t="n"/>
+      <c r="Q30" s="6" t="n"/>
+      <c r="R30" s="6" t="n"/>
+      <c r="S30" s="6" t="n">
+        <v>18.6</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -6595,6 +7023,24 @@
       </c>
       <c r="M31" s="5" t="n">
         <v>28443.6</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>30634.7</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>25525.5</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>29512</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>33014</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>21461.1</v>
+      </c>
+      <c r="S31" s="5" t="n">
+        <v>24248.6</v>
       </c>
     </row>
     <row r="32">
@@ -6615,6 +7061,12 @@
       <c r="K32" s="6" t="n"/>
       <c r="L32" s="6" t="n"/>
       <c r="M32" s="6" t="n"/>
+      <c r="N32" s="6" t="n"/>
+      <c r="O32" s="6" t="n"/>
+      <c r="P32" s="6" t="n"/>
+      <c r="Q32" s="6" t="n"/>
+      <c r="R32" s="6" t="n"/>
+      <c r="S32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -6658,6 +7110,24 @@
       <c r="M33" s="6" t="n">
         <v>2840.3</v>
       </c>
+      <c r="N33" s="6" t="n">
+        <v>2795.3</v>
+      </c>
+      <c r="O33" s="6" t="n">
+        <v>2712.3</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v>2462.3</v>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v>2462.3</v>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v>2426.4</v>
+      </c>
+      <c r="S33" s="6" t="n">
+        <v>2314.6</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -6701,6 +7171,24 @@
       <c r="M34" s="6" t="n">
         <v>15.6</v>
       </c>
+      <c r="N34" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="O34" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="S34" s="6" t="n">
+        <v>15.6</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -6742,6 +7230,12 @@
         <v>-16.4</v>
       </c>
       <c r="M35" s="6" t="n"/>
+      <c r="N35" s="6" t="n"/>
+      <c r="O35" s="6" t="n"/>
+      <c r="P35" s="6" t="n"/>
+      <c r="Q35" s="6" t="n"/>
+      <c r="R35" s="6" t="n"/>
+      <c r="S35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -6771,6 +7265,12 @@
       <c r="K36" s="6" t="n"/>
       <c r="L36" s="6" t="n"/>
       <c r="M36" s="6" t="n"/>
+      <c r="N36" s="6" t="n"/>
+      <c r="O36" s="6" t="n"/>
+      <c r="P36" s="6" t="n"/>
+      <c r="Q36" s="6" t="n"/>
+      <c r="R36" s="6" t="n"/>
+      <c r="S36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -6814,6 +7314,24 @@
       <c r="M37" s="6" t="n">
         <v>-2416.3</v>
       </c>
+      <c r="N37" s="6" t="n">
+        <v>-2385.8</v>
+      </c>
+      <c r="O37" s="6" t="n">
+        <v>-2380.3</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v>-2208.4</v>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v>-2056.1</v>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v>-2087.9</v>
+      </c>
+      <c r="S37" s="6" t="n">
+        <v>-1817.7</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -6857,6 +7375,24 @@
       <c r="M38" s="5" t="n">
         <v>439.6</v>
       </c>
+      <c r="N38" s="5" t="n">
+        <v>425.1</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>347.6</v>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>421.8</v>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>354.1</v>
+      </c>
+      <c r="S38" s="5" t="n">
+        <v>512.5</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -6900,21 +7436,41 @@
       <c r="M39" s="5" t="n">
         <v>28883.2</v>
       </c>
+      <c r="N39" s="5" t="n">
+        <v>31059.8</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>25873.1</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>29781.5</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>33435.8</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>21815.2</v>
+      </c>
+      <c r="S39" s="5" t="n">
+        <v>24761.1</v>
+      </c>
     </row>
     <row r="41" ht="260" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
 Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863028d4802cdc23dd6552c_2020-mizuho-international-plc-annual-report.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302ac32d1c7376f1f1877_2019-mizuho-international-plc-annual-report.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302c5e1d535ec3306fbee_2018-mizuho-international-plc-annual-report-1.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302d732d1c7376f1f2ad2_2017-mizuho-international-plc-annual-report.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302eda925dd5c1687cecd_2016-mizuho-international-plc-annual-report.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68630302eca4998ff565c8ea_2015-mizuho-international-plc-annual-report.pdf; FY2014: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzEwNDY4NTMyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Official Companies House statutory filing sources for the FY2008-FY2013 extension (HD-075): FY2013: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA4MDE5NTMxMmFkaXF6a2N4/document?format=pdf&amp;download=0; FY2012: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA2NTI2MzY4MGFkaXF6a2N4/document?format=pdf&amp;download=0; FY2011: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA0NDQ4MDc5N2FkaXF6a2N4/document?format=pdf&amp;download=0; FY2010: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzAyMzM2MTY3OWFkaXF6a2N4/document?format=pdf&amp;download=0; FY2009: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MjA0MjM3OTU5NmFkaXF6a2N4/document?format=pdf&amp;download=0; FY2008: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MjAxMDQ0NzA1NmFkaXF6a2N4/document?format=pdf&amp;download=0
 Balance Sheet/P&amp;L/Equity figures are the Consolidated Mizuho International plc Group basis for FY2019-FY2025 (distinct from the Company-only basis also shown in each Annual Report). FY2025/FY2024: Annual Report 2025, Consolidated Statement of Comprehensive Income and Consolidated Statement of Financial Position p.88-89, Consolidated Statement of Changes in Equity p.90-91. FY2023/FY2022: Annual Report 2024, same statements p.86-89. FY2021: Annual Report 2022, Consolidated Statement of Comprehensive Income p.84-85, Consolidated Statement of Financial Position and Consolidated Statement of Changes in Equity p.86, 88. FY2020: Annual Report 2020, Consolidated Statement of Comprehensive Income/Financial Position/Changes in Equity/Cash Flows p.34-39. FY2019: Annual Report 2019, same Consolidated statements p.22-27.
-REPORTING BASIS: FY2019-FY2025 are Consolidated Mizuho International plc Group basis (Group consolidation began FY2019). FY2015-FY2018 are Company-only basis under FRS 102 (restated from UK GAAP as at 1 April 2015 transition date); the Company did not yet prepare group accounts. FY2014 is Company-only, originally-filed UK GAAP (pre-FRS 102), sourced from the Companies House statutory filing rather than Mizuho's own site (see AR/P3 source dict comments) - there is a real ~£0.5m equity break between FY2014 as originally filed and the FRS102-restated FY2015 opening position (see the Statement of Changes in Equity's transition row). None of FY2014-FY2020 include a cash flow statement (FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent publishes consolidated accounts).
-FY2015-FY2018 (Company-only basis): FY2018 Annual Report, Statement of Comprehensive Income p.22, Statement of Financial Position p.23, Statement of Changes in Equity p.24. FY2017 Annual Report, same statements p.15-17. FY2016 Annual Report, same statements p.14-16 (FY2016 report's own FY2015 comparative column is the source for FY2015, restated to FRS 102). FY2014 (originally-filed UK GAAP, Company-only): Companies House 'Full accounts made up to 31 March 2014' filing, Profit and Loss Account p.13, Balance Sheet p.14, Consolidated Statement of Total Recognised Gains and Losses p.15.</t>
+REPORTING BASIS: FY2019-FY2025 are Consolidated Mizuho International plc Group basis (Group consolidation began FY2019). FY2015-FY2018 are Company-only basis under FRS 102 (restated from UK GAAP as at 1 April 2015 transition date); the Company did not yet prepare group accounts. FY2010-FY2014 are Company-only, originally-filed UK GAAP (pre-FRS 102), sourced from the Companies House statutory filing rather than Mizuho's own site (see AR/P3/CH_STATUTORY source dict comments) - there is a real ~£0.5m equity break between FY2014 as originally filed and the FRS102-restated FY2015 opening position (see the Statement of Changes in Equity's transition row). FY2008-FY2009 are a mixed basis dictated by what each year's own filing actually presents: the Balance Sheet is Company-only (matching the FY2010-FY2014 convention) but the Profit and Loss Account is Consolidated (the Company did not present its own P&amp;L those two years, relying on the Companies Act exemption for a subsidiary whose consolidated P&amp;L is presented instead) - Total Equity is identical under either basis for FY2008/FY2009 (the Group/Company difference is confined to derivative and repo gross-up presentation on the asset/liability sides), so this mixed basis does not affect the equity reconciliation ladder. None of FY2008-FY2020 include a cash flow statement (FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent publishes consolidated accounts, per each year's own Annual Report). FY2012's own filing discloses a voluntary accounting policy change made during FY2012, from trade-date to settlement-date accounting for regular-way trading securities transactions; applied retrospectively, it shrank the FY2011 comparative shown in FY2012's own report (Total Assets 29,781.5 -&gt; 27,034.4, largely a reclassification out of 'Other assets') versus FY2011's own originally-filed trade-date figures used for the FY2011 column here (per this project's own-year-filing sourcing rule) - a real, disclosed break between the FY2011 and FY2012 columns, not a transcription error.
+FY2015-FY2018 (Company-only basis): FY2018 Annual Report, Statement of Comprehensive Income p.22, Statement of Financial Position p.23, Statement of Changes in Equity p.24. FY2017 Annual Report, same statements p.15-17. FY2016 Annual Report, same statements p.14-16 (FY2016 report's own FY2015 comparative column is the source for FY2015, restated to FRS 102). FY2014 (originally-filed UK GAAP, Company-only): Companies House 'Full accounts made up to 31 March 2014' filing, Profit and Loss Account p.13, Balance Sheet p.14, Consolidated Statement of Total Recognised Gains and Losses p.15.
+HD-075 (FY2008-FY2013, all Companies House statutory filings, see CH_STATUTORY above): FY2013 'Full accounts made up to 31 March 2013' filing, Profit and Loss Account p.12, Balance Sheet p.13, Statement of Total Recognised Gains and Losses p.14, Equity note (note 26, also source for the FY2012 comparative column) p.45. FY2012 'Full accounts made up to 31 March 2012' filing, Profit and Loss Account p.14, Balance Sheet p.15, Statement of Total Recognised Gains and Losses p.16, Changes in accounting policy note (settlement-date vs trade-date accounting change disclosed against the FY2011 comparative) p.18. FY2011 'Full accounts made up to 31 March 2011' filing (own originally-filed trade-date basis, not FY2012's restated comparative), Profit and Loss Account p.13, Balance Sheet p.14, Statement of Total Recognised Gains and Losses p.15. FY2010 'Full accounts made up to 31 March 2010' filing, Profit and Loss Account p.13, Balance Sheet p.14, Statement of Total Recognised Gains and Losses p.16 (own FY2009 comparative column cross-checked against the FY2009 filing below). FY2009 'Group of companies' accounts made up to 31 March 2009' filing: Company Balance Sheet p.15 (Company-only basis used here, per REPORTING BASIS note above); Consolidated Profit and Loss Account p.12 and Statement of Total Recognised Gains and Losses p.14 (no separate Company P&amp;L presented that year - Companies Act exemption); Equity note (note 28, also source for the FY2008 comparative column and dividend disclosure) p.52. FY2008 'Group of companies' accounts made up to 31 March 2008' filing: Balance Sheet (Company-only) p.16, Consolidated Profit and Loss Account p.13, Statement of Total Recognised Gains and Losses p.15, Called Up Share Capital note 27 p.51, Equity note 28 (share capital movements, dividends paid, actuarial loss, fair value reserve release, and the FY2007 opening position used as the equity ladder's starting row) p.52.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A41:M41"/>
+    <mergeCell ref="A41:S41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6926,7 +7482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -6942,6 +7498,12 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6954,7 +7516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Group basis for FY2019-FY2025; Company-only basis for FY2014-FY2018 (see the 'REPORTING BASIS' source note). Re-measurement losses from defined benefit scheme were nil (not disclosed as a line) in FY2021; Provisions for liabilities was nil in FY2021 Company statement terms and is shown blank for FY2021 Consolidated as the report discloses no separate figure. FY2014-FY2020 did not disclose a separate FX translation line (shown blank, not zero). FY2014-FY2017 each disclosed a £nil tax charge/credit (shown here as 0, per each year's own source).</t>
+          <t>Consolidated Group basis for FY2019-FY2025; Company-only basis for FY2014-FY2018 (see the 'REPORTING BASIS' source note). Re-measurement losses from defined benefit scheme were nil (not disclosed as a line) in FY2021; Provisions for liabilities was nil in FY2021 Company statement terms and is shown blank for FY2021 Consolidated as the report discloses no separate figure. FY2014-FY2020 did not disclose a separate FX translation line (shown blank, not zero). FY2014-FY2017 each disclosed a £nil tax charge/credit (shown here as 0, per each year's own source). HD-075: FY2008/FY2009 figures are Consolidated (the Company did not present its own P&amp;L those two years - a Companies Act exemption for a subsidiary whose consolidated P&amp;L is presented instead; see the REPORTING BASIS note); FY2010-FY2013 are Company-only. FY2011's original statement did not disclose a separate 'Interest payable' line at all (folded into 'Dealing profit' - shown blank here, not zero; FY2012's report separated it out for FY2011's restated comparative, but this project sources FY2011 from FY2011's own filing - see the REPORTING BASIS note). FY2010 disclosed £nil for Interest payable, Other operating income and Provisions for liabilities (shown as 0, not blank). 'Disposal of Custody business' (£28.2m, FY2013 only) reflects the sale of the Company's Custody business to Mizuho Trust &amp; Banking (Luxembourg) S.A., disclosed as a separate line between operating expenses and profit before tax in the FY2013 source. 'Valuation adjustments on available-for-sale financial investments released from equity' (£0.2m, FY2008 only) is a one-off item disclosed in the FY2008 Statement of Total Recognised Gains and Losses.</t>
         </is>
       </c>
     </row>
@@ -7022,6 +7584,36 @@
       <c r="M3" s="4" t="inlineStr">
         <is>
           <t>FY2014 (£m)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>FY2013 (£m)</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>FY2012 (£m)</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>FY2011 (£m)</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>FY2010 (£m)</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>FY2009 (£m)</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>FY2008 (£m)</t>
         </is>
       </c>
     </row>
@@ -7043,6 +7635,12 @@
       <c r="K4" s="6" t="n"/>
       <c r="L4" s="6" t="n"/>
       <c r="M4" s="6" t="n"/>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="6" t="n"/>
+      <c r="R4" s="6" t="n"/>
+      <c r="S4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7086,6 +7684,24 @@
       <c r="M5" s="6" t="n">
         <v>0.5</v>
       </c>
+      <c r="N5" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>31.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -7129,6 +7745,22 @@
       <c r="M6" s="6" t="n">
         <v>-9.300000000000001</v>
       </c>
+      <c r="N6" s="6" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="O6" s="6" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>-2.9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -7172,6 +7804,24 @@
       <c r="M7" s="5" t="n">
         <v>-8.800000000000001</v>
       </c>
+      <c r="N7" s="5" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>28.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -7215,6 +7865,24 @@
       <c r="M8" s="6" t="n">
         <v>71.3</v>
       </c>
+      <c r="N8" s="6" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>32.7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -7258,6 +7926,24 @@
       <c r="M9" s="6" t="n">
         <v>-28.5</v>
       </c>
+      <c r="N9" s="6" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>-36.6</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>-49.2</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>-56.3</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>-33.8</v>
+      </c>
+      <c r="S9" s="6" t="n">
+        <v>-53.4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -7301,6 +7987,24 @@
       <c r="M10" s="5" t="n">
         <v>42.8</v>
       </c>
+      <c r="N10" s="5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>-20.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -7344,6 +8048,24 @@
       <c r="M11" s="6" t="n">
         <v>53.5</v>
       </c>
+      <c r="N11" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>-41</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>-149.3</v>
+      </c>
+      <c r="S11" s="6" t="n">
+        <v>-1850.4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7387,6 +8109,24 @@
       <c r="M12" s="6" t="n">
         <v>0.1</v>
       </c>
+      <c r="N12" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -7430,6 +8170,24 @@
       <c r="M13" s="5" t="n">
         <v>87.59999999999999</v>
       </c>
+      <c r="N13" s="5" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>-17.3</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>159.8</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>-131.2</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>-1840.4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -7473,6 +8231,24 @@
       <c r="M14" s="6" t="n">
         <v>-111.8</v>
       </c>
+      <c r="N14" s="6" t="n">
+        <v>-104.7</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>-105.5</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>-134.6</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v>-120.9</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>-128.5</v>
+      </c>
+      <c r="S14" s="6" t="n">
+        <v>-183.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -7515,6 +8291,24 @@
       </c>
       <c r="M15" s="6" t="n">
         <v>-4.4</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="O15" s="6" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>-6.6</v>
       </c>
     </row>
     <row r="16">
@@ -7557,6 +8351,22 @@
       <c r="M16" s="6" t="n">
         <v>0.6</v>
       </c>
+      <c r="N16" s="6" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>-68.8</v>
+      </c>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="S16" s="6" t="n">
+        <v>-8.699999999999999</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -7600,282 +8410,458 @@
       <c r="M17" s="5" t="n">
         <v>-115.6</v>
       </c>
+      <c r="N17" s="5" t="n">
+        <v>-125.1</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>-178.7</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>-138.5</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>-126</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>-136.1</v>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>-199.1</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Disposal of Custody business</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="6" t="n"/>
+      <c r="R18" s="6" t="n"/>
+      <c r="S18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Profit/(loss) on ordinary activities before taxation</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B19" s="5" t="n">
         <v>5.8</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D19" s="5" t="n">
         <v>-10.4</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E19" s="5" t="n">
         <v>-37.6</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F19" s="5" t="n">
         <v>43.8</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G19" s="5" t="n">
         <v>-50.1</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H19" s="5" t="n">
         <v>-29.3</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>29.8</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="J19" s="5" t="n">
         <v>12.2</v>
       </c>
-      <c r="K18" s="5" t="n">
+      <c r="K19" s="5" t="n">
         <v>-15.4</v>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="L19" s="5" t="n">
         <v>4.9</v>
       </c>
-      <c r="M18" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>-28</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="N19" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>-170.7</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>-155.8</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>-267.3</v>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>-2039.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Tax credit/(charge) on profit/(loss) on ordinary activities</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B20" s="6" t="n">
         <v>1.4</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C20" s="6" t="n">
         <v>-1.5</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D20" s="6" t="n">
         <v>5.9</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E20" s="6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F20" s="6" t="n">
         <v>-1</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G20" s="6" t="n">
         <v>9.4</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H20" s="6" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I20" s="6" t="n">
         <v>-2.2</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="L20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="6" t="n">
+      <c r="M20" s="6" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Profit/(loss) for the year</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>-28.8</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-40.7</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>-19.5</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>-15.4</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>-28</v>
+      <c r="N20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>Profit/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>-40.7</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>-28</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>-170.3</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>-152.8</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="R21" s="5" t="n">
+        <v>-267.5</v>
+      </c>
+      <c r="S21" s="5" t="n">
+        <v>-2040.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
           <t>Other comprehensive income/(loss)</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
-      <c r="M21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Re-measurement losses from defined benefit scheme</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>-0.3</v>
-      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="L22" s="6" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="M22" s="6" t="n">
-        <v>-2.5</v>
-      </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="n"/>
+      <c r="R22" s="6" t="n"/>
+      <c r="S22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
+          <t>Re-measurement losses from defined benefit scheme</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="S23" s="6" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>FX translation gain/(loss) relating to net investment in subsidiary</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B24" s="6" t="n">
         <v>-0.2</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C24" s="6" t="n">
         <v>-0.2</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D24" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E24" s="6" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F24" s="6" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="n"/>
-      <c r="M23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="6" t="n"/>
+      <c r="Q24" s="6" t="n"/>
+      <c r="R24" s="6" t="n"/>
+      <c r="S24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Valuation adjustments on available-for-sale financial investments released from equity</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="6" t="n"/>
+      <c r="Q25" s="6" t="n"/>
+      <c r="R25" s="6" t="n"/>
+      <c r="S25" s="6" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Total comprehensive income/(loss) for the year</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B26" s="5" t="n">
         <v>6.7</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C26" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D26" s="5" t="n">
         <v>-4.7</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E26" s="5" t="n">
         <v>-29.2</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F26" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G26" s="5" t="n">
         <v>-41</v>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H26" s="5" t="n">
         <v>-21.4</v>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="I26" s="5" t="n">
         <v>25.2</v>
       </c>
-      <c r="J24" s="5" t="n">
+      <c r="J26" s="5" t="n">
         <v>7.7</v>
       </c>
-      <c r="K24" s="5" t="n">
+      <c r="K26" s="5" t="n">
         <v>-15.8</v>
       </c>
-      <c r="L24" s="5" t="n">
+      <c r="L26" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="M24" s="5" t="n">
+      <c r="M26" s="5" t="n">
         <v>-30.5</v>
       </c>
-    </row>
-    <row r="26" ht="240" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="N26" s="5" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>-171.9</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>-152.3</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>-270.2</v>
+      </c>
+      <c r="S26" s="5" t="n">
+        <v>-2041.1</v>
+      </c>
+    </row>
+    <row r="28" ht="240" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
 Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863028d4802cdc23dd6552c_2020-mizuho-international-plc-annual-report.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302ac32d1c7376f1f1877_2019-mizuho-international-plc-annual-report.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302c5e1d535ec3306fbee_2018-mizuho-international-plc-annual-report-1.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302d732d1c7376f1f2ad2_2017-mizuho-international-plc-annual-report.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302eda925dd5c1687cecd_2016-mizuho-international-plc-annual-report.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68630302eca4998ff565c8ea_2015-mizuho-international-plc-annual-report.pdf; FY2014: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzEwNDY4NTMyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Official Companies House statutory filing sources for the FY2008-FY2013 extension (HD-075): FY2013: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA4MDE5NTMxMmFkaXF6a2N4/document?format=pdf&amp;download=0; FY2012: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA2NTI2MzY4MGFkaXF6a2N4/document?format=pdf&amp;download=0; FY2011: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA0NDQ4MDc5N2FkaXF6a2N4/document?format=pdf&amp;download=0; FY2010: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzAyMzM2MTY3OWFkaXF6a2N4/document?format=pdf&amp;download=0; FY2009: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MjA0MjM3OTU5NmFkaXF6a2N4/document?format=pdf&amp;download=0; FY2008: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MjAxMDQ0NzA1NmFkaXF6a2N4/document?format=pdf&amp;download=0
 Balance Sheet/P&amp;L/Equity figures are the Consolidated Mizuho International plc Group basis for FY2019-FY2025 (distinct from the Company-only basis also shown in each Annual Report). FY2025/FY2024: Annual Report 2025, Consolidated Statement of Comprehensive Income and Consolidated Statement of Financial Position p.88-89, Consolidated Statement of Changes in Equity p.90-91. FY2023/FY2022: Annual Report 2024, same statements p.86-89. FY2021: Annual Report 2022, Consolidated Statement of Comprehensive Income p.84-85, Consolidated Statement of Financial Position and Consolidated Statement of Changes in Equity p.86, 88. FY2020: Annual Report 2020, Consolidated Statement of Comprehensive Income/Financial Position/Changes in Equity/Cash Flows p.34-39. FY2019: Annual Report 2019, same Consolidated statements p.22-27.
-REPORTING BASIS: FY2019-FY2025 are Consolidated Mizuho International plc Group basis (Group consolidation began FY2019). FY2015-FY2018 are Company-only basis under FRS 102 (restated from UK GAAP as at 1 April 2015 transition date); the Company did not yet prepare group accounts. FY2014 is Company-only, originally-filed UK GAAP (pre-FRS 102), sourced from the Companies House statutory filing rather than Mizuho's own site (see AR/P3 source dict comments) - there is a real ~£0.5m equity break between FY2014 as originally filed and the FRS102-restated FY2015 opening position (see the Statement of Changes in Equity's transition row). None of FY2014-FY2020 include a cash flow statement (FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent publishes consolidated accounts).
-FY2015-FY2018 (Company-only basis): FY2018 Annual Report, Statement of Comprehensive Income p.22, Statement of Financial Position p.23, Statement of Changes in Equity p.24. FY2017 Annual Report, same statements p.15-17. FY2016 Annual Report, same statements p.14-16 (FY2016 report's own FY2015 comparative column is the source for FY2015, restated to FRS 102). FY2014 (originally-filed UK GAAP, Company-only): Companies House 'Full accounts made up to 31 March 2014' filing, Profit and Loss Account p.13, Balance Sheet p.14, Consolidated Statement of Total Recognised Gains and Losses p.15.</t>
+REPORTING BASIS: FY2019-FY2025 are Consolidated Mizuho International plc Group basis (Group consolidation began FY2019). FY2015-FY2018 are Company-only basis under FRS 102 (restated from UK GAAP as at 1 April 2015 transition date); the Company did not yet prepare group accounts. FY2010-FY2014 are Company-only, originally-filed UK GAAP (pre-FRS 102), sourced from the Companies House statutory filing rather than Mizuho's own site (see AR/P3/CH_STATUTORY source dict comments) - there is a real ~£0.5m equity break between FY2014 as originally filed and the FRS102-restated FY2015 opening position (see the Statement of Changes in Equity's transition row). FY2008-FY2009 are a mixed basis dictated by what each year's own filing actually presents: the Balance Sheet is Company-only (matching the FY2010-FY2014 convention) but the Profit and Loss Account is Consolidated (the Company did not present its own P&amp;L those two years, relying on the Companies Act exemption for a subsidiary whose consolidated P&amp;L is presented instead) - Total Equity is identical under either basis for FY2008/FY2009 (the Group/Company difference is confined to derivative and repo gross-up presentation on the asset/liability sides), so this mixed basis does not affect the equity reconciliation ladder. None of FY2008-FY2020 include a cash flow statement (FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent publishes consolidated accounts, per each year's own Annual Report). FY2012's own filing discloses a voluntary accounting policy change made during FY2012, from trade-date to settlement-date accounting for regular-way trading securities transactions; applied retrospectively, it shrank the FY2011 comparative shown in FY2012's own report (Total Assets 29,781.5 -&gt; 27,034.4, largely a reclassification out of 'Other assets') versus FY2011's own originally-filed trade-date figures used for the FY2011 column here (per this project's own-year-filing sourcing rule) - a real, disclosed break between the FY2011 and FY2012 columns, not a transcription error.
+FY2015-FY2018 (Company-only basis): FY2018 Annual Report, Statement of Comprehensive Income p.22, Statement of Financial Position p.23, Statement of Changes in Equity p.24. FY2017 Annual Report, same statements p.15-17. FY2016 Annual Report, same statements p.14-16 (FY2016 report's own FY2015 comparative column is the source for FY2015, restated to FRS 102). FY2014 (originally-filed UK GAAP, Company-only): Companies House 'Full accounts made up to 31 March 2014' filing, Profit and Loss Account p.13, Balance Sheet p.14, Consolidated Statement of Total Recognised Gains and Losses p.15.
+HD-075 (FY2008-FY2013, all Companies House statutory filings, see CH_STATUTORY above): FY2013 'Full accounts made up to 31 March 2013' filing, Profit and Loss Account p.12, Balance Sheet p.13, Statement of Total Recognised Gains and Losses p.14, Equity note (note 26, also source for the FY2012 comparative column) p.45. FY2012 'Full accounts made up to 31 March 2012' filing, Profit and Loss Account p.14, Balance Sheet p.15, Statement of Total Recognised Gains and Losses p.16, Changes in accounting policy note (settlement-date vs trade-date accounting change disclosed against the FY2011 comparative) p.18. FY2011 'Full accounts made up to 31 March 2011' filing (own originally-filed trade-date basis, not FY2012's restated comparative), Profit and Loss Account p.13, Balance Sheet p.14, Statement of Total Recognised Gains and Losses p.15. FY2010 'Full accounts made up to 31 March 2010' filing, Profit and Loss Account p.13, Balance Sheet p.14, Statement of Total Recognised Gains and Losses p.16 (own FY2009 comparative column cross-checked against the FY2009 filing below). FY2009 'Group of companies' accounts made up to 31 March 2009' filing: Company Balance Sheet p.15 (Company-only basis used here, per REPORTING BASIS note above); Consolidated Profit and Loss Account p.12 and Statement of Total Recognised Gains and Losses p.14 (no separate Company P&amp;L presented that year - Companies Act exemption); Equity note (note 28, also source for the FY2008 comparative column and dividend disclosure) p.52. FY2008 'Group of companies' accounts made up to 31 March 2008' filing: Balance Sheet (Company-only) p.16, Consolidated Profit and Loss Account p.13, Statement of Total Recognised Gains and Losses p.15, Called Up Share Capital note 27 p.51, Equity note 28 (share capital movements, dividends paid, actuarial loss, fair value reserve release, and the FY2007 opening position used as the equity ladder's starting row) p.52.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A28:S28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7887,7 +8873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -7909,7 +8895,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Chronological roll-forward, oldest to newest. Consolidated Group basis FY2019 onward; Company-only basis FY2014-FY2018 (see the 'REPORTING BASIS' source note). £m. Equity reconciliation ladder confirmed: every year's own closing balance ties exactly to both the next year's own opening balance and that year's own Balance Sheet Total Equity across all 12 years, with one disclosed exception: a real ~£0.5m break between FY2014's closing position as originally filed (UK GAAP, Companies House) and the FRS102-restated FY2015 opening position shown in the FY2016 Annual Report - the 'FRS 102 transition adjustment' row makes that break explicit rather than silently plugging it. FY2025's Capital injection/Equity contribution/Transfer-to-P&amp;L rows relate to a capital raise and the release of a net dilapidation provision following termination of the Company's sub-lease, per the source's own explanatory note. The FY2017 'Share capital reduction' cancelled MHI's cumulative loss balance (135,000,000 JPY ordinary shares and £111,534,584 ordinary shares were cancelled per the source's own explanatory note).</t>
+          <t>Chronological roll-forward, oldest to newest. Consolidated Group basis FY2019 onward; Company-only basis FY2010-FY2018 (mixed Company-only Balance Sheet / Consolidated P&amp;L basis for FY2008-FY2009 - see the 'REPORTING BASIS' source note; Total Equity is unaffected by that mix, since it nets out on consolidation). £m. Equity reconciliation ladder confirmed: every year's own closing balance ties exactly to both the next year's own opening balance and that year's own Balance Sheet Total Equity across all 18 years (FY2008-FY2025), with one disclosed exception: a real ~£0.5m break between FY2014's closing position as originally filed (UK GAAP, Companies House) and the FRS102-restated FY2015 opening position shown in the FY2016 Annual Report - the 'FRS 102 transition adjustment' row makes that break explicit rather than silently plugging it. FY2025's Capital injection/Equity contribution/Transfer-to-P&amp;L rows relate to a capital raise and the release of a net dilapidation provision following termination of the Company's sub-lease, per the source's own explanatory note. The FY2017 'Share capital reduction' cancelled MHI's cumulative loss balance (135,000,000 JPY ordinary shares and £111,534,584 ordinary shares were cancelled per the source's own explanatory note). HD-075: FY2008-FY2013 fold each year's own separately-disclosed 'Pension reserve' equity component into the 'Profit and loss account' column (Pension reserve left blank, matching the immediately following 'At 1 April 2013' row's own convention) since each year's own primary Balance Sheet shows only one combined 'Profit and loss account' line - the underlying source notes (note 26/28 'Equity') disclose the pension split for readers who want it, but it plays no part in this sheet's own column totals. The FY2008 opening row (1 April 2007) and that year's large £2,057.0m share capital increase, £20.0m dividend paid, and £0.2m fair value reserve release are all sourced from the FY2008 filing's own Equity note (note 28), which also gives the FY2007 opening position used as this ladder's starting point. FY2011's closing row uses that year's own originally-filed figures.</t>
         </is>
       </c>
     </row>
@@ -7953,22 +8939,24 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>At 1 April 2013 (FY2014 opening, originally-filed UK GAAP)</t>
+          <t>At 1 April 2007 (FY2008 opening)</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>2795.3</v>
+        <v>257.6</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>15.6</v>
       </c>
       <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
+      <c r="E4" s="5" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="F4" s="5" t="n">
-        <v>-2385.8</v>
+        <v>243.6</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>425.1</v>
+        <v>516.6</v>
       </c>
     </row>
     <row r="5">
@@ -7978,14 +8966,14 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>45</v>
+        <v>2057</v>
       </c>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n">
-        <v>45</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="6">
@@ -7999,16 +8987,16 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n">
-        <v>-28</v>
+        <v>-2040.7</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-28</v>
+        <v>-2040.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Actuarial loss on defined benefit scheme</t>
+          <t>Dividends paid</t>
         </is>
       </c>
       <c r="B7" s="6" t="n"/>
@@ -8016,252 +9004,238 @@
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n">
-        <v>-2.5</v>
+        <v>-20</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-2.5</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>At 31 March 2014 (FY2014 closing, originally-filed UK GAAP)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>2840.3</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n">
-        <v>-2416.3</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>439.6</v>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Actuarial loss on defined benefit scheme and related deferred tax</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>FRS 102 transition adjustment (1 April 2014) - reclassifies a pension reserve out of the profit and loss account plus a further ~£0.5m net restatement</t>
+          <t>Fair value reserve released</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>At 1 April 2014 (FY2015 opening, FRS 102-restated)</t>
+          <t>At 31 March 2008 (FY2008 closing)</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>2840.3</v>
+        <v>2314.6</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>-14</v>
-      </c>
+      <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-2402.8</v>
+        <v>-1817.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>439.1</v>
+        <v>512.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
+          <t>Increase in paid up share capital</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>111.8</v>
+      </c>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n">
-        <v>4.9</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income/(loss)</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n">
-        <v>-2.4</v>
-      </c>
+      <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="F12" s="6" t="n">
+        <v>-267.5</v>
+      </c>
       <c r="G12" s="6" t="n">
-        <v>-2.4</v>
+        <v>-267.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>At 31 March 2015 (FY2015 closing)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>2840.3</v>
-      </c>
-      <c r="C13" s="5" t="n">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Actuarial loss on defined benefit scheme</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2009 (FY2009 closing)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2426.4</v>
+      </c>
+      <c r="C14" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>-16.4</v>
-      </c>
-      <c r="E13" s="5" t="n">
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="5" t="n">
-        <v>-2397.9</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>441.6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Increase in paid up share capital</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n">
-        <v>35</v>
+      <c r="F14" s="5" t="n">
+        <v>-2087.9</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>354.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
+          <t>Increase in paid up share capital</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>35.9</v>
+      </c>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n">
-        <v>-15.4</v>
-      </c>
+      <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n">
-        <v>-15.4</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income/(loss)</t>
+          <t>Profit for the year</t>
         </is>
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n">
-        <v>-0.4</v>
-      </c>
+      <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
+      <c r="F16" s="6" t="n">
+        <v>35.2</v>
+      </c>
       <c r="G16" s="6" t="n">
-        <v>-0.4</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>At 31 March 2016 (FY2016 closing)</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>2875.3</v>
-      </c>
-      <c r="C17" s="5" t="n">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Actuarial loss on defined benefit scheme</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2010 (FY2010 closing)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2462.3</v>
+      </c>
+      <c r="C18" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>-16.8</v>
-      </c>
-      <c r="E17" s="5" t="n">
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>-2413.3</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>460.8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Increase in paid up share capital</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>267.9</v>
-      </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n">
-        <v>267.9</v>
+      <c r="F18" s="5" t="n">
+        <v>-2056.1</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>421.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Share capital reduction (cancels cumulative loss)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>-2433.3</v>
-      </c>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n">
-        <v>20</v>
-      </c>
+      <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n">
-        <v>2413.3</v>
-      </c>
-      <c r="G19" s="6" t="n"/>
+        <v>-152.8</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-152.8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Profit for the year</t>
+          <t>Actuarial gain on defined benefit scheme</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
@@ -8269,58 +9243,56 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n">
-        <v>12.2</v>
+        <v>0.5</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>12.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Other comprehensive income/(loss)</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n">
-        <v>-4.5</v>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2011 (FY2011 closing, originally-filed trade-date basis)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2462.3</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-2208.4</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>269.5</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>At 31 March 2017 (FY2017 closing)</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>709.9</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>736.4</v>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Increase in paid up share capital</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Profit for the year</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
@@ -8328,260 +9300,244 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n">
-        <v>27.6</v>
+        <v>-170.3</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>27.6</v>
+        <v>-170.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income/(loss)</t>
+          <t>Actuarial loss on defined benefit scheme</t>
         </is>
       </c>
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n">
-        <v>-2.4</v>
-      </c>
+      <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
+      <c r="F24" s="6" t="n">
+        <v>-1.6</v>
+      </c>
       <c r="G24" s="6" t="n">
-        <v>-2.4</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>At 31 March 2018 (FY2018 closing)</t>
+          <t>At 31 March 2012 (FY2012 closing)</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>709.9</v>
+        <v>2712.3</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>-3.7</v>
-      </c>
+      <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>39.8</v>
+        <v>-2380.3</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>761.6</v>
+        <v>347.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
+          <t>Increase in paid up share capital</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>83</v>
+      </c>
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n">
-        <v>-19.5</v>
-      </c>
+      <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n">
-        <v>-19.5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income/(loss)</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n">
-        <v>-1.9</v>
-      </c>
+      <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
+      <c r="F27" s="6" t="n">
+        <v>-3</v>
+      </c>
       <c r="G27" s="6" t="n">
-        <v>-1.9</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>At 31 March 2019 (FY2019 closing)</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>709.9</v>
-      </c>
-      <c r="C28" s="5" t="n">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Actuarial loss on defined benefit scheme</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>At 1 April 2013 (FY2014 opening, originally-filed UK GAAP)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2795.3</v>
+      </c>
+      <c r="C29" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="D28" s="5" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>740.2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n">
-        <v>-40.7</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>-40.7</v>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n">
+        <v>-2385.8</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>425.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income/(loss)</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
+          <t>Increase in paid up share capital</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>45</v>
+      </c>
       <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n">
-        <v>-0.3</v>
-      </c>
+      <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n"/>
       <c r="G30" s="6" t="n">
-        <v>-0.3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>At 31 March 2020 (FY2020 closing)</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>709.9</v>
-      </c>
-      <c r="C31" s="5" t="n">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n">
+        <v>-28</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Actuarial loss on defined benefit scheme</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2014 (FY2014 closing, originally-filed UK GAAP)</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2840.3</v>
+      </c>
+      <c r="C33" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="D31" s="5" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>-20.4</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>699.2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>At 1 April 2020 (FY2021 opening)</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>709.9</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>-20.4</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>699.2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>42.8</v>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n">
+        <v>-2416.3</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>439.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income/(loss)</t>
+          <t>FRS 102 transition adjustment (1 April 2014) - reclassifies a pension reserve out of the profit and loss account plus a further ~£0.5m net restatement</t>
         </is>
       </c>
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="F34" s="6" t="n"/>
+      <c r="D34" s="6" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n">
+        <v>13.5</v>
+      </c>
       <c r="G34" s="6" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>At 31 March 2021 (FY2021 closing)</t>
+          <t>At 1 April 2014 (FY2015 opening, FRS 102-restated)</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>709.9</v>
+        <v>2840.3</v>
       </c>
       <c r="C35" s="5" t="n">
         <v>15.6</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>-5.9</v>
+        <v>-14</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>22.4</v>
+        <v>-2402.8</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>741.6</v>
+        <v>439.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
+          <t>Profit for the year</t>
         </is>
       </c>
       <c r="B36" s="6" t="n"/>
@@ -8589,10 +9545,10 @@
       <c r="D36" s="6" t="n"/>
       <c r="E36" s="6" t="n"/>
       <c r="F36" s="6" t="n">
-        <v>-28.8</v>
+        <v>4.9</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>-28.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="37">
@@ -8604,162 +9560,150 @@
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="6" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>-0.1</v>
-      </c>
+        <v>-2.4</v>
+      </c>
+      <c r="E37" s="6" t="n"/>
       <c r="F37" s="6" t="n"/>
       <c r="G37" s="6" t="n">
-        <v>-0.4</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>At 31 March 2022 (FY2022 closing)</t>
+          <t>At 31 March 2015 (FY2015 closing)</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>709.9</v>
+        <v>2840.3</v>
       </c>
       <c r="C38" s="5" t="n">
         <v>15.6</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>-6.2</v>
+        <v>-16.4</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-6.4</v>
+        <v>-2397.9</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>712.4</v>
+        <v>441.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n"/>
+          <t>Increase in paid up share capital</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>35</v>
+      </c>
       <c r="C39" s="6" t="n"/>
       <c r="D39" s="6" t="n"/>
       <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="n">
-        <v>-4.5</v>
-      </c>
+      <c r="F39" s="6" t="n"/>
       <c r="G39" s="6" t="n">
-        <v>-4.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income/(loss)</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n">
+        <v>-15.4</v>
+      </c>
       <c r="G40" s="6" t="n">
-        <v>-0.2</v>
+        <v>-15.4</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>At 31 March 2023 (FY2023 closing)</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>709.9</v>
-      </c>
-      <c r="C41" s="5" t="n">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2016 (FY2016 closing)</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>2875.3</v>
+      </c>
+      <c r="C42" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="D41" s="5" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>707.7</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Profit for the year</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G42" s="6" t="n">
-        <v>13.5</v>
+      <c r="D42" s="5" t="n">
+        <v>-16.8</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>-2413.3</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>460.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Other comprehensive income/(loss)</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n"/>
+          <t>Increase in paid up share capital</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>267.9</v>
+      </c>
       <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E43" s="6" t="n">
-        <v>-0.2</v>
-      </c>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
       <c r="F43" s="6" t="n"/>
       <c r="G43" s="6" t="n">
-        <v>-0.5</v>
+        <v>267.9</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>At 31 March 2024 (FY2024 closing)</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>709.9</v>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>720.7</v>
-      </c>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Share capital reduction (cancels cumulative loss)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>-2433.3</v>
+      </c>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n">
+        <v>2413.3</v>
+      </c>
+      <c r="G44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -8772,62 +9716,70 @@
       <c r="D45" s="6" t="n"/>
       <c r="E45" s="6" t="n"/>
       <c r="F45" s="6" t="n">
-        <v>7.2</v>
+        <v>12.2</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>7.2</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Capital injection</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="n">
-        <v>45</v>
-      </c>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n"/>
       <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
+      <c r="D46" s="6" t="n">
+        <v>-4.5</v>
+      </c>
       <c r="E46" s="6" t="n"/>
       <c r="F46" s="6" t="n"/>
       <c r="G46" s="6" t="n">
-        <v>45</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Equity contribution</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="6" t="n">
-        <v>1.1</v>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2017 (FY2017 closing)</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>736.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Transfer to profit and loss account</t>
+          <t>Profit for the year</t>
         </is>
       </c>
       <c r="B48" s="6" t="n"/>
       <c r="C48" s="6" t="n"/>
       <c r="D48" s="6" t="n"/>
-      <c r="E48" s="6" t="n">
-        <v>-1.1</v>
-      </c>
+      <c r="E48" s="6" t="n"/>
       <c r="F48" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G48" s="6" t="n"/>
+        <v>27.6</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>27.6</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -8838,55 +9790,552 @@
       <c r="B49" s="6" t="n"/>
       <c r="C49" s="6" t="n"/>
       <c r="D49" s="6" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="E49" s="6" t="n">
-        <v>-0.2</v>
-      </c>
+        <v>-2.4</v>
+      </c>
+      <c r="E49" s="6" t="n"/>
       <c r="F49" s="6" t="n"/>
       <c r="G49" s="6" t="n">
-        <v>-0.5</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>At 31 March 2025 (FY2025 closing)</t>
+          <t>At 31 March 2018 (FY2018 closing)</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>754.9</v>
+        <v>709.9</v>
       </c>
       <c r="C50" s="5" t="n">
         <v>15.6</v>
       </c>
       <c r="D50" s="5" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>761.6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>-19.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="n">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2019 (FY2019 closing)</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>740.2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="n">
+        <v>-40.7</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>-40.7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="n"/>
+      <c r="G55" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2020 (FY2020 closing)</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>699.2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>At 1 April 2020 (FY2021 opening)</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>699.2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F59" s="6" t="n"/>
+      <c r="G59" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2021 (FY2021 closing)</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>741.6</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>-28.8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F62" s="6" t="n"/>
+      <c r="G62" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2022 (FY2022 closing)</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>712.4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F65" s="6" t="n"/>
+      <c r="G65" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2023 (FY2023 closing)</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>707.7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F68" s="6" t="n"/>
+      <c r="G68" s="6" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2024 (FY2024 closing)</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>720.7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Capital injection</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="n"/>
+      <c r="G71" s="6" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Equity contribution</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F72" s="6" t="n"/>
+      <c r="G72" s="6" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Transfer to profit and loss account</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F74" s="6" t="n"/>
+      <c r="G74" s="6" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>At 31 March 2025 (FY2025 closing)</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>754.9</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D75" s="5" t="n">
         <v>-7.1</v>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="E75" s="5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F75" s="5" t="n">
         <v>10.9</v>
       </c>
-      <c r="G50" s="5" t="n">
+      <c r="G75" s="5" t="n">
         <v>773.5</v>
       </c>
     </row>
-    <row r="52" ht="150" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="77" ht="150" customHeight="1">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
 Official sources — Mizuho International plc Annual Reports: FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863028d4802cdc23dd6552c_2020-mizuho-international-plc-annual-report.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302ac32d1c7376f1f1877_2019-mizuho-international-plc-annual-report.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302c5e1d535ec3306fbee_2018-mizuho-international-plc-annual-report-1.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302d732d1c7376f1f2ad2_2017-mizuho-international-plc-annual-report.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302eda925dd5c1687cecd_2016-mizuho-international-plc-annual-report.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68630302eca4998ff565c8ea_2015-mizuho-international-plc-annual-report.pdf; FY2014: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzEwNDY4NTMyOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Official Companies House statutory filing sources for the FY2008-FY2013 extension (HD-075): FY2013: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA4MDE5NTMxMmFkaXF6a2N4/document?format=pdf&amp;download=0; FY2012: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA2NTI2MzY4MGFkaXF6a2N4/document?format=pdf&amp;download=0; FY2011: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA0NDQ4MDc5N2FkaXF6a2N4/document?format=pdf&amp;download=0; FY2010: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzAyMzM2MTY3OWFkaXF6a2N4/document?format=pdf&amp;download=0; FY2009: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MjA0MjM3OTU5NmFkaXF6a2N4/document?format=pdf&amp;download=0; FY2008: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MjAxMDQ0NzA1NmFkaXF6a2N4/document?format=pdf&amp;download=0
 Balance Sheet/P&amp;L/Equity figures are the Consolidated Mizuho International plc Group basis for FY2019-FY2025 (distinct from the Company-only basis also shown in each Annual Report). FY2025/FY2024: Annual Report 2025, Consolidated Statement of Comprehensive Income and Consolidated Statement of Financial Position p.88-89, Consolidated Statement of Changes in Equity p.90-91. FY2023/FY2022: Annual Report 2024, same statements p.86-89. FY2021: Annual Report 2022, Consolidated Statement of Comprehensive Income p.84-85, Consolidated Statement of Financial Position and Consolidated Statement of Changes in Equity p.86, 88. FY2020: Annual Report 2020, Consolidated Statement of Comprehensive Income/Financial Position/Changes in Equity/Cash Flows p.34-39. FY2019: Annual Report 2019, same Consolidated statements p.22-27.
-REPORTING BASIS: FY2019-FY2025 are Consolidated Mizuho International plc Group basis (Group consolidation began FY2019). FY2015-FY2018 are Company-only basis under FRS 102 (restated from UK GAAP as at 1 April 2015 transition date); the Company did not yet prepare group accounts. FY2014 is Company-only, originally-filed UK GAAP (pre-FRS 102), sourced from the Companies House statutory filing rather than Mizuho's own site (see AR/P3 source dict comments) - there is a real ~£0.5m equity break between FY2014 as originally filed and the FRS102-restated FY2015 opening position (see the Statement of Changes in Equity's transition row). None of FY2014-FY2020 include a cash flow statement (FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent publishes consolidated accounts).
-FY2015-FY2018 (Company-only basis): FY2018 Annual Report, Statement of Comprehensive Income p.22, Statement of Financial Position p.23, Statement of Changes in Equity p.24. FY2017 Annual Report, same statements p.15-17. FY2016 Annual Report, same statements p.14-16 (FY2016 report's own FY2015 comparative column is the source for FY2015, restated to FRS 102). FY2014 (originally-filed UK GAAP, Company-only): Companies House 'Full accounts made up to 31 March 2014' filing, Profit and Loss Account p.13, Balance Sheet p.14, Consolidated Statement of Total Recognised Gains and Losses p.15.</t>
+REPORTING BASIS: FY2019-FY2025 are Consolidated Mizuho International plc Group basis (Group consolidation began FY2019). FY2015-FY2018 are Company-only basis under FRS 102 (restated from UK GAAP as at 1 April 2015 transition date); the Company did not yet prepare group accounts. FY2010-FY2014 are Company-only, originally-filed UK GAAP (pre-FRS 102), sourced from the Companies House statutory filing rather than Mizuho's own site (see AR/P3/CH_STATUTORY source dict comments) - there is a real ~£0.5m equity break between FY2014 as originally filed and the FRS102-restated FY2015 opening position (see the Statement of Changes in Equity's transition row). FY2008-FY2009 are a mixed basis dictated by what each year's own filing actually presents: the Balance Sheet is Company-only (matching the FY2010-FY2014 convention) but the Profit and Loss Account is Consolidated (the Company did not present its own P&amp;L those two years, relying on the Companies Act exemption for a subsidiary whose consolidated P&amp;L is presented instead) - Total Equity is identical under either basis for FY2008/FY2009 (the Group/Company difference is confined to derivative and repo gross-up presentation on the asset/liability sides), so this mixed basis does not affect the equity reconciliation ladder. None of FY2008-FY2020 include a cash flow statement (FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent publishes consolidated accounts, per each year's own Annual Report). FY2012's own filing discloses a voluntary accounting policy change made during FY2012, from trade-date to settlement-date accounting for regular-way trading securities transactions; applied retrospectively, it shrank the FY2011 comparative shown in FY2012's own report (Total Assets 29,781.5 -&gt; 27,034.4, largely a reclassification out of 'Other assets') versus FY2011's own originally-filed trade-date figures used for the FY2011 column here (per this project's own-year-filing sourcing rule) - a real, disclosed break between the FY2011 and FY2012 columns, not a transcription error.
+FY2015-FY2018 (Company-only basis): FY2018 Annual Report, Statement of Comprehensive Income p.22, Statement of Financial Position p.23, Statement of Changes in Equity p.24. FY2017 Annual Report, same statements p.15-17. FY2016 Annual Report, same statements p.14-16 (FY2016 report's own FY2015 comparative column is the source for FY2015, restated to FRS 102). FY2014 (originally-filed UK GAAP, Company-only): Companies House 'Full accounts made up to 31 March 2014' filing, Profit and Loss Account p.13, Balance Sheet p.14, Consolidated Statement of Total Recognised Gains and Losses p.15.
+HD-075 (FY2008-FY2013, all Companies House statutory filings, see CH_STATUTORY above): FY2013 'Full accounts made up to 31 March 2013' filing, Profit and Loss Account p.12, Balance Sheet p.13, Statement of Total Recognised Gains and Losses p.14, Equity note (note 26, also source for the FY2012 comparative column) p.45. FY2012 'Full accounts made up to 31 March 2012' filing, Profit and Loss Account p.14, Balance Sheet p.15, Statement of Total Recognised Gains and Losses p.16, Changes in accounting policy note (settlement-date vs trade-date accounting change disclosed against the FY2011 comparative) p.18. FY2011 'Full accounts made up to 31 March 2011' filing (own originally-filed trade-date basis, not FY2012's restated comparative), Profit and Loss Account p.13, Balance Sheet p.14, Statement of Total Recognised Gains and Losses p.15. FY2010 'Full accounts made up to 31 March 2010' filing, Profit and Loss Account p.13, Balance Sheet p.14, Statement of Total Recognised Gains and Losses p.16 (own FY2009 comparative column cross-checked against the FY2009 filing below). FY2009 'Group of companies' accounts made up to 31 March 2009' filing: Company Balance Sheet p.15 (Company-only basis used here, per REPORTING BASIS note above); Consolidated Profit and Loss Account p.12 and Statement of Total Recognised Gains and Losses p.14 (no separate Company P&amp;L presented that year - Companies Act exemption); Equity note (note 28, also source for the FY2008 comparative column and dividend disclosure) p.52. FY2008 'Group of companies' accounts made up to 31 March 2008' filing: Balance Sheet (Company-only) p.16, Consolidated Profit and Loss Account p.13, Statement of Total Recognised Gains and Losses p.15, Called Up Share Capital note 27 p.51, Equity note 28 (share capital movements, dividends paid, actuarial loss, fair value reserve release, and the FY2007 opening position used as the equity ladder's starting row) p.52.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A77:G77"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8898,7 +10347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -8914,6 +10363,12 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8926,7 +10381,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Group basis, £ millions. FY2014-FY2020 are blank (not zero): none of those years' Annual Reports include a cash flow statement, each invoking the FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent (Mizuho Financial Group, Inc.) publishes consolidated financial statements including the Company - the same exemption basis as FY2021-FY2025's ENTITY NOTE.</t>
+          <t>Consolidated Group basis, £ millions. FY2008-FY2020 are blank (not zero): none of those years' Annual Reports/statutory filings include a cash flow statement, each invoking the FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent (Mizuho Financial Group, Inc.) publishes consolidated financial statements including the Company - the same exemption basis as FY2021-FY2025's ENTITY NOTE. HD-075 confirmed the exemption is invoked explicitly in each of the FY2008-FY2013 Companies House filings too.</t>
         </is>
       </c>
     </row>
@@ -8994,6 +10449,36 @@
       <c r="M3" s="4" t="inlineStr">
         <is>
           <t>FY2014 (£m)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>FY2013 (£m)</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>FY2012 (£m)</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>FY2011 (£m)</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>FY2010 (£m)</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>FY2009 (£m)</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>FY2008 (£m)</t>
         </is>
       </c>
     </row>
@@ -9015,6 +10500,12 @@
       <c r="K4" s="6" t="n"/>
       <c r="L4" s="6" t="n"/>
       <c r="M4" s="6" t="n"/>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="6" t="n"/>
+      <c r="R4" s="6" t="n"/>
+      <c r="S4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -9044,6 +10535,12 @@
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
       <c r="M5" s="6" t="n"/>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n"/>
+      <c r="Q5" s="6" t="n"/>
+      <c r="R5" s="6" t="n"/>
+      <c r="S5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -9073,6 +10570,12 @@
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="n"/>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -9102,6 +10605,12 @@
       <c r="K7" s="6" t="n"/>
       <c r="L7" s="6" t="n"/>
       <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -9131,6 +10640,12 @@
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="6" t="n"/>
       <c r="M8" s="6" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="6" t="n"/>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -9160,6 +10675,12 @@
       <c r="K9" s="6" t="n"/>
       <c r="L9" s="6" t="n"/>
       <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="6" t="n"/>
+      <c r="R9" s="6" t="n"/>
+      <c r="S9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -9189,6 +10710,12 @@
       <c r="K10" s="6" t="n"/>
       <c r="L10" s="6" t="n"/>
       <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="6" t="n"/>
+      <c r="Q10" s="6" t="n"/>
+      <c r="R10" s="6" t="n"/>
+      <c r="S10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -9218,6 +10745,12 @@
       <c r="K11" s="6" t="n"/>
       <c r="L11" s="6" t="n"/>
       <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
+      <c r="R11" s="6" t="n"/>
+      <c r="S11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -9247,6 +10780,12 @@
       <c r="K12" s="6" t="n"/>
       <c r="L12" s="6" t="n"/>
       <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="n"/>
+      <c r="R12" s="6" t="n"/>
+      <c r="S12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -9276,6 +10815,12 @@
       <c r="K13" s="6" t="n"/>
       <c r="L13" s="6" t="n"/>
       <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="6" t="n"/>
+      <c r="R13" s="6" t="n"/>
+      <c r="S13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -9305,6 +10850,12 @@
       <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -9324,6 +10875,12 @@
       <c r="K15" s="6" t="n"/>
       <c r="L15" s="6" t="n"/>
       <c r="M15" s="6" t="n"/>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="6" t="n"/>
+      <c r="R15" s="6" t="n"/>
+      <c r="S15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -9353,6 +10910,12 @@
       <c r="K16" s="6" t="n"/>
       <c r="L16" s="6" t="n"/>
       <c r="M16" s="6" t="n"/>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="6" t="n"/>
+      <c r="R16" s="6" t="n"/>
+      <c r="S16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -9382,6 +10945,12 @@
       <c r="K17" s="6" t="n"/>
       <c r="L17" s="6" t="n"/>
       <c r="M17" s="6" t="n"/>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="6" t="n"/>
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -9411,6 +10980,12 @@
       <c r="K18" s="6" t="n"/>
       <c r="L18" s="6" t="n"/>
       <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="6" t="n"/>
+      <c r="R18" s="6" t="n"/>
+      <c r="S18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -9440,6 +11015,12 @@
       <c r="K19" s="6" t="n"/>
       <c r="L19" s="6" t="n"/>
       <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="n"/>
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -9469,6 +11050,12 @@
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -9488,6 +11075,12 @@
       <c r="K21" s="6" t="n"/>
       <c r="L21" s="6" t="n"/>
       <c r="M21" s="6" t="n"/>
+      <c r="N21" s="6" t="n"/>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="6" t="n"/>
+      <c r="R21" s="6" t="n"/>
+      <c r="S21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -9517,6 +11110,12 @@
       <c r="K22" s="6" t="n"/>
       <c r="L22" s="6" t="n"/>
       <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="n"/>
+      <c r="R22" s="6" t="n"/>
+      <c r="S22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -9538,6 +11137,12 @@
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="6" t="n"/>
       <c r="M23" s="6" t="n"/>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="6" t="n"/>
+      <c r="R23" s="6" t="n"/>
+      <c r="S23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -9559,6 +11164,12 @@
       <c r="K24" s="6" t="n"/>
       <c r="L24" s="6" t="n"/>
       <c r="M24" s="6" t="n"/>
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="6" t="n"/>
+      <c r="Q24" s="6" t="n"/>
+      <c r="R24" s="6" t="n"/>
+      <c r="S24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -9588,6 +11199,12 @@
       <c r="K25" s="5" t="n"/>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="5" t="n"/>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -9617,6 +11234,12 @@
       <c r="K26" s="5" t="n"/>
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -9646,6 +11269,12 @@
       <c r="K27" s="5" t="n"/>
       <c r="L27" s="5" t="n"/>
       <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="5" t="n"/>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -9675,6 +11304,12 @@
       <c r="K28" s="5" t="n"/>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+      <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -9704,6 +11339,12 @@
       <c r="K29" s="5" t="n"/>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
+      <c r="Q29" s="5" t="n"/>
+      <c r="R29" s="5" t="n"/>
+      <c r="S29" s="5" t="n"/>
     </row>
     <row r="31" ht="240" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
@@ -9715,7 +11356,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A31:S31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
+++ b/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
@@ -1622,6 +1622,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5100,7 +5101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -5116,7 +5117,6 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5199,11 +5199,6 @@
           <t>FY2015</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -5271,7 +5266,6 @@
           <t>1.87%</t>
         </is>
       </c>
-      <c r="N4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -5290,8 +5284,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="A7:N7"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A7:M7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5303,7 +5297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -5316,10 +5310,6 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5387,26 +5377,6 @@
           <t>FY2018</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -5459,10 +5429,6 @@
           <t>396%</t>
         </is>
       </c>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
-      <c r="N4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -5481,8 +5447,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="A7:N7"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A7:J7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5494,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -5503,14 +5469,6 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5558,46 +5516,6 @@
           <t>FY2022</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -5630,14 +5548,6 @@
           <t>177.71%</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
-      <c r="N4" s="6" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -5656,8 +5566,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="A7:N7"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5780,24 +5690,77 @@
           <t>MREL Ratio</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
-      <c r="N4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: MREL ratio was not numerically disclosed in any FY2014-FY2025 official annual/Pillar 3 report checked.</t>
+          <t>Note: MREL ratio is not numerically disclosed in any Mizuho International plc annual report or Pillar 3 disclosure. RE-ESTABLISHED WITH A CONTROL 2026-09-18 rather than carried forward - the previous note asserted this for FY2014-FY2025 and was already out of date, since the workbook carries FY2026. Whole-document search of the two newest editions, both text-native and downloaded fresh (%PDF-, application/pdf): the FY2026 consolidated Pillar 3 (217,429 characters) returns ZERO hits for 'MREL', 'minimum requirement for own funds' and 'TLAC', against 145 hits for 'capital', 231 for 'ratio' and 10 for 'own funds' in the same extraction; the FY2025 edition (224,343 characters) returns the same three zeros against 152 and 228. So the zero is a fact about the documents, not a failure of the search. The FY2026 Annual Report (696,912 characters) likewise returns zero for all three.
+WHAT THE DOCUMENTS DO SAY, which is consistent with there being nothing to find. The FY2026 Pillar 3 reproduces the PRA's 'UK CCA: Main features of regulatory own funds instruments and eligible liabilities instruments' template - i.e. the template that WOULD carry an eligible-liabilities instrument if MHI had one - and its only instrument is ordinary share capital, with row 34a 'Type of subordination (only for eligible liabilities)' printed 'n/a'. The FY2026 Annual Report states that the Group 'continues to participate actively in Mizuho Financial Group's recovery and resolution planning', i.e. resolution is planned at the Japanese parent level. That is context, not proof of a scope exclusion, and it is recorded as context: what is established here is that MHI publishes no MREL ratio, not why.</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T35"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -11110,7 +11073,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Consolidated Group basis, £ millions. FY2008-FY2020 are blank (not zero): none of those years' Annual Reports/statutory filings include a cash flow statement, each invoking the FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent (Mizuho Financial Group, Inc.) publishes consolidated financial statements including the Company - the same exemption basis as FY2021-FY2025's ENTITY NOTE. HD-075 confirmed the exemption is invoked explicitly in each of the FY2008-FY2013 Companies House filings too.</t>
+          <t>Consolidated Group basis, £ millions. FY2008-FY2020 carry a statement rather than figures (and are certainly not zero): none of those years' Annual Reports/statutory filings include a cash flow statement, each invoking the FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent (Mizuho Financial Group, Inc.) publishes consolidated financial statements including the Company - the same exemption basis as FY2021-FY2025's ENTITY NOTE. HD-075 confirmed the exemption is invoked explicitly in each of the FY2008-FY2013 Companies House filings too.</t>
         </is>
       </c>
     </row>
@@ -11217,9 +11180,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Operating activities</t>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>No statement of cash flows prepared - FRS 1 / FRS 102 exemption (see note below)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -11228,44 +11191,84 @@
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
-      <c r="N4" s="6" t="n"/>
-      <c r="O4" s="6" t="n"/>
-      <c r="P4" s="6" t="n"/>
-      <c r="Q4" s="6" t="n"/>
-      <c r="R4" s="6" t="n"/>
-      <c r="S4" s="6" t="n"/>
-      <c r="T4" s="6" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no statement of cash flows prepared (FRS 1/FRS 102 exemption)</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no statement of cash flows prepared (FRS 1/FRS 102 exemption)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no statement of cash flows prepared (FRS 1/FRS 102 exemption)</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no statement of cash flows prepared (FRS 1/FRS 102 exemption)</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no statement of cash flows prepared (FRS 1/FRS 102 exemption)</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no statement of cash flows prepared (FRS 1/FRS 102 exemption)</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no statement of cash flows prepared (FRS 1/FRS 102 exemption)</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no statement of cash flows prepared (FRS 1/FRS 102 exemption)</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no statement of cash flows prepared (FRS 1/FRS 102 exemption)</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no statement of cash flows prepared (FRS 1/FRS 102 exemption)</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no statement of cash flows prepared (FRS 1/FRS 102 exemption)</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no statement of cash flows prepared (FRS 1/FRS 102 exemption)</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>Not published - no statement of cash flows prepared (FRS 1/FRS 102 exemption)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Profit / (loss) before tax</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>-37.6</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>43.8</v>
-      </c>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Operating activities</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
       <c r="I5" s="6" t="n"/>
       <c r="J5" s="6" t="n"/>
@@ -11283,26 +11286,26 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Non-cash items included in profit / (loss) before tax</t>
+          <t>Profit / (loss) before tax</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>-33</v>
+        <v>20.5</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>-30</v>
+        <v>5.8</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>-23</v>
+        <v>15</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>-6.3</v>
+        <v>-10.4</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>12.6</v>
+        <v>-37.6</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>23.3</v>
+        <v>43.8</v>
       </c>
       <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n"/>
@@ -11321,26 +11324,26 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Provision for liabilities</t>
+          <t>Non-cash items included in profit / (loss) before tax</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>7.5</v>
+        <v>-33</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.1</v>
+        <v>-30</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.9</v>
+        <v>-23</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.9</v>
+        <v>-6.3</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.2</v>
+        <v>12.6</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.4</v>
+        <v>23.3</v>
       </c>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="6" t="n"/>
@@ -11359,26 +11362,26 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Movement in Other Comprehensive Income</t>
+          <t>Provision for liabilities</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>-0.3</v>
+        <v>7.5</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="D8" s="6" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G8" s="6" t="n">
         <v>-0.4</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>-0.5</v>
       </c>
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="6" t="n"/>
@@ -11397,26 +11400,26 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Change in operating assets</t>
+          <t>Movement in Other Comprehensive Income</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>-785.1</v>
+        <v>-0.3</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>846.1</v>
+        <v>-0.5</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2479.7</v>
+        <v>-0.4</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-5424.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-3613</v>
+        <v>-0.4</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>6374.7</v>
+        <v>-0.5</v>
       </c>
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="6" t="n"/>
@@ -11435,26 +11438,26 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Change in operating liabilities</t>
+          <t>Change in operating assets</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>1171.5</v>
+        <v>-785.1</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>-938.8</v>
+        <v>846.1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>-2313.4</v>
+        <v>2479.7</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5456.5</v>
+        <v>-5424.2</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>4012.7</v>
+        <v>-3613</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-6952.2</v>
+        <v>6374.7</v>
       </c>
       <c r="H10" s="6" t="n"/>
       <c r="I10" s="6" t="n"/>
@@ -11473,26 +11476,26 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Interest paid</t>
+          <t>Change in operating liabilities</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>-67.5</v>
+        <v>1171.5</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>-93.3</v>
+        <v>-938.8</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>-92.7</v>
+        <v>-2313.4</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>-0.1</v>
+        <v>5456.5</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.2</v>
+        <v>4012.7</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-1.3</v>
+        <v>-6952.2</v>
       </c>
       <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n"/>
@@ -11511,26 +11514,26 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Interest received</t>
+          <t>Interest paid</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>100.9</v>
+        <v>-67.5</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>124.2</v>
+        <v>-93.3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>139.8</v>
+        <v>-92.7</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>11</v>
+        <v>-0.1</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>14.4</v>
+        <v>-0.2</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>16.4</v>
+        <v>-1.3</v>
       </c>
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
@@ -11549,26 +11552,26 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Tax (paid) / received</t>
+          <t>Interest received</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3.2</v>
+        <v>100.9</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-6.1</v>
+        <v>124.2</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>12.6</v>
+        <v>139.8</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-2</v>
+        <v>11</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-3.4</v>
+        <v>14.4</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>10.5</v>
+        <v>16.4</v>
       </c>
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
@@ -11585,93 +11588,93 @@
       <c r="T13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Net cash flows from operating activities</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>417.7</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>-92.5</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>216.7</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>384.9</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>-485.7</v>
-      </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="5" t="n"/>
-      <c r="T14" s="5" t="n"/>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Tax (paid) / received</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="6" t="n"/>
+      <c r="R14" s="6" t="n"/>
+      <c r="S14" s="6" t="n"/>
+      <c r="T14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>Net cash flows from operating activities</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>417.7</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-92.5</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>216.7</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>384.9</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>-485.7</v>
+      </c>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
           <t>Investing activities</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
-      <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="6" t="n"/>
-      <c r="R15" s="6" t="n"/>
-      <c r="S15" s="6" t="n"/>
-      <c r="T15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Net investment in shares in group undertakings</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>-0.1</v>
-      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n"/>
@@ -11689,26 +11692,26 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Dividends from investment in shares in group undertakings</t>
+          <t>Net investment in shares in group undertakings</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.5</v>
+        <v>-5.8</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.4</v>
+        <v>-1.4</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.7</v>
+        <v>-2</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
@@ -11727,17 +11730,27 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Sale of subsidiary (net of cash disposed)</t>
+          <t>Dividends from investment in shares in group undertakings</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.4</v>
+      </c>
       <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n"/>
@@ -11755,11 +11768,11 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Purchase of subsidiary (net of cash acquired)</t>
+          <t>Sale of subsidiary (net of cash disposed)</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>-38.7</v>
+        <v>15.4</v>
       </c>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
@@ -11783,27 +11796,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Purchase of intangible assets</t>
+          <t>Purchase of subsidiary (net of cash acquired)</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>-51.4</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>-43.8</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>-27.2</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>-28.7</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>-25.3</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>-21.8</v>
-      </c>
+        <v>-38.7</v>
+      </c>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="6" t="n"/>
@@ -11821,26 +11824,26 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Purchase of tangible assets</t>
+          <t>Purchase of intangible assets</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>-2.4</v>
+        <v>-51.4</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>-5.2</v>
+        <v>-43.8</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>-5.8</v>
+        <v>-27.2</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>-2.7</v>
+        <v>-28.7</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-6.4</v>
+        <v>-25.3</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-3.6</v>
+        <v>-21.8</v>
       </c>
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="6" t="n"/>
@@ -11857,78 +11860,88 @@
       <c r="T21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Net cash flows used in investing activities</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>-82.40000000000001</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>-50</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>-32.9</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>-31.6</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>-33</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>-25.1</v>
-      </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n"/>
-      <c r="T22" s="5" t="n"/>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Purchase of tangible assets</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="n"/>
+      <c r="R22" s="6" t="n"/>
+      <c r="S22" s="6" t="n"/>
+      <c r="T22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>Net cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>-82.40000000000001</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-50</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-32.9</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-31.6</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-33</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
           <t>Financing activities</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="n"/>
-      <c r="M23" s="6" t="n"/>
-      <c r="N23" s="6" t="n"/>
-      <c r="O23" s="6" t="n"/>
-      <c r="P23" s="6" t="n"/>
-      <c r="Q23" s="6" t="n"/>
-      <c r="R23" s="6" t="n"/>
-      <c r="S23" s="6" t="n"/>
-      <c r="T23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Proceeds from issuance of debt securities</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>738.1</v>
-      </c>
+      <c r="B24" s="6" t="n"/>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
@@ -11951,11 +11964,11 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Payment on redemption of debt securities in issue</t>
+          <t>Proceeds from issuance of debt securities</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>-1029.3</v>
+        <v>738.1</v>
       </c>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
@@ -11979,25 +11992,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Net repayment from debt securities in issue</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n">
-        <v>-101.5</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>-221.2</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>-139.6</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>-87.8</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>75.59999999999999</v>
-      </c>
+          <t>Payment on redemption of debt securities in issue</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>-1029.3</v>
+      </c>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
       <c r="H26" s="6" t="n"/>
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
@@ -12015,17 +12020,25 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Net repayment of subordinated liabilities</t>
+          <t>Net repayment from debt securities in issue</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
+      <c r="C27" s="6" t="n">
+        <v>-101.5</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>-221.2</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>-139.6</v>
+      </c>
       <c r="F27" s="6" t="n">
-        <v>-45</v>
-      </c>
-      <c r="G27" s="6" t="n"/>
+        <v>-87.8</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>75.59999999999999</v>
+      </c>
       <c r="H27" s="6" t="n"/>
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
@@ -12043,18 +12056,16 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Proceeds from the issuance of equity</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>45</v>
-      </c>
+          <t>Net repayment of subordinated liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
       <c r="D28" s="6" t="n"/>
       <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
+      <c r="F28" s="6" t="n">
+        <v>-45</v>
+      </c>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="6" t="n"/>
       <c r="I28" s="6" t="n"/>
@@ -12071,66 +12082,58 @@
       <c r="T28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Net cash flows from / (used in) financing activities</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>-236.2</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>-56.5</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>-221.2</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>-139.6</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>-132.8</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-      <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="5" t="n"/>
-      <c r="R29" s="5" t="n"/>
-      <c r="S29" s="5" t="n"/>
-      <c r="T29" s="5" t="n"/>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Proceeds from the issuance of equity</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="n"/>
+      <c r="N29" s="6" t="n"/>
+      <c r="O29" s="6" t="n"/>
+      <c r="P29" s="6" t="n"/>
+      <c r="Q29" s="6" t="n"/>
+      <c r="R29" s="6" t="n"/>
+      <c r="S29" s="6" t="n"/>
+      <c r="T29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Net (decrease) / increase in cash and cash equivalents</t>
+          <t>Net cash flows from / (used in) financing activities</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>99.09999999999999</v>
+        <v>-236.2</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>-199</v>
+        <v>-56.5</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>-37.4</v>
+        <v>-221.2</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-145.9</v>
+        <v>-139.6</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>219.1</v>
+        <v>-132.8</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-435.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
@@ -12149,26 +12152,26 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Effects of exchange rates on cash and cash equivalents</t>
+          <t>Net (decrease) / increase in cash and cash equivalents</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>2.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>-0.9</v>
+        <v>-199</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>-4.2</v>
+        <v>-37.4</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>4.3</v>
+        <v>-145.9</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>2.2</v>
+        <v>219.1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-6.6</v>
+        <v>-435.2</v>
       </c>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="n"/>
@@ -12187,26 +12190,26 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at beginning of the period</t>
+          <t>Effects of exchange rates on cash and cash equivalents</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>175.7</v>
+        <v>2.7</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>375.6</v>
+        <v>-0.9</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>417.2</v>
+        <v>-4.2</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>558.8</v>
+        <v>4.3</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>337.5</v>
+        <v>2.2</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>779.3</v>
+        <v>-6.6</v>
       </c>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="n"/>
@@ -12225,26 +12228,26 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at the end of the period</t>
+          <t>Cash and cash equivalents at beginning of the period</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>277.5</v>
+        <v>175.7</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>175.7</v>
+        <v>375.6</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>375.6</v>
+        <v>417.2</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>417.2</v>
+        <v>558.8</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>558.8</v>
+        <v>337.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>337.5</v>
+        <v>779.3</v>
       </c>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="n"/>
@@ -12260,8 +12263,46 @@
       <c r="S33" s="5" t="n"/>
       <c r="T33" s="5" t="n"/>
     </row>
-    <row r="35" ht="240" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at the end of the period</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>277.5</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>175.7</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>375.6</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>417.2</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>558.8</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
+      <c r="Q34" s="5" t="n"/>
+      <c r="R34" s="5" t="n"/>
+      <c r="S34" s="5" t="n"/>
+      <c r="T34" s="5" t="n"/>
+    </row>
+    <row r="36" ht="240" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
 Official sources — Mizuho International plc Annual Reports: FY2026: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a90390502fd9a373f296929_f9f197d433ba8e1bc5b2b2b036d0020b_Mizuho_MHI_Annual_Report_2026.pdf; FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863028d4802cdc23dd6552c_2020-mizuho-international-plc-annual-report.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302ac32d1c7376f1f1877_2019-mizuho-international-plc-annual-report.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302c5e1d535ec3306fbee_2018-mizuho-international-plc-annual-report-1.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302d732d1c7376f1f2ad2_2017-mizuho-international-plc-annual-report.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302eda925dd5c1687cecd_2016-mizuho-international-plc-annual-report.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68630302eca4998ff565c8ea_2015-mizuho-international-plc-annual-report.pdf; FY2014: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzEwNDY4NTMyOGFkaXF6a2N4/document?format=pdf&amp;download=0</t>
@@ -12270,7 +12311,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A35:T35"/>
+    <mergeCell ref="A36:T36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12918,7 +12959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="86" customWidth="1" min="1" max="1"/>
@@ -12932,9 +12973,6 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13005,21 +13043,6 @@
       <c r="K3" s="4" t="inlineStr">
         <is>
           <t>FY2017</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
         </is>
       </c>
     </row>
@@ -13039,9 +13062,6 @@
       <c r="I4" s="6" t="n"/>
       <c r="J4" s="6" t="n"/>
       <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
-      <c r="N4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -13059,9 +13079,6 @@
       <c r="I5" s="6" t="n"/>
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
-      <c r="N5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -13089,9 +13106,6 @@
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="6" t="n"/>
       <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -13119,9 +13133,6 @@
       <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -13149,9 +13160,6 @@
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -13169,9 +13177,6 @@
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -13199,9 +13204,6 @@
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -13219,9 +13221,6 @@
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-      <c r="M11" s="6" t="n"/>
-      <c r="N11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -13259,9 +13258,6 @@
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n"/>
-      <c r="N12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -13299,9 +13295,6 @@
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-      <c r="M13" s="6" t="n"/>
-      <c r="N13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -13339,9 +13332,6 @@
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
-      <c r="N14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -13359,9 +13349,6 @@
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
-      <c r="N15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -13399,9 +13386,6 @@
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
-      <c r="M16" s="6" t="n"/>
-      <c r="N16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -13439,9 +13423,6 @@
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
-      <c r="M17" s="6" t="n"/>
-      <c r="N17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -13459,9 +13440,6 @@
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
-      <c r="M18" s="6" t="n"/>
-      <c r="N18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -13499,9 +13477,6 @@
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
-      <c r="M19" s="6" t="n"/>
-      <c r="N19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -13539,9 +13514,6 @@
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
-      <c r="M20" s="6" t="n"/>
-      <c r="N20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -13579,9 +13551,6 @@
       <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
-      <c r="M21" s="6" t="n"/>
-      <c r="N21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -13619,9 +13588,6 @@
       <c r="I22" s="6" t="n"/>
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
-      <c r="M22" s="6" t="n"/>
-      <c r="N22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -13659,9 +13625,6 @@
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="n"/>
-      <c r="M23" s="6" t="n"/>
-      <c r="N23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -13679,9 +13642,6 @@
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
-      <c r="L24" s="6" t="n"/>
-      <c r="M24" s="6" t="n"/>
-      <c r="N24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -13709,9 +13669,6 @@
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
-      <c r="M25" s="6" t="n"/>
-      <c r="N25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -13749,9 +13706,6 @@
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
-      <c r="L26" s="6" t="n"/>
-      <c r="M26" s="6" t="n"/>
-      <c r="N26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -13785,9 +13739,6 @@
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
-      <c r="M27" s="6" t="n"/>
-      <c r="N27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -13825,9 +13776,6 @@
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
-      <c r="L28" s="6" t="n"/>
-      <c r="M28" s="6" t="n"/>
-      <c r="N28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -13861,9 +13809,6 @@
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
-      <c r="M29" s="6" t="n"/>
-      <c r="N29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -13897,9 +13842,6 @@
       <c r="I30" s="6" t="n"/>
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
-      <c r="M30" s="6" t="n"/>
-      <c r="N30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -13933,9 +13875,6 @@
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
-      <c r="L31" s="6" t="n"/>
-      <c r="M31" s="6" t="n"/>
-      <c r="N31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -13953,9 +13892,6 @@
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
-      <c r="L32" s="6" t="n"/>
-      <c r="M32" s="6" t="n"/>
-      <c r="N32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -13983,9 +13919,6 @@
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="6" t="n"/>
-      <c r="L33" s="6" t="n"/>
-      <c r="M33" s="6" t="n"/>
-      <c r="N33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -14013,9 +13946,6 @@
       <c r="I34" s="6" t="n"/>
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="6" t="n"/>
-      <c r="L34" s="6" t="n"/>
-      <c r="M34" s="6" t="n"/>
-      <c r="N34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -14043,9 +13973,6 @@
       <c r="I35" s="6" t="n"/>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="6" t="n"/>
-      <c r="L35" s="6" t="n"/>
-      <c r="M35" s="6" t="n"/>
-      <c r="N35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -14073,9 +14000,6 @@
       <c r="I36" s="6" t="n"/>
       <c r="J36" s="6" t="n"/>
       <c r="K36" s="6" t="n"/>
-      <c r="L36" s="6" t="n"/>
-      <c r="M36" s="6" t="n"/>
-      <c r="N36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -14113,9 +14037,6 @@
       <c r="I37" s="6" t="n"/>
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="6" t="n"/>
-      <c r="L37" s="6" t="n"/>
-      <c r="M37" s="6" t="n"/>
-      <c r="N37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -14133,9 +14054,6 @@
       <c r="I38" s="6" t="n"/>
       <c r="J38" s="6" t="n"/>
       <c r="K38" s="6" t="n"/>
-      <c r="L38" s="6" t="n"/>
-      <c r="M38" s="6" t="n"/>
-      <c r="N38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -14163,9 +14081,6 @@
       <c r="I39" s="6" t="n"/>
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="6" t="n"/>
-      <c r="L39" s="6" t="n"/>
-      <c r="M39" s="6" t="n"/>
-      <c r="N39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -14193,9 +14108,6 @@
       <c r="I40" s="6" t="n"/>
       <c r="J40" s="6" t="n"/>
       <c r="K40" s="6" t="n"/>
-      <c r="L40" s="6" t="n"/>
-      <c r="M40" s="6" t="n"/>
-      <c r="N40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -14233,9 +14145,6 @@
       <c r="I41" s="6" t="n"/>
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="6" t="n"/>
-      <c r="L41" s="6" t="n"/>
-      <c r="M41" s="6" t="n"/>
-      <c r="N41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -14253,9 +14162,6 @@
       <c r="I42" s="6" t="n"/>
       <c r="J42" s="6" t="n"/>
       <c r="K42" s="6" t="n"/>
-      <c r="L42" s="6" t="n"/>
-      <c r="M42" s="6" t="n"/>
-      <c r="N42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -14273,9 +14179,6 @@
       <c r="I43" s="6" t="n"/>
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="6" t="n"/>
-      <c r="L43" s="6" t="n"/>
-      <c r="M43" s="6" t="n"/>
-      <c r="N43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -14303,9 +14206,6 @@
       <c r="K44" s="6" t="n">
         <v>658.3</v>
       </c>
-      <c r="L44" s="6" t="n"/>
-      <c r="M44" s="6" t="n"/>
-      <c r="N44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -14333,9 +14233,6 @@
       <c r="K45" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="L45" s="6" t="n"/>
-      <c r="M45" s="6" t="n"/>
-      <c r="N45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -14363,9 +14260,6 @@
       <c r="K46" s="6" t="n">
         <v>703.3</v>
       </c>
-      <c r="L46" s="6" t="n"/>
-      <c r="M46" s="6" t="n"/>
-      <c r="N46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -14383,9 +14277,6 @@
       <c r="I47" s="6" t="n"/>
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="6" t="n"/>
-      <c r="L47" s="6" t="n"/>
-      <c r="M47" s="6" t="n"/>
-      <c r="N47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -14413,9 +14304,6 @@
       <c r="K48" s="6" t="n">
         <v>2002.2</v>
       </c>
-      <c r="L48" s="6" t="n"/>
-      <c r="M48" s="6" t="n"/>
-      <c r="N48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -14433,9 +14321,6 @@
       <c r="I49" s="6" t="n"/>
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="6" t="n"/>
-      <c r="L49" s="6" t="n"/>
-      <c r="M49" s="6" t="n"/>
-      <c r="N49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -14473,9 +14358,6 @@
           <t>32.9%</t>
         </is>
       </c>
-      <c r="L50" s="6" t="n"/>
-      <c r="M50" s="6" t="n"/>
-      <c r="N50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -14513,9 +14395,6 @@
           <t>32.9%</t>
         </is>
       </c>
-      <c r="L51" s="6" t="n"/>
-      <c r="M51" s="6" t="n"/>
-      <c r="N51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -14553,9 +14432,6 @@
           <t>35.1%</t>
         </is>
       </c>
-      <c r="L52" s="6" t="n"/>
-      <c r="M52" s="6" t="n"/>
-      <c r="N52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -14573,9 +14449,6 @@
       <c r="I53" s="6" t="n"/>
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="6" t="n"/>
-      <c r="L53" s="6" t="n"/>
-      <c r="M53" s="6" t="n"/>
-      <c r="N53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -14613,9 +14486,6 @@
           <t>1.250%</t>
         </is>
       </c>
-      <c r="L54" s="6" t="n"/>
-      <c r="M54" s="6" t="n"/>
-      <c r="N54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -14653,9 +14523,6 @@
           <t>0.081%</t>
         </is>
       </c>
-      <c r="L55" s="6" t="n"/>
-      <c r="M55" s="6" t="n"/>
-      <c r="N55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -14693,9 +14560,6 @@
           <t>1.331%</t>
         </is>
       </c>
-      <c r="L56" s="6" t="n"/>
-      <c r="M56" s="6" t="n"/>
-      <c r="N56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -14713,9 +14577,6 @@
       <c r="I57" s="6" t="n"/>
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="6" t="n"/>
-      <c r="L57" s="6" t="n"/>
-      <c r="M57" s="6" t="n"/>
-      <c r="N57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -14743,9 +14604,6 @@
       <c r="K58" s="6" t="n">
         <v>15108.3</v>
       </c>
-      <c r="L58" s="6" t="n"/>
-      <c r="M58" s="6" t="n"/>
-      <c r="N58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -14783,9 +14641,6 @@
           <t>4.36%</t>
         </is>
       </c>
-      <c r="L59" s="6" t="n"/>
-      <c r="M59" s="6" t="n"/>
-      <c r="N59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -14803,9 +14658,6 @@
       <c r="I60" s="6" t="n"/>
       <c r="J60" s="6" t="n"/>
       <c r="K60" s="6" t="n"/>
-      <c r="L60" s="6" t="n"/>
-      <c r="M60" s="6" t="n"/>
-      <c r="N60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -14835,9 +14687,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L61" s="6" t="n"/>
-      <c r="M61" s="6" t="n"/>
-      <c r="N61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -14867,9 +14716,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L62" s="6" t="n"/>
-      <c r="M62" s="6" t="n"/>
-      <c r="N62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -14907,9 +14753,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L63" s="6" t="n"/>
-      <c r="M63" s="6" t="n"/>
-      <c r="N63" s="6" t="n"/>
     </row>
     <row r="65" ht="420" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
@@ -14940,7 +14783,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A65:N65"/>
+    <mergeCell ref="A65:K65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
+++ b/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
@@ -14684,7 +14684,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -14713,7 +14713,7 @@
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -14750,7 +14750,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -14772,7 +14772,7 @@
 FY2017: NO KEY-METRICS TABLE EXISTS IN THE FY2017 EDITION - this column is the FY2018 edition's own 2017 comparative column (Table 6, p.15), and is the only column on this sheet not taken from its own year's edition. It is filled rather than left blank because the FY2017 document publishes no such table at all, so there is no original disclosure for a later one to displace; the distinction matters, and a BLANK on this sheet means the figure was never published for that date in any edition. The FY2017 and FY2016 editions were both read in full: neither contains a key-metrics table, and the extraction is not at fault - the FY2017 document is rich on neighbouring terms and does print a leverage exposure table and a CC1-style own-funds template, but has no line 'Total risk-weighted assets', no 'Liquidity Coverage Ratio' heading and no 'Total capital ratio' row anywhere.
 FY2016 AND EARLIER ARE BLANK FOR TWO REASONS AT ONCE: no edition prints the table, and the FY2014-FY2016 Pillar 3 documents are in any case disclosures of Mizuho Securities UK Holdings Ltd (MSUKH), MHI's immediate parent, not of MHI - a parent's consolidated figures are not this entity's and are not reproduced here on any sheet.
 WHY TWO BLOCKS RATHER THAN ONE SERIES. The template changed at 1 January 2022 and the two versions are not row-compatible: the pre-2022 table has no SREP rows, no NSFR rows, no 'including claims on central banks' leverage variants and no average-leverage rows, while it does carry a standalone 'Tier 2' line that the UK template does not. Its leverage rows are also on the EBA exposure measure, which is the basis break map rule 5 exists for. Nothing is carried across the boundary and no row is filled by inference from the other block.
-ROWS THE BANK DID NOT PRINT ARE BLANK, NOT ZERO. Each FY2022-FY2026 edition states: 'Only rows relevant to the Group are shown in Table 6, remaining rows from the PRA disclosure template have been left out as these are nil rows' - which is why rows 10, UK 8a, UK 9a and UK 10a never appear. Within the UK block, rows 14a, 14c, 14d and 14e are blank for FY2022 because the FY2022 edition does not print them (it prints 'n/a' in its own 2021 comparative column for several rows, but that column is not used here - FY2021 comes from the FY2021 edition). The FY2018 edition prints 'N/A' for all three LCR rows in its 2017 comparative, footnoted 'Not applicable as this disclosure is being made for the first time in 2018'; that glyph is reproduced as printed rather than blanked.
+ROWS THE BANK DID NOT PRINT ARE BLANK, NOT ZERO. Each FY2022-FY2026 edition states: 'Only rows relevant to the Group are shown in Table 6, remaining rows from the PRA disclosure template have been left out as these are nil rows' - which is why rows 10, UK 8a, UK 9a and UK 10a never appear. Within the UK block, rows 14a, 14c, 14d and 14e are blank for FY2022 because the FY2022 edition does not print them (it prints 'n/a' in its own 2021 comparative column for several rows, but that column is not used here - FY2021 comes from the FY2021 edition). The FY2018 edition prints 'N/A' for all three LCR rows in its 2017 comparative, footnoted 'Not applicable as this disclosure is being made for the first time in 2018'; that glyph is carried as a plain '-' (KM1 map rule 2, applied GA-020 2026-09-19; the printed glyph is 'N/A') rather than blanked.
 FY2025 LCR - THREE DIFFERENT PUBLISHED FIGURES FOR ONE DATE, ALL RECORDED, NONE RECONCILED.
   (a) This sheet's FY2025 column carries the FY2025 edition's own figures: HQLA 2,014.2, net cash outflows 850.4, LCR 239.20%.
   (b) The FY2026 edition RESTATES that comparative, with its own footnote: 'Values for the year ended 31 March 2025 were reported incorrectly before. Comparative values have been restated' - giving HQLA 2,056.1, net cash outflows 891.2 and LCR 236.5%. Under this project's own-year rule the original stands in the FY2025 column and the restatement is recorded here rather than substituted.

--- a/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
+++ b/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
@@ -817,12 +817,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$BN$25:$BZ$25</f>
+              <f>'Overview'!$BN$25:$BS$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$BN$26:$BZ$26</f>
+              <f>'Overview'!$BN$26:$BS$26</f>
             </numRef>
           </val>
         </ser>
@@ -841,12 +841,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$BN$25:$BZ$25</f>
+              <f>'Overview'!$BN$25:$BS$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$BN$27:$BZ$27</f>
+              <f>'Overview'!$BN$27:$BS$27</f>
             </numRef>
           </val>
         </ser>
@@ -865,12 +865,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Overview'!$BN$25:$BZ$25</f>
+              <f>'Overview'!$BN$25:$BS$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$BN$28:$BZ$28</f>
+              <f>'Overview'!$BN$28:$BS$28</f>
             </numRef>
           </val>
         </ser>
@@ -980,7 +980,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!CC6</f>
+              <f>'Overview'!BV6</f>
             </strRef>
           </tx>
           <spPr>
@@ -998,12 +998,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$CD$5:$CP$5</f>
+              <f>'Overview'!$BW$5:$CI$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$CD$6:$CP$6</f>
+              <f>'Overview'!$BW$6:$CI$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1013,7 +1013,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!CC7</f>
+              <f>'Overview'!BV7</f>
             </strRef>
           </tx>
           <spPr>
@@ -1031,12 +1031,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$CD$5:$CP$5</f>
+              <f>'Overview'!$BW$5:$CI$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$CD$7:$CP$7</f>
+              <f>'Overview'!$BW$7:$CI$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1511,7 +1511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP35"/>
+  <dimension ref="A1:CI35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1599,13 +1599,6 @@
     <col hidden="1" width="13" customWidth="1" min="85" max="85"/>
     <col hidden="1" width="13" customWidth="1" min="86" max="86"/>
     <col hidden="1" width="13" customWidth="1" min="87" max="87"/>
-    <col hidden="1" width="13" customWidth="1" min="88" max="88"/>
-    <col hidden="1" width="13" customWidth="1" min="89" max="89"/>
-    <col hidden="1" width="13" customWidth="1" min="90" max="90"/>
-    <col hidden="1" width="13" customWidth="1" min="91" max="91"/>
-    <col hidden="1" width="13" customWidth="1" min="92" max="92"/>
-    <col hidden="1" width="13" customWidth="1" min="93" max="93"/>
-    <col hidden="1" width="13" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1766,67 +1759,67 @@
           <t>FY2026</t>
         </is>
       </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>FY2014</t>
+          <t>FY2021</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>FY2015</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>FY2016</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>FY2017</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="CJ5" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="CK5" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="CL5" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="CM5" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="CN5" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="CO5" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="CP5" t="inlineStr">
         <is>
           <t>FY2026</t>
         </is>
@@ -1921,48 +1914,48 @@
       <c r="AD6" t="n">
         <v>24841.5</v>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
+      <c r="BW6" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>20.02</v>
+      </c>
       <c r="CD6" t="n">
-        <v>50.3</v>
+        <v>31.12</v>
       </c>
       <c r="CE6" t="n">
-        <v>49.5</v>
+        <v>31.14</v>
       </c>
       <c r="CF6" t="n">
-        <v>36.4</v>
+        <v>28</v>
       </c>
       <c r="CG6" t="n">
-        <v>32.9</v>
+        <v>22.8</v>
       </c>
       <c r="CH6" t="n">
-        <v>30.6</v>
+        <v>20</v>
       </c>
       <c r="CI6" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>20.02</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>31.12</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>28</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>20</v>
-      </c>
-      <c r="CP6" t="n">
         <v>26.19</v>
       </c>
     </row>
@@ -2050,45 +2043,45 @@
       <c r="AD7" t="n">
         <v>5981.7</v>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
+      <c r="BX7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>4.75</v>
+      </c>
       <c r="CE7" t="n">
-        <v>1.87</v>
+        <v>4.07</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.28</v>
+        <v>4.24</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.36</v>
+        <v>4.07</v>
       </c>
       <c r="CH7" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="CI7" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="CP7" t="n">
         <v>4.43</v>
       </c>
     </row>
@@ -3233,102 +3226,32 @@
           <t>FY2021</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
-        </is>
-      </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>FY2014</t>
+          <t>FY2021</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>FY2015</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>FY2016</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>FY2017</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="BT25" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="BU25" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="BV25" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="BW25" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="BX25" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="BY25" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="BZ25" t="inlineStr">
         <is>
           <t>FY2026</t>
         </is>
@@ -3358,34 +3281,27 @@
       <c r="G26" s="5" t="n">
         <v>-485.7</v>
       </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
       <c r="BM26" t="inlineStr">
         <is>
           <t>Net cash flow from operating activities</t>
         </is>
       </c>
-      <c r="BU26" t="n">
+      <c r="BN26" t="n">
         <v>-485.7</v>
       </c>
-      <c r="BV26" t="n">
+      <c r="BO26" t="n">
         <v>384.9</v>
       </c>
-      <c r="BW26" t="n">
+      <c r="BP26" t="n">
         <v>25.3</v>
       </c>
-      <c r="BX26" t="n">
+      <c r="BQ26" t="n">
         <v>216.7</v>
       </c>
-      <c r="BY26" t="n">
+      <c r="BR26" t="n">
         <v>-92.5</v>
       </c>
-      <c r="BZ26" t="n">
+      <c r="BS26" t="n">
         <v>417.7</v>
       </c>
     </row>
@@ -3413,34 +3329,27 @@
       <c r="G27" s="5" t="n">
         <v>-25.1</v>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
       <c r="BM27" t="inlineStr">
         <is>
           <t>Net cash flows used in investing activities</t>
         </is>
       </c>
-      <c r="BU27" t="n">
+      <c r="BN27" t="n">
         <v>-25.1</v>
       </c>
-      <c r="BV27" t="n">
+      <c r="BO27" t="n">
         <v>-33</v>
       </c>
-      <c r="BW27" t="n">
+      <c r="BP27" t="n">
         <v>-31.6</v>
       </c>
-      <c r="BX27" t="n">
+      <c r="BQ27" t="n">
         <v>-32.9</v>
       </c>
-      <c r="BY27" t="n">
+      <c r="BR27" t="n">
         <v>-50</v>
       </c>
-      <c r="BZ27" t="n">
+      <c r="BS27" t="n">
         <v>-82.40000000000001</v>
       </c>
     </row>
@@ -3468,34 +3377,27 @@
       <c r="G28" s="5" t="n">
         <v>337.5</v>
       </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
       <c r="BM28" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at end of period</t>
         </is>
       </c>
-      <c r="BU28" t="n">
+      <c r="BN28" t="n">
         <v>337.5</v>
       </c>
-      <c r="BV28" t="n">
+      <c r="BO28" t="n">
         <v>558.8</v>
       </c>
-      <c r="BW28" t="n">
+      <c r="BP28" t="n">
         <v>417.2</v>
       </c>
-      <c r="BX28" t="n">
+      <c r="BQ28" t="n">
         <v>375.6</v>
       </c>
-      <c r="BY28" t="n">
+      <c r="BR28" t="n">
         <v>175.7</v>
       </c>
-      <c r="BZ28" t="n">
+      <c r="BS28" t="n">
         <v>277.5</v>
       </c>
     </row>

--- a/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
+++ b/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
@@ -116,7 +116,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="N33" s="6" t="n"/>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" ht="30" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
           <t>Note: Annual data; Consolidated Group basis FY2019-FY2025, Company-only basis FY2014-FY2018 (see the Balance Sheet sheet's REPORTING BASIS note). Cash flow totals are blank for FY2014-FY2020 (no cash flow statement prepared those years).</t>
@@ -4165,7 +4165,7 @@
         <v>456.9</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2015/FY2014: Total capital equals Tier 1 capital because no Tier 2 capital had yet been issued (first appears FY2016).</t>
@@ -5003,10 +5003,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -5031,7 +5031,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£m / %</t>
         </is>
       </c>
     </row>
@@ -5169,15 +5169,148 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2014 leverage ratio was discussed qualitatively (implementation of PRA bank-level reporting was noted as having 'commenced') but no computed ratio was numerically disclosed in the FY2014 Pillar 3 document.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="220" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total exposure measure including claims on central banks (£m) - LR2 row 24</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>15552</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>16115.3</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>15997.4</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>15184.7</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>16210.5</v>
+      </c>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>(-) Claims on central banks excluded (£m) - LR2 row 24a</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-217.2</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-115.7</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-328.9</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-371.9</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-483.4</v>
+      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Total exposure measure excluding claims on central banks (£m) - LR2 row 24b</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>15334.8</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>15999.6</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>15668.5</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>14812.8</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>15727.1</v>
+      </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Leverage ratio including claims on central banks (%) - LR2 row 25c</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>4.37%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>4.16%</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>4.07%</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>4.13%</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>3.95%</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="299" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2014 leverage ratio was discussed qualitatively (implementation of PRA bank-level reporting was noted as having 'commenced') but no computed ratio was numerically disclosed in the FY2014 Pillar 3 document.
+BOTH LEVERAGE BASES, FY2022-FY2026 (GA-026, 2026-10-09). For periods from 1 January 2022 the UK template UK LR2 (LRCom) prints the exposure measure and the leverage ratio on TWO bases - INCLUDING and EXCLUDING claims on central banks - reconciling at the deduction row 24a. Mizuho International publishes both, and this sheet now carries both, read at 300 dpi from each edition's own 'Table 15: Leverage ratio common disclosure (LRCom)' (2026 edition p.26, 2025 p.28, 2024 p.28, 2023 p.27, 2022 p.26).
+ROW NUMBERING - WHY THIS BANK WAS NEARLY MISSED. MHI prints the dual-basis rows as bare '24', '24a', '24b', '25', '25c', WITHOUT the 'UK-' prefix the template specifies, and wraps the labels across lines. The label WORDING is the UK template's verbatim. A search for the discriminating row 'UK-24a' - the row that exists only in the dual-basis template - therefore returns nothing here, and this bank was initially mis-classified as an old single-basis CRR filer on that zero.
+TOP ROW DELIBERATELY UNCHANGED AND DELIBERATELY NOT RELABELLED. The 'Leverage Ratio' row is exactly as before. It must stay FIRST, because check_overview_ties.py takes the first cell PRINTED AS A PERCENTAGE on a ratio sheet as that sheet's headline. It is not relabelled as an excluding-basis row because its FY2021 and earlier figures come from the pre-2022 CRR template, which has no basis split at all.
+FY2024 ROW 25c - THE BANK'S OWN TWO EDITIONS DISAGREE. BOTH ARE RECORDED; NEITHER IS RECONCILED. The 2024 edition's own column prints row 25c (including claims on central banks) as 4.07%, the same figure as its own row 25 (excluding). The 2025 edition's FY2024 comparative prints 3.98% for that same row and date, while agreeing with the 2024 edition on every amount in the column (15,997.4 / -328.9 / 15,668.5) and on row 25 (4.07%). Under this project's own-edition rule the 2024 edition's own 4.07% stands in the FY2024 cell and the later 3.98% is recorded here rather than substituted for it. Stated as an observation only, and NOT as the source of any figure on this sheet: Tier 1 capital 637.4 over the including measure 15,997.4 is 3.98%, and over the excluding measure 15,668.5 is 4.07%.
+EVERY OTHER COMPARATIVE AGREES EXACTLY. The 2026 edition's FY2025 column, the 2024 edition's FY2023 column and the 2023 edition's FY2022 column each reproduce the next edition's own figures on all five rows, checked at 300 dpi.
+FY2021 LEFT BLANK ON THE FOUR NEW ROWS, DELIBERATELY. The dual basis is effective only for periods from 1 January 2022, and MHI's FY2021 (year ended 31 March 2021) pre-dates it: the 2021 edition's own Table 15 is the old CRR template, with a single 'Leverage ratio total exposure measure' of 14,224.7 and one ratio, 4.75%. The 2022 edition RESTATES that comparative onto the dual basis - including 14,452.2, row 24a -227.5, excluding 14,224.7, row 25 4.75%, row 25c 4.67% - and under the own-edition rule that restatement is recorded here, not written into the FY2021 cells. Note that the old template's single measure, 14,224.7, is identical to the restated EXCLUDING measure, which is why the FY2021 ratio is unchanged at 4.75%.
+TRANSCRIBED AS PRINTED: the 2022 edition sets row 24b as '15,727.10', to two decimals where every other figure in that table carries one. The 2022 edition also captions row 25 as just 'Leverage ratio', where the later editions caption it 'Leverage ratio excluding claims on central banks (%)'; the row number and the reconciliation to row 24b are the same.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="220" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
 Official Mizuho International plc Pillar 3 disclosures: FY2026: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903d9cec6eb609b9981dde_MHI%20consolidated%20Pillar%203%20disclosure%202026.pdf; FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
@@ -5186,8 +5319,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A9:M9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5332,7 +5465,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: LCR was first disclosed in the FY2018 Pillar 3 document (the document itself states this); not disclosed FY2014-FY2017.</t>
@@ -5451,14 +5584,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: NSFR was not disclosed in the 2021 report or any FY2014-FY2020 report; 2025 is from the Annual Report KPI section.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="220" customHeight="1">
+    <row r="7" ht="247" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
@@ -5658,7 +5791,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="78" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: MREL ratio is not numerically disclosed in any Mizuho International plc annual report or Pillar 3 disclosure. RE-ESTABLISHED WITH A CONTROL 2026-09-18 rather than carried forward - the previous note asserted this for FY2014-FY2025 and was already out of date, since the workbook carries FY2026. Whole-document search of the two newest editions, both text-native and downloaded fresh (%PDF-, application/pdf): the FY2026 consolidated Pillar 3 (217,429 characters) returns ZERO hits for 'MREL', 'minimum requirement for own funds' and 'TLAC', against 145 hits for 'capital', 231 for 'ratio' and 10 for 'own funds' in the same extraction; the FY2025 edition (224,343 characters) returns the same three zeros against 152 and 228. So the zero is a fact about the documents, not a failure of the search. The FY2026 Annual Report (696,912 characters) likewise returns zero for all three.
@@ -7888,7 +8021,7 @@
         <v>24761.1</v>
       </c>
     </row>
-    <row r="42" ht="260" customHeight="1">
+    <row r="42" ht="390" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
@@ -9346,7 +9479,7 @@
         <v>-2041.1</v>
       </c>
     </row>
-    <row r="28" ht="240" customHeight="1">
+    <row r="28" ht="390" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
@@ -9373,7 +9506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -10913,12 +11046,19 @@
         <v>845.2</v>
       </c>
     </row>
-    <row r="82" ht="150" customHeight="1">
+    <row r="82" ht="325" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
 Official sources — Mizuho International plc Annual Reports: FY2026: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a90390502fd9a373f296929_f9f197d433ba8e1bc5b2b2b036d0020b_Mizuho_MHI_Annual_Report_2026.pdf; FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6949753a5e4af5e79887a666_MIzuho_MHI_Annual_Report_2025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686301edbbd3ea24c5c8059f_mizuho_annual_report_2024_final_v02.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863021624e9468651ae2fbd_mizuho_annual_report_2023_final_02.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302389cf6e01446043fd2_2022-mizuho-international-plc-annual-report.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302637f7fc2c72f2e2f59_2021-mizuho-international-plc-annual-report.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6863028d4802cdc23dd6552c_2020-mizuho-international-plc-annual-report.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302ac32d1c7376f1f1877_2019-mizuho-international-plc-annual-report.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302c5e1d535ec3306fbee_2018-mizuho-international-plc-annual-report-1.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302d732d1c7376f1f2ad2_2017-mizuho-international-plc-annual-report.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686302eda925dd5c1687cecd_2016-mizuho-international-plc-annual-report.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68630302eca4998ff565c8ea_2015-mizuho-international-plc-annual-report.pdf; FY2014: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzEwNDY4NTMyOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Official Companies House statutory filing sources for the FY2008-FY2013 extension (HD-075): FY2013: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA4MDE5NTMxMmFkaXF6a2N4/document?format=pdf&amp;download=0; FY2012: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA2NTI2MzY4MGFkaXF6a2N4/document?format=pdf&amp;download=0; FY2011: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA0NDQ4MDc5N2FkaXF6a2N4/document?format=pdf&amp;download=0; FY2010: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzAyMzM2MTY3OWFkaXF6a2N4/document?format=pdf&amp;download=0; FY2009: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MjA0MjM3OTU5NmFkaXF6a2N4/document?format=pdf&amp;download=0; FY2008: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MjAxMDQ0NzA1NmFkaXF6a2N4/document?format=pdf&amp;download=0
+Official Companies House statutory filing sources for the FY2008-FY2013 extension (HD-075): FY2013: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA4MDE5NTMxMmFkaXF6a2N4/document?format=pdf&amp;download=0; FY2012: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA2NTI2MzY4MGFkaXF6a2N4/document?format=pdf&amp;download=0; FY2011: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzA0NDQ4MDc5N2FkaXF6a2N4/document?format=pdf&amp;download=0; FY2010: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MzAyMzM2MTY3OWFkaXF6a2N4/document?format=pdf&amp;download=0; FY2009: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MjA0MjM3OTU5NmFkaXF6a2N4/document?format=pdf&amp;download=0; FY2008: https://find-and-update.company-information.service.gov.uk/company/01203696/filing-history/MjAxMDQ0NzA1NmFkaXF6a2N4/document?format=pdf&amp;download=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="403" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 Balance Sheet/P&amp;L/Equity figures are the Consolidated Mizuho International plc Group basis for FY2019-FY2025 (distinct from the Company-only basis also shown in each Annual Report). FY2026: Annual Report 2026 (year ended 31 March 2026), Consolidated Statement of Comprehensive Income p.79, Consolidated Statement of Financial Position p.80, Consolidated Statement of Changes in Equity p.82, Consolidated Statement of Cash Flows p.84. FY2025/FY2024: Annual Report 2025, Consolidated Statement of Comprehensive Income and Consolidated Statement of Financial Position p.88-89, Consolidated Statement of Changes in Equity p.90-91. FY2023/FY2022: Annual Report 2024, same statements p.86-89. FY2021: Annual Report 2022, Consolidated Statement of Comprehensive Income p.84-85, Consolidated Statement of Financial Position and Consolidated Statement of Changes in Equity p.86, 88. FY2020: Annual Report 2020, Consolidated Statement of Comprehensive Income/Financial Position/Changes in Equity/Cash Flows p.34-39. FY2019: Annual Report 2019, same Consolidated statements p.22-27.
 REPORTING BASIS: FY2019-FY2025 are Consolidated Mizuho International plc Group basis (Group consolidation began FY2019). FY2015-FY2018 are Company-only basis under FRS 102 (restated from UK GAAP as at 1 April 2015 transition date); the Company did not yet prepare group accounts. FY2010-FY2014 are Company-only, originally-filed UK GAAP (pre-FRS 102), sourced from the Companies House statutory filing rather than Mizuho's own site (see AR/P3/CH_STATUTORY source dict comments) - there is a real ~£0.5m equity break between FY2014 as originally filed and the FRS102-restated FY2015 opening position (see the Statement of Changes in Equity's transition row). FY2008-FY2009 are a mixed basis dictated by what each year's own filing actually presents: the Balance Sheet is Company-only (matching the FY2010-FY2014 convention) but the Profit and Loss Account is Consolidated (the Company did not present its own P&amp;L those two years, relying on the Companies Act exemption for a subsidiary whose consolidated P&amp;L is presented instead) - Total Equity is identical under either basis for FY2008/FY2009 (the Group/Company difference is confined to derivative and repo gross-up presentation on the asset/liability sides), so this mixed basis does not affect the equity reconciliation ladder. None of FY2008-FY2020 include a cash flow statement (FRS 1/FRS 102 exemption for a qualifying subsidiary whose ultimate parent publishes consolidated accounts, per each year's own Annual Report). FY2012's own filing discloses a voluntary accounting policy change made during FY2012, from trade-date to settlement-date accounting for regular-way trading securities transactions; applied retrospectively, it shrank the FY2011 comparative shown in FY2012's own report (Total Assets 29,781.5 -&gt; 27,034.4, largely a reclassification out of 'Other assets') versus FY2011's own originally-filed trade-date figures used for the FY2011 column here (per this project's own-year-filing sourcing rule) - a real, disclosed break between the FY2011 and FY2012 columns, not a transcription error.
 FY2015-FY2018 (Company-only basis): FY2018 Annual Report, Statement of Comprehensive Income p.22, Statement of Financial Position p.23, Statement of Changes in Equity p.24. FY2017 Annual Report, same statements p.15-17. FY2016 Annual Report, same statements p.14-16 (FY2016 report's own FY2015 comparative column is the source for FY2015, restated to FRS 102). FY2014 (originally-filed UK GAAP, Company-only): Companies House 'Full accounts made up to 31 March 2014' filing, Profit and Loss Account p.13, Balance Sheet p.14, Consolidated Statement of Total Recognised Gains and Losses p.15.
@@ -10927,7 +11067,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A84:G84"/>
     <mergeCell ref="A82:G82"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12861,7 +13002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="86" customWidth="1" min="1" max="1"/>
@@ -14656,7 +14797,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="420" customHeight="1">
+    <row r="65" ht="409" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
           <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
@@ -14673,7 +14814,14 @@
 FY2018: Pillar 3 disclosures 2018, Table 6, p.15.
 FY2017: NO KEY-METRICS TABLE EXISTS IN THE FY2017 EDITION - this column is the FY2018 edition's own 2017 comparative column (Table 6, p.15), and is the only column on this sheet not taken from its own year's edition. It is filled rather than left blank because the FY2017 document publishes no such table at all, so there is no original disclosure for a later one to displace; the distinction matters, and a BLANK on this sheet means the figure was never published for that date in any edition. The FY2017 and FY2016 editions were both read in full: neither contains a key-metrics table, and the extraction is not at fault - the FY2017 document is rich on neighbouring terms and does print a leverage exposure table and a CC1-style own-funds template, but has no line 'Total risk-weighted assets', no 'Liquidity Coverage Ratio' heading and no 'Total capital ratio' row anywhere.
 FY2016 AND EARLIER ARE BLANK FOR TWO REASONS AT ONCE: no edition prints the table, and the FY2014-FY2016 Pillar 3 documents are in any case disclosures of Mizuho Securities UK Holdings Ltd (MSUKH), MHI's immediate parent, not of MHI - a parent's consolidated figures are not this entity's and are not reproduced here on any sheet.
-WHY TWO BLOCKS RATHER THAN ONE SERIES. The template changed at 1 January 2022 and the two versions are not row-compatible: the pre-2022 table has no SREP rows, no NSFR rows, no 'including claims on central banks' leverage variants and no average-leverage rows, while it does carry a standalone 'Tier 2' line that the UK template does not. Its leverage rows are also on the EBA exposure measure, which is the basis break map rule 5 exists for. Nothing is carried across the boundary and no row is filled by inference from the other block.
+WHY TWO BLOCKS RATHER THAN ONE SERIES. The template changed at 1 January 2022 and the two versions are not row-compatible: the pre-2022 table has no SREP rows, no NSFR rows, no 'including claims on central banks' leverage variants and no average-leverage rows, while it does carry a standalone 'Tier 2' line that the UK template does not. Its leverage rows are also on the EBA exposure measure, which is the basis break map rule 5 exists for. Nothing is carried across the boundary and no row is filled by inference from the other block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="409" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 ROWS THE BANK DID NOT PRINT ARE BLANK, NOT ZERO. Each FY2022-FY2026 edition states: 'Only rows relevant to the Group are shown in Table 6, remaining rows from the PRA disclosure template have been left out as these are nil rows' - which is why rows 10, UK 8a, UK 9a and UK 10a never appear. Within the UK block, rows 14a, 14c, 14d and 14e are blank for FY2022 because the FY2022 edition does not print them (it prints 'n/a' in its own 2021 comparative column for several rows, but that column is not used here - FY2021 comes from the FY2021 edition). The FY2018 edition prints 'N/A' for all three LCR rows in its 2017 comparative, footnoted 'Not applicable as this disclosure is being made for the first time in 2018'; that glyph is carried as a plain '-' (KM1 map rule 2, applied GA-020 2026-09-19; the printed glyph is 'N/A') rather than blanked.
 FY2025 LCR - THREE DIFFERENT PUBLISHED FIGURES FOR ONE DATE, ALL RECORDED, NONE RECONCILED.
   (a) This sheet's FY2025 column carries the FY2025 edition's own figures: HQLA 2,014.2, net cash outflows 850.4, LCR 239.20%.
@@ -14684,8 +14832,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14848,7 +14997,7 @@
         <v>456.9</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2025 Annual Report states regulatory capital consists solely of Tier 1 capital; treated as CET1 for this metric because no Tier 2 capital is reported. FY2014-FY2016 capital resources consisted solely of common equity Tier 1 (no Tier 2 issued yet); FY2014-FY2016 are MSUKH group-level figures, not MHI-level (see the P3 source dict comment).</t>

--- a/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
+++ b/banks/MIZUHO INTERNATIONAL FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3664,14 +3665,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mizuho International plc — Tier 1 Capital</t>
+          <t>Mizuho International plc — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£ millions</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -3750,47 +3751,73 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 Capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>679.8</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>670.5</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>637.4</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>627.7</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>640.8</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>675.6</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>623.7</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>662.5</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>690.9</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>658.3</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>408.3</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>451.9</v>
-      </c>
-      <c r="N4" s="6" t="n">
-        <v>456.9</v>
+          <t>CET1 Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>26.19%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>22.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>28.0%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>31.14%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>31.12%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>20.02%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>30.6%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>32.9%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>49.5%</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>50.3%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="220" customHeight="1">
@@ -3837,14 +3864,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mizuho International plc — Tier 1 Ratio</t>
+          <t>Mizuho International plc — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>£ millions</t>
         </is>
       </c>
     </row>
@@ -3923,73 +3950,47 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>26.19%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>22.84%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>28.00%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>31.14%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>31.12%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>20.02%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>27.8%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>30.6%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>32.9%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>49.5%</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>50.3%</t>
-        </is>
+          <t>Tier 1 Capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>679.8</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>670.5</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>637.4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>627.7</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>640.8</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>675.6</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>623.7</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>662.5</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>690.9</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>658.3</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>408.3</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>451.9</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>456.9</v>
       </c>
     </row>
     <row r="6" ht="220" customHeight="1">
@@ -4009,6 +4010,205 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mizuho International plc — Tier 1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>26.19%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>22.84%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>28.00%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>31.14%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>31.12%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>20.02%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>30.6%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>32.9%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>49.5%</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>50.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="220" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2026: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903d9cec6eb609b9981dde_MHI%20consolidated%20Pillar%203%20disclosure%202026.pdf; FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:N6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4184,205 +4384,6 @@
   <mergeCells count="2">
     <mergeCell ref="A5:N5"/>
     <mergeCell ref="A7:N7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mizuho International plc — Total Capital Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2026</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total Capital Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>26.19%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>22.84%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>28.00%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>31.14%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>32.78%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>21.46%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>29.7%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>32.6%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>35.1%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>40.4%</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>49.5%</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>50.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="220" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
-Official Mizuho International plc Pillar 3 disclosures: FY2026: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903d9cec6eb609b9981dde_MHI%20consolidated%20Pillar%203%20disclosure%202026.pdf; FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:N6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4416,14 +4417,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mizuho International plc — Total RWAs</t>
+          <t>Mizuho International plc — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£ millions</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -4502,47 +4503,73 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total RWAs</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>2595.5</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>3353.2</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>2790.7</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>2241.7</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>2057.9</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>2171</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>3115.3</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>2385.8</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>2257</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>2002.2</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>1122.3</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>913.7</v>
-      </c>
-      <c r="N4" s="6" t="n">
-        <v>908.5</v>
+          <t>Total Capital Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>26.19%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>22.84%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>28.00%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>31.14%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>32.78%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>21.46%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>29.7%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>32.6%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>35.1%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>40.4%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>49.5%</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>50.3%</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="220" customHeight="1">
@@ -4562,6 +4589,179 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mizuho International plc — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£ millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total RWAs</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>2595.5</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>3353.2</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2790.7</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>2241.7</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>2057.9</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>2171</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>3115.3</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>2385.8</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>2257</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>2002.2</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>1122.3</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>913.7</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>908.5</v>
+      </c>
+    </row>
+    <row r="6" ht="220" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2026: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903d9cec6eb609b9981dde_MHI%20consolidated%20Pillar%203%20disclosure%202026.pdf; FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:N6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4997,7 +5197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5326,7 +5526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5489,7 +5689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5603,214 +5803,6 @@
   <mergeCells count="2">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mizuho International plc — MREL Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2026</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>MREL Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="78" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: MREL ratio is not numerically disclosed in any Mizuho International plc annual report or Pillar 3 disclosure. RE-ESTABLISHED WITH A CONTROL 2026-09-18 rather than carried forward - the previous note asserted this for FY2014-FY2025 and was already out of date, since the workbook carries FY2026. Whole-document search of the two newest editions, both text-native and downloaded fresh (%PDF-, application/pdf): the FY2026 consolidated Pillar 3 (217,429 characters) returns ZERO hits for 'MREL', 'minimum requirement for own funds' and 'TLAC', against 145 hits for 'capital', 231 for 'ratio' and 10 for 'own funds' in the same extraction; the FY2025 edition (224,343 characters) returns the same three zeros against 152 and 228. So the zero is a fact about the documents, not a failure of the search. The FY2026 Annual Report (696,912 characters) likewise returns zero for all three.
-WHAT THE DOCUMENTS DO SAY, which is consistent with there being nothing to find. The FY2026 Pillar 3 reproduces the PRA's 'UK CCA: Main features of regulatory own funds instruments and eligible liabilities instruments' template - i.e. the template that WOULD carry an eligible-liabilities instrument if MHI had one - and its only instrument is ordinary share capital, with row 34a 'Type of subordination (only for eligible liabilities)' printed 'n/a'. The FY2026 Annual Report states that the Group 'continues to participate actively in Mizuho Financial Group's recovery and resolution planning', i.e. resolution is planned at the Japanese parent level. That is context, not proof of a scope exclusion, and it is recorded as context: what is established here is that MHI publishes no MREL ratio, not why.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="220" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
-Official Mizuho International plc Pillar 3 disclosures: FY2026: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903d9cec6eb609b9981dde_MHI%20consolidated%20Pillar%203%20disclosure%202026.pdf; FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="A7:N7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8037,6 +8029,214 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A42:T42"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mizuho International plc — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>Not disclosed - MHI publishes no MREL ratio in any edition</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: MREL ratio is not numerically disclosed in any Mizuho International plc annual report or Pillar 3 disclosure. RE-ESTABLISHED WITH A CONTROL 2026-09-18 rather than carried forward - the previous note asserted this for FY2014-FY2025 and was already out of date, since the workbook carries FY2026. Whole-document search of the two newest editions, both text-native and downloaded fresh (%PDF-, application/pdf): the FY2026 consolidated Pillar 3 (217,429 characters) returns ZERO hits for 'MREL', 'minimum requirement for own funds' and 'TLAC', against 145 hits for 'capital', 231 for 'ratio' and 10 for 'own funds' in the same extraction; the FY2025 edition (224,343 characters) returns the same three zeros against 152 and 228. So the zero is a fact about the documents, not a failure of the search. The FY2026 Annual Report (696,912 characters) likewise returns zero for all three.
+WHAT THE DOCUMENTS DO SAY, which is consistent with there being nothing to find. The FY2026 Pillar 3 reproduces the PRA's 'UK CCA: Main features of regulatory own funds instruments and eligible liabilities instruments' template - i.e. the template that WOULD carry an eligible-liabilities instrument if MHI had one - and its only instrument is ordinary share capital, with row 34a 'Type of subordination (only for eligible liabilities)' printed 'n/a'. The FY2026 Annual Report states that the Group 'continues to participate actively in Mizuho Financial Group's recovery and resolution planning', i.e. resolution is planned at the Japanese parent level. That is context, not proof of a scope exclusion, and it is recorded as context: what is established here is that MHI publishes no MREL ratio, not why.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="220" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
+Official Mizuho International plc Pillar 3 disclosures: FY2026: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903d9cec6eb609b9981dde_MHI%20consolidated%20Pillar%203%20disclosure%202026.pdf; FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A7:N7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13002,6 +13202,495 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mizuho International plc — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>2.10%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>1.89%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>-0.63%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>-3.96%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>5.94%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>-5.66%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>-2.60%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>3.68%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>2.04%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>-3.41%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>1.11%</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>1.87%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>-0.64%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>-4.04%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>5.77%</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>-5.82%</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>-2.63%</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>3.62%</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>1.66%</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>-3.34%</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>1.11%</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>-6.37%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Mizuho International plc's own published return</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="130" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: COMPUTED, NOT PUBLISHED. Mizuho International plc publishes NO ROE, ROA or RoTE in its Annual Report 2026 (year ended 31 March 2026; 207 pages, Companies House 'Group of companies' accounts made up to 31 March 2026', filed 25 Aug 2026). The filing is a scan with no text layer (pdftotext returns 0 bytes), so all 207 pages were rendered at 120 dpi and OCR'd; searches for 'return on (equity|assets|average|capital|tangible)', '\bROE\b', '\bROA\b', 'RoTE|ROTE' produced only two hits, both 'Return on assets' inside the pension scheme note (PDF pp.125-126), which is the IAS 19 return on plan assets and not a published return measure. The Strategic Report's section 2.4 'Key Metrics' (printed p.10, PDF p.11) carries seven measures - Net income from operations, Operating expenses, Cost to Income Ratio, Leverage Ratio, Liquidity Coverage Ratio, CET1 Ratio, Net Stable Funding Ratio - with footnoted definitions for the four regulatory ratios and no return on equity or assets, despite the preamble saying the metrics 'support management's assessment of profitability'. Every percentage above is therefore this project's own arithmetic on the figures printed on this workbook's statement sheets, and is labelled as such. That the bank publishes none is a POSITIVE FINDING, recorded in research/profitability/published_returns.jsonl, and not a failed search: for this bank the computed figure is the only figure there is.
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return.
+FY2014 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2014 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2014 because it needs only the closing balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “profit/(loss) for the year” and the Balance Sheet rows “total equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from Mizuho International plc's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The finding that Mizuho International plc publishes no return of its own is recorded in research/profitability/published_returns.jsonl under ‘MIZUHO INTERNATIONAL’, verified against the bank's own annual report rendered at 300 dpi.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="A11:N11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -14840,7 +15529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15019,203 +15708,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mizuho International plc — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2026</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>CET1 Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>26.19%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>22.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>28.0%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>31.14%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>31.12%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>20.02%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>27.8%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>30.6%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>32.9%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>49.5%</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>50.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="220" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ENTITY NOTE: Mizuho International plc (company 01203696, FRN 119256; LEI 213800HZ54TG54H2KV03) is the legal entity in Banks List 2608.xlsx. Companies House confirms the active UK public company. Figures are the consolidated Mizuho International plc Group basis used in the official reports, in £ millions. The company accounts use the FRS 102 exemption from preparing a separate company cash-flow statement (or, for FY2014-FY2018, the equivalent predecessor exemption; see the reporting-basis note below for those years).
-Official Mizuho International plc Pillar 3 disclosures: FY2026: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903d9cec6eb609b9981dde_MHI%20consolidated%20Pillar%203%20disclosure%202026.pdf; FY2025: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6a903f20d82fcd0100158b9f_MHI%20consolidated%20Pillar%203%20disclosure%202025.pdf; FY2024: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864747a2fb833ca68387b1e_mhi-consolidated-pillar-3-disclosure-2024-final.pdf; FY2023: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/68647496be5f9b72fe43c3f9_mhi-consolidated-pillar-3-disclosure-2023-final.pdf; FY2022: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686474abd90349ac917e208a_2022-mhi-consolidated-pillar-3-disclosure.pdf; FY2021: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864754eb71eb72dcfb8ec06_2021-mizuho-international-plc-pillar-3-disclosure.pdf; FY2020: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475629a3272fed34cef93_2020-pillar-3-disclosure.pdf; FY2019: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475789a3272fed34cf5a7_2019-pillar-3-disclosure.pdf; FY2018: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864758d6847432aa76ef044_2018-pillar-3-disclosure.pdf; FY2017: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/6864759fa4cb331151bf5ee9_2017-pillar-3-disclosure.pdf; FY2016: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475b6c99b915dfa9735fb_2016-pillar-3-disclosure.pdf; FY2015: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475c97ce484821ccefc82_2015-pillar-3-disclosure.pdf; FY2014: https://cdn.prod.website-files.com/67cb23eaf0c6c4d4080e059a/686475e150ef186144c44568_2014-pillar-3-disclosure.pdf</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:N6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>